--- a/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (QQQ)_v3.xlsx
+++ b/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (QQQ)_v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="27">
   <si>
     <t>High
 Price</t>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V126"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -567,4286 +567,8434 @@
     </row>
     <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="2">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="B3">
-        <v>11.339599609375</v>
+        <v>4.3778076171875</v>
       </c>
       <c r="C3">
-        <v>0.62603759765625</v>
+        <v>8.908935546875</v>
       </c>
       <c r="D3">
-        <v>-6.712646484375</v>
+        <v>18.5191040039063</v>
       </c>
       <c r="E3">
-        <v>688.299987792969</v>
+        <v>725.150024414063</v>
       </c>
       <c r="F3">
-        <v>701.590026855469</v>
+        <v>733.960021972656</v>
       </c>
       <c r="G3">
-        <v>685.820007324219</v>
+        <v>724.030029296875</v>
       </c>
       <c r="H3">
-        <v>700.070007324219</v>
+        <v>732.070007324219</v>
       </c>
       <c r="I3">
-        <v>701.723510742188</v>
+        <v>732.538391113281</v>
       </c>
       <c r="J3">
-        <v>691.503540039063</v>
+        <v>727.682556152344</v>
       </c>
       <c r="K3">
-        <v>44790208</v>
+        <v>31599700</v>
       </c>
       <c r="L3">
-        <v>-0.909996390342712</v>
+        <v>-0.488571882247925</v>
       </c>
       <c r="M3">
-        <v>75.4976272583008</v>
+        <v>40.9084243774414</v>
       </c>
       <c r="N3">
-        <v>-15.1427478790283</v>
+        <v>-31.3219966888428</v>
       </c>
       <c r="O3" t="s">
         <v>1</v>
       </c>
       <c r="P3">
-        <v>66.5761184692383</v>
+        <v>30.4323463439941</v>
       </c>
       <c r="Q3">
-        <v>689.914428710938</v>
+        <v>726.150024414063</v>
       </c>
       <c r="R3">
-        <v>688.366577148438</v>
+        <v>718.895812988281</v>
       </c>
       <c r="S3">
-        <v>695.902160644531</v>
+        <v>711.396850585938</v>
       </c>
       <c r="T3">
-        <v>0.13348388671875</v>
+        <v>-1.421630859375</v>
       </c>
       <c r="U3">
-        <v>5.68353271484375</v>
+        <v>3.65252685546875</v>
       </c>
       <c r="V3">
-        <v>10.219970703125</v>
+        <v>4.8558349609375</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="2">
-        <v>46234</v>
+        <v>46246</v>
       </c>
       <c r="B4">
-        <v>5.615966796875</v>
+        <v>2.327392578125</v>
       </c>
       <c r="C4">
-        <v>-5.2982177734375</v>
+        <v>9.25762939453125</v>
       </c>
       <c r="D4">
-        <v>-11.5888671875</v>
+        <v>17.2620849609375</v>
       </c>
       <c r="E4">
-        <v>692.109985351563</v>
+        <v>727.080017089844</v>
       </c>
       <c r="F4">
-        <v>695.77001953125</v>
+        <v>727.25</v>
       </c>
       <c r="G4">
-        <v>680.051208496094</v>
+        <v>722.919982910156</v>
       </c>
       <c r="H4">
-        <v>687.989990234375</v>
+        <v>723.700012207031</v>
       </c>
       <c r="I4">
-        <v>690.9306640625</v>
+        <v>726.914245605469</v>
       </c>
       <c r="J4">
-        <v>681.263366699219</v>
+        <v>721.6142578125</v>
       </c>
       <c r="K4">
-        <v>50540400</v>
+        <v>29065900</v>
       </c>
       <c r="L4">
-        <v>-2.08857083320618</v>
+        <v>-1.10904657840729</v>
       </c>
       <c r="M4">
-        <v>88.9701538085938</v>
+        <v>59.5655403137207</v>
       </c>
       <c r="N4">
-        <v>2.25866198539734</v>
+        <v>-8.88726615905762</v>
       </c>
       <c r="O4" t="s">
         <v>1</v>
       </c>
       <c r="P4">
-        <v>67.7133255004883</v>
+        <v>18.1262340545654</v>
       </c>
       <c r="Q4">
-        <v>682.060668945313</v>
+        <v>721.5166015625</v>
       </c>
       <c r="R4">
-        <v>685.576721191406</v>
+        <v>715.153076171875</v>
       </c>
       <c r="S4">
-        <v>695.608276367188</v>
+        <v>709.211975097656</v>
       </c>
       <c r="T4">
-        <v>-4.83935546875</v>
+        <v>-0.33575439453125</v>
       </c>
       <c r="U4">
-        <v>1.212158203125</v>
+        <v>-1.30572509765625</v>
       </c>
       <c r="V4">
-        <v>9.66729736328125</v>
+        <v>5.29998779296875</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="2">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="B5">
-        <v>0.4974365234375</v>
+        <v>0.384765625</v>
       </c>
       <c r="C5">
-        <v>-9.81195068359375</v>
+        <v>12.8827514648438</v>
       </c>
       <c r="D5">
-        <v>-15.7636108398438</v>
+        <v>15.763671875</v>
       </c>
       <c r="E5">
-        <v>674.760009765625</v>
+        <v>723.289978027344</v>
       </c>
       <c r="F5">
-        <v>685.119995117188</v>
+        <v>723.349975585938</v>
       </c>
       <c r="G5">
-        <v>673.299987792969</v>
+        <v>715.5</v>
       </c>
       <c r="H5">
-        <v>683.549987792969</v>
+        <v>718.450012207031</v>
       </c>
       <c r="I5">
-        <v>687.009155273438</v>
+        <v>721.348022460938</v>
       </c>
       <c r="J5">
-        <v>678.221374511719</v>
+        <v>715.432067871094</v>
       </c>
       <c r="K5">
-        <v>66753600</v>
+        <v>29286100</v>
       </c>
       <c r="L5">
-        <v>-2.08381009101868</v>
+        <v>-0.973330557346344</v>
       </c>
       <c r="M5">
-        <v>87.0050048828125</v>
+        <v>65.3756484985352</v>
       </c>
       <c r="N5">
-        <v>-12.9949884414673</v>
+        <v>2.9482729434967</v>
       </c>
       <c r="O5" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P5">
-        <v>68.3619155883789</v>
+        <v>-9.89096736907959</v>
       </c>
       <c r="Q5">
-        <v>677.404541015625</v>
+        <v>718.969360351563</v>
       </c>
       <c r="R5">
-        <v>684.794189453125</v>
+        <v>712.544189453125</v>
       </c>
       <c r="S5">
-        <v>696.5146484375</v>
+        <v>707.421081542969</v>
       </c>
       <c r="T5">
-        <v>1.88916015625</v>
+        <v>-2.001953125</v>
       </c>
       <c r="U5">
-        <v>4.92138671875</v>
+        <v>-0.06793212890625</v>
       </c>
       <c r="V5">
-        <v>8.78778076171875</v>
+        <v>5.91595458984375</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="2">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="B6">
-        <v>-11.2006225585938</v>
+        <v>0.97235107421875</v>
       </c>
       <c r="C6">
-        <v>-15.3350219726563</v>
+        <v>16.9237670898438</v>
       </c>
       <c r="D6">
-        <v>-19.4429321289063</v>
+        <v>15.2864379882813</v>
       </c>
       <c r="E6">
-        <v>675.510009765625</v>
+        <v>722.390014648438</v>
       </c>
       <c r="F6">
-        <v>680.049987792969</v>
+        <v>724.669982910156</v>
       </c>
       <c r="G6">
-        <v>661.140014648438</v>
+        <v>720.330017089844</v>
       </c>
       <c r="H6">
-        <v>661.72998046875</v>
+        <v>720.869995117188</v>
       </c>
       <c r="I6">
-        <v>670.015625</v>
+        <v>724.498474121094</v>
       </c>
       <c r="J6">
-        <v>656.316345214844</v>
+        <v>718.993835449219</v>
       </c>
       <c r="K6">
-        <v>57233200</v>
+        <v>26243100</v>
       </c>
       <c r="L6">
-        <v>-1.9204740524292</v>
+        <v>-1.02761697769165</v>
       </c>
       <c r="M6">
-        <v>99.9999923706055</v>
+        <v>63.5033950805664</v>
       </c>
       <c r="N6">
-        <v>3.20350408554077</v>
+        <v>4.0243992805481</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>-68.9146041870117</v>
+        <v>9.99762535095215</v>
       </c>
       <c r="Q6">
-        <v>671.892639160156</v>
+        <v>719.53515625</v>
       </c>
       <c r="R6">
-        <v>685.085021972656</v>
+        <v>710.855163574219</v>
       </c>
       <c r="S6">
-        <v>697.902770996094</v>
+        <v>706.193542480469</v>
       </c>
       <c r="T6">
-        <v>-10.0343627929688</v>
+        <v>-0.1715087890625</v>
       </c>
       <c r="U6">
-        <v>-4.82366943359375</v>
+        <v>-1.336181640625</v>
       </c>
       <c r="V6">
-        <v>13.6992797851563</v>
+        <v>5.504638671875</v>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="2">
-        <v>46231</v>
+        <v>46241</v>
       </c>
       <c r="B7">
-        <v>-9.48968505859375</v>
+        <v>4.0394287109375</v>
       </c>
       <c r="C7">
-        <v>-12.2387084960938</v>
+        <v>18.4527587890625</v>
       </c>
       <c r="D7">
-        <v>-15.5038452148438</v>
+        <v>14.3407592773438</v>
       </c>
       <c r="E7">
-        <v>676.22998046875</v>
+        <v>720.150024414063</v>
       </c>
       <c r="F7">
-        <v>679.400024414063</v>
+        <v>723.630004882813</v>
       </c>
       <c r="G7">
-        <v>667.880004882813</v>
+        <v>716.510009765625</v>
       </c>
       <c r="H7">
-        <v>675.489990234375</v>
+        <v>723.030029296875</v>
       </c>
       <c r="I7">
-        <v>681.398559570313</v>
+        <v>726.10888671875</v>
       </c>
       <c r="J7">
-        <v>669.311828613281</v>
+        <v>718.251037597656</v>
       </c>
       <c r="K7">
-        <v>51398700</v>
+        <v>31070300</v>
       </c>
       <c r="L7">
-        <v>-0.783804774284363</v>
+        <v>-0.726187586784363</v>
       </c>
       <c r="M7">
-        <v>96.8959274291992</v>
+        <v>61.0466346740723</v>
       </c>
       <c r="N7">
-        <v>5.64116907119751</v>
+        <v>-0.528325259685516</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>-45.0695037841797</v>
+        <v>26.1653099060059</v>
       </c>
       <c r="Q7">
-        <v>681.100524902344</v>
+        <v>717.619018554688</v>
       </c>
       <c r="R7">
-        <v>691.612365722656</v>
+        <v>707.809143066406</v>
       </c>
       <c r="S7">
-        <v>701.984680175781</v>
+        <v>704.476501464844</v>
       </c>
       <c r="T7">
-        <v>1.99853515625</v>
+        <v>2.4788818359375</v>
       </c>
       <c r="U7">
-        <v>1.43182373046875</v>
+        <v>1.74102783203125</v>
       </c>
       <c r="V7">
-        <v>12.0867309570313</v>
+        <v>7.85784912109375</v>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="2">
-        <v>46230</v>
+        <v>46240</v>
       </c>
       <c r="B8">
-        <v>-10.3001098632813</v>
+        <v>5.7655029296875</v>
       </c>
       <c r="C8">
-        <v>-11.3073120117188</v>
+        <v>17.0516967773438</v>
       </c>
       <c r="D8">
-        <v>-12.7749633789063</v>
+        <v>11.1168212890625</v>
       </c>
       <c r="E8">
-        <v>691.679992675781</v>
+        <v>710.820007324219</v>
       </c>
       <c r="F8">
-        <v>692.299987792969</v>
+        <v>719.320007324219</v>
       </c>
       <c r="G8">
-        <v>675.945007324219</v>
+        <v>708.5</v>
       </c>
       <c r="H8">
-        <v>682.119995117188</v>
+        <v>714.650024414063</v>
       </c>
       <c r="I8">
-        <v>687.197937011719</v>
+        <v>718.173400878906</v>
       </c>
       <c r="J8">
-        <v>676.772521972656</v>
+        <v>708.951232910156</v>
       </c>
       <c r="K8">
-        <v>42681400</v>
+        <v>33035800</v>
       </c>
       <c r="L8">
-        <v>-0.777614057064056</v>
+        <v>-0.627615809440613</v>
       </c>
       <c r="M8">
-        <v>91.7217483520508</v>
+        <v>61.3708724975586</v>
       </c>
       <c r="N8">
-        <v>28.3568496704102</v>
+        <v>-10.5575513839722</v>
       </c>
       <c r="O8" t="s">
         <v>23</v>
       </c>
       <c r="P8">
-        <v>-35.6940422058105</v>
+        <v>-23.3668766021729</v>
       </c>
       <c r="Q8">
-        <v>686.793579101563</v>
+        <v>712.781005859375</v>
       </c>
       <c r="R8">
-        <v>696.032958984375</v>
+        <v>703.359313964844</v>
       </c>
       <c r="S8">
-        <v>705.08837890625</v>
+        <v>702.144226074219</v>
       </c>
       <c r="T8">
-        <v>-5.10205078125</v>
+        <v>-1.1466064453125</v>
       </c>
       <c r="U8">
-        <v>0.8275146484375</v>
+        <v>0.45123291015625</v>
       </c>
       <c r="V8">
-        <v>10.4254150390625</v>
+        <v>9.22216796875</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="2">
-        <v>46227</v>
+        <v>46239</v>
       </c>
       <c r="B9">
-        <v>-8.69158935546875</v>
+        <v>13.2140502929688</v>
       </c>
       <c r="C9">
-        <v>-9.875</v>
+        <v>17.2907104492188</v>
       </c>
       <c r="D9">
-        <v>-11.1927490234375</v>
+        <v>8.81109619140625</v>
       </c>
       <c r="E9">
-        <v>690.409973144531</v>
+        <v>726.25</v>
       </c>
       <c r="F9">
-        <v>692.630004882813</v>
+        <v>728.539978027344</v>
       </c>
       <c r="G9">
-        <v>682.47998046875</v>
+        <v>716.919982910156</v>
       </c>
       <c r="H9">
-        <v>684.22998046875</v>
+        <v>717.299987792969</v>
       </c>
       <c r="I9">
-        <v>690.563537597656</v>
+        <v>722.862182617188</v>
       </c>
       <c r="J9">
-        <v>679.935974121094</v>
+        <v>712.977844238281</v>
       </c>
       <c r="K9">
-        <v>42876600</v>
+        <v>33540100</v>
       </c>
       <c r="L9">
-        <v>-0.775710344314575</v>
+        <v>-0.500950396060944</v>
       </c>
       <c r="M9">
-        <v>71.4583969116211</v>
+        <v>68.6149291992188</v>
       </c>
       <c r="N9">
-        <v>26.3548107147217</v>
+        <v>15.4603137969971</v>
       </c>
       <c r="O9" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>-63.8044128417969</v>
+        <v>28.8229656219482</v>
       </c>
       <c r="Q9">
-        <v>691.569458007813</v>
+        <v>711.650634765625</v>
       </c>
       <c r="R9">
-        <v>699.823181152344</v>
+        <v>700.618591308594</v>
       </c>
       <c r="S9">
-        <v>707.758605957031</v>
+        <v>700.785400390625</v>
       </c>
       <c r="T9">
-        <v>-2.06646728515625</v>
+        <v>-5.67779541015625</v>
       </c>
       <c r="U9">
-        <v>-2.54400634765625</v>
+        <v>-3.942138671875</v>
       </c>
       <c r="V9">
-        <v>10.6275634765625</v>
+        <v>9.88433837890625</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="2">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="B10">
-        <v>-3.48541259765625</v>
+        <v>20.4347534179688</v>
       </c>
       <c r="C10">
-        <v>-8.06353759765625</v>
+        <v>12.6027221679688</v>
       </c>
       <c r="D10">
-        <v>-8.079833984375</v>
+        <v>3.1591796875</v>
       </c>
       <c r="E10">
-        <v>694.669982910156</v>
+        <v>708.159973144531</v>
       </c>
       <c r="F10">
-        <v>698.659973144531</v>
+        <v>725.659973144531</v>
       </c>
       <c r="G10">
-        <v>687.789978027344</v>
+        <v>707.530029296875</v>
       </c>
       <c r="H10">
-        <v>691.960021972656</v>
+        <v>723.849975585938</v>
       </c>
       <c r="I10">
-        <v>696.182250976563</v>
+        <v>724.495361328125</v>
       </c>
       <c r="J10">
-        <v>686.057800292969</v>
+        <v>715.428039550781</v>
       </c>
       <c r="K10">
-        <v>44028500</v>
+        <v>59778600</v>
       </c>
       <c r="L10">
-        <v>-0.707615435123444</v>
+        <v>-0.300473153591156</v>
       </c>
       <c r="M10">
-        <v>56.5537605285645</v>
+        <v>59.4272842407227</v>
       </c>
       <c r="N10">
-        <v>7.45290517807007</v>
+        <v>-21.2858924865723</v>
       </c>
       <c r="O10" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>-56.6292991638184</v>
+        <v>100.000007629395</v>
       </c>
       <c r="Q10">
-        <v>698.227111816406</v>
+        <v>705.591552734375</v>
       </c>
       <c r="R10">
-        <v>704.183776855469</v>
+        <v>695.908142089844</v>
       </c>
       <c r="S10">
-        <v>710.521728515625</v>
+        <v>698.772827148438</v>
       </c>
       <c r="T10">
-        <v>-2.47772216796875</v>
+        <v>-1.16461181640625</v>
       </c>
       <c r="U10">
-        <v>-1.732177734375</v>
+        <v>7.89801025390625</v>
       </c>
       <c r="V10">
-        <v>10.1244506835938</v>
+        <v>9.06732177734375</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="2">
-        <v>46225</v>
+        <v>46237</v>
       </c>
       <c r="B11">
-        <v>3.01220703125</v>
+        <v>11.339599609375</v>
       </c>
       <c r="C11">
-        <v>-5.4625244140625</v>
+        <v>0.62603759765625</v>
       </c>
       <c r="D11">
-        <v>-6.10992431640625</v>
+        <v>-6.712646484375</v>
       </c>
       <c r="E11">
-        <v>703.619995117188</v>
+        <v>688.299987792969</v>
       </c>
       <c r="F11">
-        <v>709.650024414063</v>
+        <v>701.590026855469</v>
       </c>
       <c r="G11">
-        <v>703.619995117188</v>
+        <v>685.820007324219</v>
       </c>
       <c r="H11">
-        <v>705.349975585938</v>
+        <v>700.070007324219</v>
       </c>
       <c r="I11">
-        <v>708.769348144531</v>
+        <v>701.723510742188</v>
       </c>
       <c r="J11">
-        <v>701.754638671875</v>
+        <v>691.503540039063</v>
       </c>
       <c r="K11">
-        <v>23692100</v>
+        <v>44965000</v>
       </c>
       <c r="L11">
-        <v>-0.678091883659363</v>
+        <v>-0.909996390342712</v>
       </c>
       <c r="M11">
-        <v>52.6312065124512</v>
+        <v>75.4976272583008</v>
       </c>
       <c r="N11">
-        <v>-15.308910369873</v>
+        <v>-15.1427478790283</v>
       </c>
       <c r="O11" t="s">
         <v>1</v>
       </c>
       <c r="P11">
-        <v>10.9916353225708</v>
+        <v>66.5761184692383</v>
       </c>
       <c r="Q11">
-        <v>705.042114257813</v>
+        <v>689.914428710938</v>
       </c>
       <c r="R11">
-        <v>707.900085449219</v>
+        <v>688.366577148438</v>
       </c>
       <c r="S11">
-        <v>712.692932128906</v>
+        <v>695.902160644531</v>
       </c>
       <c r="T11">
-        <v>-0.88067626953125</v>
+        <v>0.13348388671875</v>
       </c>
       <c r="U11">
-        <v>-1.8653564453125</v>
+        <v>5.68353271484375</v>
       </c>
       <c r="V11">
-        <v>7.01470947265625</v>
+        <v>10.219970703125</v>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="2">
-        <v>46224</v>
+        <v>46234</v>
       </c>
       <c r="B12">
-        <v>0.6416015625</v>
+        <v>5.615966796875</v>
       </c>
       <c r="C12">
-        <v>-6.202392578125</v>
+        <v>-5.2982177734375</v>
       </c>
       <c r="D12">
-        <v>-7.814697265625</v>
+        <v>-11.5888671875</v>
       </c>
       <c r="E12">
-        <v>706.570007324219</v>
+        <v>692.109985351563</v>
       </c>
       <c r="F12">
-        <v>710.049987792969</v>
+        <v>695.77001953125</v>
       </c>
       <c r="G12">
-        <v>702.799987792969</v>
+        <v>680.051208496094</v>
       </c>
       <c r="H12">
-        <v>708.969970703125</v>
+        <v>687.989990234375</v>
       </c>
       <c r="I12">
-        <v>712.483276367188</v>
+        <v>690.9306640625</v>
       </c>
       <c r="J12">
-        <v>705.233276367188</v>
+        <v>681.263366699219</v>
       </c>
       <c r="K12">
-        <v>33728300</v>
+        <v>50540400</v>
       </c>
       <c r="L12">
-        <v>-0.954281747341156</v>
+        <v>-2.08857083320618</v>
       </c>
       <c r="M12">
-        <v>62.1449165344238</v>
+        <v>88.9701538085938</v>
       </c>
       <c r="N12">
-        <v>-6.62933874130249</v>
+        <v>2.25866198539734</v>
       </c>
       <c r="O12" t="s">
         <v>1</v>
       </c>
       <c r="P12">
-        <v>48.3449096679688</v>
+        <v>67.7133255004883</v>
       </c>
       <c r="Q12">
-        <v>704.79150390625</v>
+        <v>682.060668945313</v>
       </c>
       <c r="R12">
-        <v>708.46826171875</v>
+        <v>685.576721191406</v>
       </c>
       <c r="S12">
-        <v>713.447265625</v>
+        <v>695.608276367188</v>
       </c>
       <c r="T12">
-        <v>2.43328857421875</v>
+        <v>-4.83935546875</v>
       </c>
       <c r="U12">
-        <v>2.43328857421875</v>
+        <v>1.212158203125</v>
       </c>
       <c r="V12">
-        <v>7.25</v>
+        <v>9.66729736328125</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="2">
-        <v>46223</v>
+        <v>46233</v>
       </c>
       <c r="B13">
-        <v>-8.39520263671875</v>
+        <v>0.4974365234375</v>
       </c>
       <c r="C13">
-        <v>-8.765380859375</v>
+        <v>-9.81195068359375</v>
       </c>
       <c r="D13">
-        <v>-9.8062744140625</v>
+        <v>-15.7636108398438</v>
       </c>
       <c r="E13">
-        <v>702.159973144531</v>
+        <v>674.760009765625</v>
       </c>
       <c r="F13">
-        <v>705.799987792969</v>
+        <v>685.119995117188</v>
       </c>
       <c r="G13">
-        <v>695.510009765625</v>
+        <v>673.299987792969</v>
       </c>
       <c r="H13">
-        <v>696.059997558594</v>
+        <v>683.549987792969</v>
       </c>
       <c r="I13">
-        <v>703.789184570313</v>
+        <v>687.009155273438</v>
       </c>
       <c r="J13">
-        <v>693.406494140625</v>
+        <v>678.221374511719</v>
       </c>
       <c r="K13">
-        <v>29687500</v>
+        <v>66753600</v>
       </c>
       <c r="L13">
-        <v>-0.905709385871887</v>
+        <v>-2.08381009101868</v>
       </c>
       <c r="M13">
-        <v>66.5572204589844</v>
+        <v>87.0050048828125</v>
       </c>
       <c r="N13">
-        <v>22.5973968505859</v>
+        <v>-12.9949884414673</v>
       </c>
       <c r="O13" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>-6.00122213363647</v>
+        <v>68.3619155883789</v>
       </c>
       <c r="Q13">
-        <v>700.701416015625</v>
+        <v>677.404541015625</v>
       </c>
       <c r="R13">
-        <v>708.291809082031</v>
+        <v>684.794189453125</v>
       </c>
       <c r="S13">
-        <v>713.96923828125</v>
+        <v>696.5146484375</v>
       </c>
       <c r="T13">
-        <v>-2.01080322265625</v>
+        <v>1.88916015625</v>
       </c>
       <c r="U13">
-        <v>-2.103515625</v>
+        <v>4.92138671875</v>
       </c>
       <c r="V13">
-        <v>10.3826904296875</v>
+        <v>8.78778076171875</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="2">
-        <v>46220</v>
+        <v>46232</v>
       </c>
       <c r="B14">
-        <v>-9.927001953125</v>
+        <v>-11.2006225585938</v>
       </c>
       <c r="C14">
-        <v>-7.9847412109375</v>
+        <v>-15.3350219726563</v>
       </c>
       <c r="D14">
-        <v>-7.42694091796875</v>
+        <v>-19.4429321289063</v>
       </c>
       <c r="E14">
-        <v>691.650024414063</v>
+        <v>675.510009765625</v>
       </c>
       <c r="F14">
-        <v>702.299987792969</v>
+        <v>680.049987792969</v>
       </c>
       <c r="G14">
-        <v>686.760009765625</v>
+        <v>661.140014648438</v>
       </c>
       <c r="H14">
-        <v>695.330017089844</v>
+        <v>661.72998046875</v>
       </c>
       <c r="I14">
-        <v>701.341003417969</v>
+        <v>670.015625</v>
       </c>
       <c r="J14">
-        <v>688.661193847656</v>
+        <v>656.316345214844</v>
       </c>
       <c r="K14">
-        <v>54109200</v>
+        <v>57233200</v>
       </c>
       <c r="L14">
-        <v>-1.21904349327087</v>
+        <v>-1.9204740524292</v>
       </c>
       <c r="M14">
-        <v>54.2892608642578</v>
+        <v>99.9999923706055</v>
       </c>
       <c r="N14">
-        <v>8.37738990783691</v>
+        <v>3.20350408554077</v>
       </c>
       <c r="O14" t="s">
         <v>23</v>
       </c>
       <c r="P14">
-        <v>-64.7480239868164</v>
+        <v>-68.9146041870117</v>
       </c>
       <c r="Q14">
-        <v>703.639892578125</v>
+        <v>671.892639160156</v>
       </c>
       <c r="R14">
-        <v>711.3662109375</v>
+        <v>685.085021972656</v>
       </c>
       <c r="S14">
-        <v>715.791137695313</v>
+        <v>697.902770996094</v>
       </c>
       <c r="T14">
-        <v>-0.958984375</v>
+        <v>-10.0343627929688</v>
       </c>
       <c r="U14">
-        <v>1.90118408203125</v>
+        <v>-4.82366943359375</v>
       </c>
       <c r="V14">
-        <v>12.6798095703125</v>
+        <v>13.6992797851563</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="2">
-        <v>46219</v>
+        <v>46231</v>
       </c>
       <c r="B15">
-        <v>-5.863037109375</v>
+        <v>-9.48968505859375</v>
       </c>
       <c r="C15">
-        <v>-2.36517333984375</v>
+        <v>-12.2387084960938</v>
       </c>
       <c r="D15">
-        <v>-3.09661865234375</v>
+        <v>-15.5038452148438</v>
       </c>
       <c r="E15">
-        <v>712.010009765625</v>
+        <v>676.22998046875</v>
       </c>
       <c r="F15">
-        <v>713.598999023438</v>
+        <v>679.400024414063</v>
       </c>
       <c r="G15">
-        <v>702.609985351563</v>
+        <v>667.880004882813</v>
       </c>
       <c r="H15">
-        <v>705.940002441406</v>
+        <v>675.489990234375</v>
       </c>
       <c r="I15">
-        <v>712.521850585938</v>
+        <v>681.398559570313</v>
       </c>
       <c r="J15">
-        <v>701.248962402344</v>
+        <v>669.311828613281</v>
       </c>
       <c r="K15">
-        <v>39402000</v>
+        <v>51398700</v>
       </c>
       <c r="L15">
-        <v>-1.98428201675415</v>
+        <v>-0.783804774284363</v>
       </c>
       <c r="M15">
-        <v>50.0927925109863</v>
+        <v>96.8959274291992</v>
       </c>
       <c r="N15">
-        <v>7.75767660140991</v>
+        <v>5.64116907119751</v>
       </c>
       <c r="O15" t="s">
         <v>23</v>
       </c>
       <c r="P15">
-        <v>-43.6580963134766</v>
+        <v>-45.0695037841797</v>
       </c>
       <c r="Q15">
-        <v>712.182556152344</v>
+        <v>681.100524902344</v>
       </c>
       <c r="R15">
-        <v>715.892822265625</v>
+        <v>691.612365722656</v>
       </c>
       <c r="S15">
-        <v>718.15576171875</v>
+        <v>701.984680175781</v>
       </c>
       <c r="T15">
-        <v>-1.0771484375</v>
+        <v>1.99853515625</v>
       </c>
       <c r="U15">
-        <v>-1.36102294921875</v>
+        <v>1.43182373046875</v>
       </c>
       <c r="V15">
-        <v>11.2728881835938</v>
+        <v>12.0867309570313</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="2">
-        <v>46218</v>
+        <v>46230</v>
       </c>
       <c r="B16">
-        <v>-1.943359375</v>
+        <v>-10.3001098632813</v>
       </c>
       <c r="C16">
-        <v>0.40814208984375</v>
+        <v>-11.3073120117188</v>
       </c>
       <c r="D16">
-        <v>-0.0054931640625</v>
+        <v>-12.7749633789063</v>
       </c>
       <c r="E16">
-        <v>723.849975585938</v>
+        <v>691.679992675781</v>
       </c>
       <c r="F16">
-        <v>724.359985351563</v>
+        <v>692.299987792969</v>
       </c>
       <c r="G16">
-        <v>710.22998046875</v>
+        <v>675.945007324219</v>
       </c>
       <c r="H16">
-        <v>717.739990234375</v>
+        <v>682.119995117188</v>
       </c>
       <c r="I16">
-        <v>721.251037597656</v>
+        <v>687.197937011719</v>
       </c>
       <c r="J16">
-        <v>712.604736328125</v>
+        <v>676.772521972656</v>
       </c>
       <c r="K16">
-        <v>32627500</v>
+        <v>42681400</v>
       </c>
       <c r="L16">
-        <v>-1.41428053379059</v>
+        <v>-0.777614057064056</v>
       </c>
       <c r="M16">
-        <v>46.4865188598633</v>
+        <v>91.7217483520508</v>
       </c>
       <c r="N16">
-        <v>-4.76508235931396</v>
+        <v>28.3568496704102</v>
       </c>
       <c r="O16" t="s">
         <v>23</v>
       </c>
       <c r="P16">
-        <v>-2.18429470062256</v>
+        <v>-35.6940422058105</v>
       </c>
       <c r="Q16">
-        <v>717.8037109375</v>
+        <v>686.793579101563</v>
       </c>
       <c r="R16">
-        <v>718.531005859375</v>
+        <v>696.032958984375</v>
       </c>
       <c r="S16">
-        <v>719.552307128906</v>
+        <v>705.08837890625</v>
       </c>
       <c r="T16">
-        <v>-3.10894775390625</v>
+        <v>-5.10205078125</v>
       </c>
       <c r="U16">
-        <v>2.374755859375</v>
+        <v>0.8275146484375</v>
       </c>
       <c r="V16">
-        <v>8.64630126953125</v>
+        <v>10.4254150390625</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="2">
-        <v>46217</v>
+        <v>46227</v>
       </c>
       <c r="B17">
-        <v>0.21160888671875</v>
+        <v>-8.69158935546875</v>
       </c>
       <c r="C17">
-        <v>-1.59527587890625</v>
+        <v>-9.875</v>
       </c>
       <c r="D17">
-        <v>0.46612548828125</v>
+        <v>-11.1927490234375</v>
       </c>
       <c r="E17">
-        <v>720.219970703125</v>
+        <v>690.409973144531</v>
       </c>
       <c r="F17">
-        <v>722.289978027344</v>
+        <v>692.630004882813</v>
       </c>
       <c r="G17">
-        <v>714.340026855469</v>
+        <v>682.47998046875</v>
       </c>
       <c r="H17">
-        <v>719.690002441406</v>
+        <v>684.22998046875</v>
       </c>
       <c r="I17">
-        <v>723.544555664063</v>
+        <v>690.563537597656</v>
       </c>
       <c r="J17">
-        <v>716.334533691406</v>
+        <v>679.935974121094</v>
       </c>
       <c r="K17">
-        <v>29448100</v>
+        <v>42876600</v>
       </c>
       <c r="L17">
-        <v>-0.94570779800415</v>
+        <v>-0.775710344314575</v>
       </c>
       <c r="M17">
-        <v>48.8124732971191</v>
+        <v>71.4583969116211</v>
       </c>
       <c r="N17">
-        <v>-5.16571569442749</v>
+        <v>26.3548107147217</v>
       </c>
       <c r="O17" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P17">
-        <v>5.93372297286987</v>
+        <v>-63.8044128417969</v>
       </c>
       <c r="Q17">
-        <v>718.3955078125</v>
+        <v>691.569458007813</v>
       </c>
       <c r="R17">
-        <v>718.438903808594</v>
+        <v>699.823181152344</v>
       </c>
       <c r="S17">
-        <v>719.708923339844</v>
+        <v>707.758605957031</v>
       </c>
       <c r="T17">
-        <v>1.25457763671875</v>
+        <v>-2.06646728515625</v>
       </c>
       <c r="U17">
-        <v>1.9945068359375</v>
+        <v>-2.54400634765625</v>
       </c>
       <c r="V17">
-        <v>7.21002197265625</v>
+        <v>10.6275634765625</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="2">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="B18">
-        <v>-0.3555908203125</v>
+        <v>-3.48541259765625</v>
       </c>
       <c r="C18">
-        <v>-3.0672607421875</v>
+        <v>-8.06353759765625</v>
       </c>
       <c r="D18">
-        <v>-1.38330078125</v>
+        <v>-8.079833984375</v>
       </c>
       <c r="E18">
-        <v>717.719970703125</v>
+        <v>694.669982910156</v>
       </c>
       <c r="F18">
-        <v>718.739990234375</v>
+        <v>698.659973144531</v>
       </c>
       <c r="G18">
-        <v>710.080017089844</v>
+        <v>687.789978027344</v>
       </c>
       <c r="H18">
-        <v>711.739990234375</v>
+        <v>691.960021972656</v>
       </c>
       <c r="I18">
-        <v>717.577209472656</v>
+        <v>696.182250976563</v>
       </c>
       <c r="J18">
-        <v>707.793212890625</v>
+        <v>686.057800292969</v>
       </c>
       <c r="K18">
-        <v>36552300</v>
+        <v>44028500</v>
       </c>
       <c r="L18">
-        <v>-0.0714227557182312</v>
+        <v>-0.707615435123444</v>
       </c>
       <c r="M18">
-        <v>51.4713363647461</v>
+        <v>56.5537605285645</v>
       </c>
       <c r="N18">
-        <v>4.72496747970581</v>
+        <v>7.45290517807007</v>
       </c>
       <c r="O18" t="s">
         <v>23</v>
       </c>
       <c r="P18">
-        <v>-42.1362648010254</v>
+        <v>-56.6292991638184</v>
       </c>
       <c r="Q18">
-        <v>716.920593261719</v>
+        <v>698.227111816406</v>
       </c>
       <c r="R18">
-        <v>718.116577148438</v>
+        <v>704.183776855469</v>
       </c>
       <c r="S18">
-        <v>719.618469238281</v>
+        <v>710.521728515625</v>
       </c>
       <c r="T18">
-        <v>-1.16278076171875</v>
+        <v>-2.47772216796875</v>
       </c>
       <c r="U18">
-        <v>-2.28680419921875</v>
+        <v>-1.732177734375</v>
       </c>
       <c r="V18">
-        <v>9.78399658203125</v>
+        <v>10.1244506835938</v>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="2">
-        <v>46213</v>
+        <v>46225</v>
       </c>
       <c r="B19">
-        <v>4.54119873046875</v>
+        <v>3.01220703125</v>
       </c>
       <c r="C19">
-        <v>1.09893798828125</v>
+        <v>-5.4625244140625</v>
       </c>
       <c r="D19">
-        <v>-0.62530517578125</v>
+        <v>-6.10992431640625</v>
       </c>
       <c r="E19">
-        <v>720.700012207031</v>
+        <v>703.619995117188</v>
       </c>
       <c r="F19">
-        <v>726.390014648438</v>
+        <v>709.650024414063</v>
       </c>
       <c r="G19">
-        <v>717</v>
+        <v>703.619995117188</v>
       </c>
       <c r="H19">
-        <v>725.510009765625</v>
+        <v>705.349975585938</v>
       </c>
       <c r="I19">
-        <v>728.048034667969</v>
+        <v>708.769348144531</v>
       </c>
       <c r="J19">
-        <v>721.283996582031</v>
+        <v>701.754638671875</v>
       </c>
       <c r="K19">
-        <v>26415900</v>
+        <v>23692100</v>
       </c>
       <c r="L19">
-        <v>-0.166184201836586</v>
+        <v>-0.678091883659363</v>
       </c>
       <c r="M19">
-        <v>49.1490592956543</v>
+        <v>52.6312065124512</v>
       </c>
       <c r="N19">
-        <v>-9.55446624755859</v>
+        <v>-15.308910369873</v>
       </c>
       <c r="O19" t="s">
         <v>1</v>
       </c>
       <c r="P19">
-        <v>29.1831836700439</v>
+        <v>10.9916353225708</v>
       </c>
       <c r="Q19">
-        <v>721.479248046875</v>
+        <v>705.042114257813</v>
       </c>
       <c r="R19">
-        <v>719.98193359375</v>
+        <v>707.900085449219</v>
       </c>
       <c r="S19">
-        <v>720.620422363281</v>
+        <v>712.692932128906</v>
       </c>
       <c r="T19">
-        <v>1.65802001953125</v>
+        <v>-0.88067626953125</v>
       </c>
       <c r="U19">
-        <v>4.28399658203125</v>
+        <v>-1.8653564453125</v>
       </c>
       <c r="V19">
-        <v>6.7640380859375</v>
+        <v>7.01470947265625</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="2">
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="B20">
-        <v>3.296630859375</v>
+        <v>0.6416015625</v>
       </c>
       <c r="C20">
-        <v>-0.72021484375</v>
+        <v>-6.202392578125</v>
       </c>
       <c r="D20">
-        <v>-2.30474853515625</v>
+        <v>-7.814697265625</v>
       </c>
       <c r="E20">
-        <v>718.330017089844</v>
+        <v>706.570007324219</v>
       </c>
       <c r="F20">
-        <v>724.22998046875</v>
+        <v>710.049987792969</v>
       </c>
       <c r="G20">
-        <v>715.125</v>
+        <v>702.799987792969</v>
       </c>
       <c r="H20">
-        <v>723.280029296875</v>
+        <v>708.969970703125</v>
       </c>
       <c r="I20">
-        <v>726.686767578125</v>
+        <v>712.483276367188</v>
       </c>
       <c r="J20">
-        <v>719.118225097656</v>
+        <v>705.233276367188</v>
       </c>
       <c r="K20">
-        <v>33654700</v>
+        <v>33728300</v>
       </c>
       <c r="L20">
-        <v>-1.11665856838226</v>
+        <v>-0.954281747341156</v>
       </c>
       <c r="M20">
-        <v>54.3410568237305</v>
+        <v>62.1449165344238</v>
       </c>
       <c r="N20">
-        <v>-1.37647461891174</v>
+        <v>-6.62933874130249</v>
       </c>
       <c r="O20" t="s">
         <v>1</v>
       </c>
       <c r="P20">
-        <v>56.2780990600586</v>
+        <v>48.3449096679688</v>
       </c>
       <c r="Q20">
-        <v>718.006164550781</v>
+        <v>704.79150390625</v>
       </c>
       <c r="R20">
-        <v>718.503051757813</v>
+        <v>708.46826171875</v>
       </c>
       <c r="S20">
-        <v>720.065307617188</v>
+        <v>713.447265625</v>
       </c>
       <c r="T20">
-        <v>2.456787109375</v>
+        <v>2.43328857421875</v>
       </c>
       <c r="U20">
-        <v>3.99322509765625</v>
+        <v>2.43328857421875</v>
       </c>
       <c r="V20">
-        <v>7.56854248046875</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="2">
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="B21">
-        <v>-4.7235107421875</v>
+        <v>-8.39520263671875</v>
       </c>
       <c r="C21">
-        <v>-3.04364013671875</v>
+        <v>-8.765380859375</v>
       </c>
       <c r="D21">
-        <v>-5.07476806640625</v>
+        <v>-9.8062744140625</v>
       </c>
       <c r="E21">
-        <v>704.950012207031</v>
+        <v>702.159973144531</v>
       </c>
       <c r="F21">
-        <v>712.259887695313</v>
+        <v>705.799987792969</v>
       </c>
       <c r="G21">
-        <v>700.909973144531</v>
+        <v>695.510009765625</v>
       </c>
       <c r="H21">
-        <v>711.440002441406</v>
+        <v>696.059997558594</v>
       </c>
       <c r="I21">
-        <v>715.620361328125</v>
+        <v>703.789184570313</v>
       </c>
       <c r="J21">
-        <v>704.994506835938</v>
+        <v>693.406494140625</v>
       </c>
       <c r="K21">
-        <v>35603100</v>
+        <v>29687500</v>
       </c>
       <c r="L21">
-        <v>-1.43523001670837</v>
+        <v>-0.905709385871887</v>
       </c>
       <c r="M21">
-        <v>55.0994873046875</v>
+        <v>66.5572204589844</v>
       </c>
       <c r="N21">
-        <v>-16.1432189941406</v>
+        <v>22.5973968505859</v>
       </c>
       <c r="O21" t="s">
         <v>23</v>
       </c>
       <c r="P21">
-        <v>-15.6323156356812</v>
+        <v>-6.00122213363647</v>
       </c>
       <c r="Q21">
-        <v>712.987182617188</v>
+        <v>700.701416015625</v>
       </c>
       <c r="R21">
-        <v>717.214111328125</v>
+        <v>708.291809082031</v>
       </c>
       <c r="S21">
-        <v>719.531494140625</v>
+        <v>713.96923828125</v>
       </c>
       <c r="T21">
-        <v>3.3604736328125</v>
+        <v>-2.01080322265625</v>
       </c>
       <c r="U21">
-        <v>4.08453369140625</v>
+        <v>-2.103515625</v>
       </c>
       <c r="V21">
-        <v>10.6258544921875</v>
+        <v>10.3826904296875</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="2">
-        <v>46210</v>
+        <v>46220</v>
       </c>
       <c r="B22">
-        <v>-7.9444580078125</v>
+        <v>-9.927001953125</v>
       </c>
       <c r="C22">
-        <v>-0.99530029296875</v>
+        <v>-7.9847412109375</v>
       </c>
       <c r="D22">
-        <v>-5.45904541015625</v>
+        <v>-7.42694091796875</v>
       </c>
       <c r="E22">
-        <v>714.169982910156</v>
+        <v>691.650024414063</v>
       </c>
       <c r="F22">
-        <v>716.349975585938</v>
+        <v>702.299987792969</v>
       </c>
       <c r="G22">
-        <v>704.900024414063</v>
+        <v>686.760009765625</v>
       </c>
       <c r="H22">
-        <v>709.429992675781</v>
+        <v>695.330017089844</v>
       </c>
       <c r="I22">
-        <v>714.261169433594</v>
+        <v>701.341003417969</v>
       </c>
       <c r="J22">
-        <v>704.237060546875</v>
+        <v>688.661193847656</v>
       </c>
       <c r="K22">
-        <v>42483000</v>
+        <v>54109200</v>
       </c>
       <c r="L22">
-        <v>-2.93475341796875</v>
+        <v>-1.21904349327087</v>
       </c>
       <c r="M22">
-        <v>65.706657409668</v>
+        <v>54.2892608642578</v>
       </c>
       <c r="N22">
-        <v>-6.48241281509399</v>
+        <v>8.37738990783691</v>
       </c>
       <c r="O22" t="s">
         <v>23</v>
       </c>
       <c r="P22">
-        <v>-38.1205101013184</v>
+        <v>-64.7480239868164</v>
       </c>
       <c r="Q22">
-        <v>715.312561035156</v>
+        <v>703.639892578125</v>
       </c>
       <c r="R22">
-        <v>718.993896484375</v>
+        <v>711.3662109375</v>
       </c>
       <c r="S22">
-        <v>720.435485839844</v>
+        <v>715.791137695313</v>
       </c>
       <c r="T22">
-        <v>-2.08880615234375</v>
+        <v>-0.958984375</v>
       </c>
       <c r="U22">
-        <v>-0.6629638671875</v>
+        <v>1.90118408203125</v>
       </c>
       <c r="V22">
-        <v>10.0241088867188</v>
+        <v>12.6798095703125</v>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="2">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="B23">
-        <v>-2.8165283203125</v>
+        <v>-5.863037109375</v>
       </c>
       <c r="C23">
-        <v>0.947509765625</v>
+        <v>-2.36517333984375</v>
       </c>
       <c r="D23">
-        <v>-2.495361328125</v>
+        <v>-3.09661865234375</v>
       </c>
       <c r="E23">
-        <v>719.929992675781</v>
+        <v>712.010009765625</v>
       </c>
       <c r="F23">
-        <v>726.080017089844</v>
+        <v>713.598999023438</v>
       </c>
       <c r="G23">
-        <v>718.450012207031</v>
+        <v>702.609985351563</v>
       </c>
       <c r="H23">
-        <v>722.820007324219</v>
+        <v>705.940002441406</v>
       </c>
       <c r="I23">
-        <v>729.223693847656</v>
+        <v>712.521850585938</v>
       </c>
       <c r="J23">
-        <v>718.437683105469</v>
+        <v>701.248962402344</v>
       </c>
       <c r="K23">
-        <v>30220400</v>
+        <v>39402000</v>
       </c>
       <c r="L23">
-        <v>-2.4647536277771</v>
+        <v>-1.98428201675415</v>
       </c>
       <c r="M23">
-        <v>70.2612838745117</v>
+        <v>50.0927925109863</v>
       </c>
       <c r="N23">
-        <v>3.65661525726318</v>
+        <v>7.75767660140991</v>
       </c>
       <c r="O23" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P23">
-        <v>18.3796253204346</v>
+        <v>-43.6580963134766</v>
       </c>
       <c r="Q23">
-        <v>721.317932128906</v>
+        <v>712.182556152344</v>
       </c>
       <c r="R23">
-        <v>721.685180664063</v>
+        <v>715.892822265625</v>
       </c>
       <c r="S23">
-        <v>721.850463867188</v>
+        <v>718.15576171875</v>
       </c>
       <c r="T23">
-        <v>3.1436767578125</v>
+        <v>-1.0771484375</v>
       </c>
       <c r="U23">
-        <v>-0.0123291015625</v>
+        <v>-1.36102294921875</v>
       </c>
       <c r="V23">
-        <v>10.7860107421875</v>
+        <v>11.2728881835938</v>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="2">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="B24">
-        <v>-3.747802734375</v>
+        <v>-1.943359375</v>
       </c>
       <c r="C24">
-        <v>-2.68170166015625</v>
+        <v>0.40814208984375</v>
       </c>
       <c r="D24">
-        <v>-3.40606689453125</v>
+        <v>-0.0054931640625</v>
       </c>
       <c r="E24">
-        <v>725.580017089844</v>
+        <v>723.849975585938</v>
       </c>
       <c r="F24">
-        <v>730.830017089844</v>
+        <v>724.359985351563</v>
       </c>
       <c r="G24">
-        <v>707.559997558594</v>
+        <v>710.22998046875</v>
       </c>
       <c r="H24">
-        <v>712.599975585938</v>
+        <v>717.739990234375</v>
       </c>
       <c r="I24">
-        <v>718.628479003906</v>
+        <v>721.251037597656</v>
       </c>
       <c r="J24">
-        <v>705.427856445313</v>
+        <v>712.604736328125</v>
       </c>
       <c r="K24">
-        <v>51086000</v>
+        <v>32627500</v>
       </c>
       <c r="L24">
-        <v>-2.74999117851257</v>
+        <v>-1.41428053379059</v>
       </c>
       <c r="M24">
-        <v>67.7827301025391</v>
+        <v>46.4865188598633</v>
       </c>
       <c r="N24">
-        <v>14.6252498626709</v>
+        <v>-4.76508235931396</v>
       </c>
       <c r="O24" t="s">
         <v>23</v>
       </c>
       <c r="P24">
-        <v>-52.3691177368164</v>
+        <v>-2.18429470062256</v>
       </c>
       <c r="Q24">
-        <v>719.125122070313</v>
+        <v>717.8037109375</v>
       </c>
       <c r="R24">
-        <v>720.899353027344</v>
+        <v>718.531005859375</v>
       </c>
       <c r="S24">
-        <v>721.46142578125</v>
+        <v>719.552307128906</v>
       </c>
       <c r="T24">
-        <v>-12.2015380859375</v>
+        <v>-3.10894775390625</v>
       </c>
       <c r="U24">
-        <v>-2.13214111328125</v>
+        <v>2.374755859375</v>
       </c>
       <c r="V24">
-        <v>13.2006225585938</v>
+        <v>8.64630126953125</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="2">
-        <v>46204</v>
+        <v>46217</v>
       </c>
       <c r="B25">
-        <v>5.48199462890625</v>
+        <v>0.21160888671875</v>
       </c>
       <c r="C25">
-        <v>1.29547119140625</v>
+        <v>-1.59527587890625</v>
       </c>
       <c r="D25">
-        <v>1.181640625</v>
+        <v>0.46612548828125</v>
       </c>
       <c r="E25">
-        <v>729.190002441406</v>
+        <v>720.219970703125</v>
       </c>
       <c r="F25">
-        <v>731.919982910156</v>
+        <v>722.289978027344</v>
       </c>
       <c r="G25">
-        <v>724.599975585938</v>
+        <v>714.340026855469</v>
       </c>
       <c r="H25">
-        <v>725.169982910156</v>
+        <v>719.690002441406</v>
       </c>
       <c r="I25">
-        <v>731.202941894531</v>
+        <v>723.544555664063</v>
       </c>
       <c r="J25">
-        <v>721.92822265625</v>
+        <v>716.334533691406</v>
       </c>
       <c r="K25">
-        <v>40803700</v>
+        <v>29448100</v>
       </c>
       <c r="L25">
-        <v>-1.9528489112854</v>
+        <v>-0.94570779800415</v>
       </c>
       <c r="M25">
-        <v>59.134204864502</v>
+        <v>48.8124732971191</v>
       </c>
       <c r="N25">
-        <v>25.8970050811768</v>
+        <v>-5.16571569442749</v>
       </c>
       <c r="O25" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>-6.59338569641113</v>
+        <v>5.93372297286987</v>
       </c>
       <c r="Q25">
-        <v>726.038452148438</v>
+        <v>718.3955078125</v>
       </c>
       <c r="R25">
-        <v>723.370727539063</v>
+        <v>718.438903808594</v>
       </c>
       <c r="S25">
-        <v>722.493774414063</v>
+        <v>719.708923339844</v>
       </c>
       <c r="T25">
-        <v>-0.717041015625</v>
+        <v>1.25457763671875</v>
       </c>
       <c r="U25">
-        <v>-2.6717529296875</v>
+        <v>1.9945068359375</v>
       </c>
       <c r="V25">
-        <v>9.27471923828125</v>
+        <v>7.21002197265625</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="2">
-        <v>46203</v>
+        <v>46216</v>
       </c>
       <c r="B26">
-        <v>10.5760498046875</v>
+        <v>-0.3555908203125</v>
       </c>
       <c r="C26">
-        <v>1.1090087890625</v>
+        <v>-3.0672607421875</v>
       </c>
       <c r="D26">
-        <v>2.15655517578125</v>
+        <v>-1.38330078125</v>
       </c>
       <c r="E26">
-        <v>724.179992675781</v>
+        <v>717.719970703125</v>
       </c>
       <c r="F26">
-        <v>737.619995117188</v>
+        <v>718.739990234375</v>
       </c>
       <c r="G26">
-        <v>723.909973144531</v>
+        <v>710.080017089844</v>
       </c>
       <c r="H26">
-        <v>736.400024414063</v>
+        <v>711.739990234375</v>
       </c>
       <c r="I26">
-        <v>740.130432128906</v>
+        <v>717.577209472656</v>
       </c>
       <c r="J26">
-        <v>729.166198730469</v>
+        <v>707.793212890625</v>
       </c>
       <c r="K26">
-        <v>42121800</v>
+        <v>36552300</v>
       </c>
       <c r="L26">
-        <v>-1.489990234375</v>
+        <v>-0.0714227557182312</v>
       </c>
       <c r="M26">
-        <v>46.9703025817871</v>
+        <v>51.4713363647461</v>
       </c>
       <c r="N26">
-        <v>-18.5084857940674</v>
+        <v>4.72496747970581</v>
       </c>
       <c r="O26" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P26">
-        <v>57.9281425476074</v>
+        <v>-42.1362648010254</v>
       </c>
       <c r="Q26">
-        <v>725.990234375</v>
+        <v>716.920593261719</v>
       </c>
       <c r="R26">
-        <v>723.10791015625</v>
+        <v>718.116577148438</v>
       </c>
       <c r="S26">
-        <v>722.2724609375</v>
+        <v>719.618469238281</v>
       </c>
       <c r="T26">
-        <v>2.51043701171875</v>
+        <v>-1.16278076171875</v>
       </c>
       <c r="U26">
-        <v>5.2562255859375</v>
+        <v>-2.28680419921875</v>
       </c>
       <c r="V26">
-        <v>10.9642333984375</v>
+        <v>9.78399658203125</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="2">
-        <v>46202</v>
+        <v>46213</v>
       </c>
       <c r="B27">
-        <v>3.40582275390625</v>
+        <v>4.54119873046875</v>
       </c>
       <c r="C27">
-        <v>-7.25604248046875</v>
+        <v>1.09893798828125</v>
       </c>
       <c r="D27">
-        <v>-1.9508056640625</v>
+        <v>-0.62530517578125</v>
       </c>
       <c r="E27">
-        <v>713.989990234375</v>
+        <v>720.700012207031</v>
       </c>
       <c r="F27">
-        <v>724.580017089844</v>
+        <v>726.390014648438</v>
       </c>
       <c r="G27">
-        <v>705.171997070313</v>
+        <v>717</v>
       </c>
       <c r="H27">
-        <v>724.080017089844</v>
+        <v>725.510009765625</v>
       </c>
       <c r="I27">
-        <v>725.809997558594</v>
+        <v>728.048034667969</v>
       </c>
       <c r="J27">
-        <v>714.771484375</v>
+        <v>721.283996582031</v>
       </c>
       <c r="K27">
-        <v>44939000</v>
+        <v>26415900</v>
       </c>
       <c r="L27">
-        <v>-2.04951691627502</v>
+        <v>-0.166184201836586</v>
       </c>
       <c r="M27">
-        <v>57.6382751464844</v>
+        <v>49.1490592956543</v>
       </c>
       <c r="N27">
-        <v>-16.8400115966797</v>
+        <v>-9.55446624755859</v>
       </c>
       <c r="O27" t="s">
         <v>1</v>
       </c>
       <c r="P27">
-        <v>20.9863204956055</v>
+        <v>29.1831836700439</v>
       </c>
       <c r="Q27">
-        <v>716.725952148438</v>
+        <v>721.479248046875</v>
       </c>
       <c r="R27">
-        <v>719.314147949219</v>
+        <v>719.98193359375</v>
       </c>
       <c r="S27">
-        <v>720.439880371094</v>
+        <v>720.620422363281</v>
       </c>
       <c r="T27">
-        <v>1.22998046875</v>
+        <v>1.65802001953125</v>
       </c>
       <c r="U27">
-        <v>9.5994873046875</v>
+        <v>4.28399658203125</v>
       </c>
       <c r="V27">
-        <v>11.0385131835938</v>
+        <v>6.7640380859375</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="2">
-        <v>46199</v>
+        <v>46212</v>
       </c>
       <c r="B28">
-        <v>-7.16119384765625</v>
+        <v>3.296630859375</v>
       </c>
       <c r="C28">
-        <v>-10.2252807617188</v>
+        <v>-0.72021484375</v>
       </c>
       <c r="D28">
-        <v>-2.2767333984375</v>
+        <v>-2.30474853515625</v>
       </c>
       <c r="E28">
-        <v>707.130004882813</v>
+        <v>718.330017089844</v>
       </c>
       <c r="F28">
-        <v>715.554992675781</v>
+        <v>724.22998046875</v>
       </c>
       <c r="G28">
-        <v>702.809997558594</v>
+        <v>715.125</v>
       </c>
       <c r="H28">
-        <v>706.52001953125</v>
+        <v>723.280029296875</v>
       </c>
       <c r="I28">
-        <v>714.332336425781</v>
+        <v>726.686767578125</v>
       </c>
       <c r="J28">
-        <v>700.900329589844</v>
+        <v>719.118225097656</v>
       </c>
       <c r="K28">
-        <v>47081800</v>
+        <v>33654700</v>
       </c>
       <c r="L28">
-        <v>-2.25047087669373</v>
+        <v>-1.11665856838226</v>
       </c>
       <c r="M28">
-        <v>69.3101043701172</v>
+        <v>54.3410568237305</v>
       </c>
       <c r="N28">
-        <v>-0.319649010896683</v>
+        <v>-1.37647461891174</v>
       </c>
       <c r="O28" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P28">
-        <v>-17.0330448150635</v>
+        <v>56.2780990600586</v>
       </c>
       <c r="Q28">
-        <v>711.891967773438</v>
+        <v>718.006164550781</v>
       </c>
       <c r="R28">
-        <v>718.471069335938</v>
+        <v>718.503051757813</v>
       </c>
       <c r="S28">
-        <v>720.244934082031</v>
+        <v>720.065307617188</v>
       </c>
       <c r="T28">
-        <v>-1.22265625</v>
+        <v>2.456787109375</v>
       </c>
       <c r="U28">
-        <v>-1.90966796875</v>
+        <v>3.99322509765625</v>
       </c>
       <c r="V28">
-        <v>13.4320068359375</v>
+        <v>7.56854248046875</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="2">
-        <v>46198</v>
+        <v>46211</v>
       </c>
       <c r="B29">
-        <v>-8.75091552734375</v>
+        <v>-4.7235107421875</v>
       </c>
       <c r="C29">
-        <v>-6.632568359375</v>
+        <v>-3.04364013671875</v>
       </c>
       <c r="D29">
-        <v>-0.59619140625</v>
+        <v>-5.07476806640625</v>
       </c>
       <c r="E29">
-        <v>725.900024414063</v>
+        <v>704.950012207031</v>
       </c>
       <c r="F29">
-        <v>726.830017089844</v>
+        <v>712.259887695313</v>
       </c>
       <c r="G29">
-        <v>705.299987792969</v>
+        <v>700.909973144531</v>
       </c>
       <c r="H29">
-        <v>716.380004882813</v>
+        <v>711.440002441406</v>
       </c>
       <c r="I29">
-        <v>721.428955078125</v>
+        <v>715.620361328125</v>
       </c>
       <c r="J29">
-        <v>708.903259277344</v>
+        <v>704.994506835938</v>
       </c>
       <c r="K29">
-        <v>50144000</v>
+        <v>35603100</v>
       </c>
       <c r="L29">
-        <v>-2.38856720924377</v>
+        <v>-1.43523001670837</v>
       </c>
       <c r="M29">
-        <v>69.5323638916016</v>
+        <v>55.0994873046875</v>
       </c>
       <c r="N29">
-        <v>-7.88510894775391</v>
+        <v>-16.1432189941406</v>
       </c>
       <c r="O29" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P29">
-        <v>7.70187902450562</v>
+        <v>-15.6323156356812</v>
       </c>
       <c r="Q29">
-        <v>716.514770507813</v>
+        <v>712.987182617188</v>
       </c>
       <c r="R29">
-        <v>721.650451660156</v>
+        <v>717.214111328125</v>
       </c>
       <c r="S29">
-        <v>721.85107421875</v>
+        <v>719.531494140625</v>
       </c>
       <c r="T29">
-        <v>-5.40106201171875</v>
+        <v>3.3604736328125</v>
       </c>
       <c r="U29">
-        <v>3.603271484375</v>
+        <v>4.08453369140625</v>
       </c>
       <c r="V29">
-        <v>12.5256958007813</v>
+        <v>10.6258544921875</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="2">
-        <v>46197</v>
+        <v>46210</v>
       </c>
       <c r="B30">
-        <v>-10.9425048828125</v>
+        <v>-7.9444580078125</v>
       </c>
       <c r="C30">
-        <v>-3.42388916015625</v>
+        <v>-0.99530029296875</v>
       </c>
       <c r="D30">
-        <v>-0.86822509765625</v>
+        <v>-5.45904541015625</v>
       </c>
       <c r="E30">
-        <v>715.369995117188</v>
+        <v>714.169982910156</v>
       </c>
       <c r="F30">
-        <v>719.929992675781</v>
+        <v>716.349975585938</v>
       </c>
       <c r="G30">
-        <v>704.450012207031</v>
+        <v>704.900024414063</v>
       </c>
       <c r="H30">
-        <v>710.619995117188</v>
+        <v>709.429992675781</v>
       </c>
       <c r="I30">
-        <v>716.792297363281</v>
+        <v>714.261169433594</v>
       </c>
       <c r="J30">
-        <v>704.093078613281</v>
+        <v>704.237060546875</v>
       </c>
       <c r="K30">
-        <v>52480400</v>
+        <v>42483000</v>
       </c>
       <c r="L30">
-        <v>-1.72951829433441</v>
+        <v>-2.93475341796875</v>
       </c>
       <c r="M30">
-        <v>75.4843902587891</v>
+        <v>65.706657409668</v>
       </c>
       <c r="N30">
-        <v>5.82126092910767</v>
+        <v>-6.48241281509399</v>
       </c>
       <c r="O30" t="s">
         <v>23</v>
       </c>
       <c r="P30">
-        <v>-41.3770904541016</v>
+        <v>-38.1205101013184</v>
       </c>
       <c r="Q30">
-        <v>717.46728515625</v>
+        <v>715.312561035156</v>
       </c>
       <c r="R30">
-        <v>722.873840332031</v>
+        <v>718.993896484375</v>
       </c>
       <c r="S30">
-        <v>722.430297851563</v>
+        <v>720.435485839844</v>
       </c>
       <c r="T30">
-        <v>-3.1376953125</v>
+        <v>-2.08880615234375</v>
       </c>
       <c r="U30">
-        <v>-0.35693359375</v>
+        <v>-0.6629638671875</v>
       </c>
       <c r="V30">
-        <v>12.69921875</v>
+        <v>10.0241088867188</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="2">
-        <v>46196</v>
+        <v>46209</v>
       </c>
       <c r="B31">
-        <v>-7.54193115234375</v>
+        <v>-2.8165283203125</v>
       </c>
       <c r="C31">
-        <v>2.93658447265625</v>
+        <v>0.947509765625</v>
       </c>
       <c r="D31">
-        <v>1.19757080078125</v>
+        <v>-2.495361328125</v>
       </c>
       <c r="E31">
-        <v>715.739990234375</v>
+        <v>719.929992675781</v>
       </c>
       <c r="F31">
-        <v>723.609985351563</v>
+        <v>726.080017089844</v>
       </c>
       <c r="G31">
-        <v>712.110107421875</v>
+        <v>718.450012207031</v>
       </c>
       <c r="H31">
-        <v>713.650024414063</v>
+        <v>722.820007324219</v>
       </c>
       <c r="I31">
-        <v>720.155700683594</v>
+        <v>729.223693847656</v>
       </c>
       <c r="J31">
-        <v>707.419250488281</v>
+        <v>718.437683105469</v>
       </c>
       <c r="K31">
-        <v>53354100</v>
+        <v>30220400</v>
       </c>
       <c r="L31">
-        <v>-1.52856731414795</v>
+        <v>-2.4647536277771</v>
       </c>
       <c r="M31">
-        <v>71.3319702148438</v>
+        <v>70.2612838745117</v>
       </c>
       <c r="N31">
-        <v>-2.70278596878052</v>
+        <v>3.65661525726318</v>
       </c>
       <c r="O31" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P31">
-        <v>-68.6438598632813</v>
+        <v>18.3796253204346</v>
       </c>
       <c r="Q31">
-        <v>724.445922851563</v>
+        <v>721.317932128906</v>
       </c>
       <c r="R31">
-        <v>726.346984863281</v>
+        <v>721.685180664063</v>
       </c>
       <c r="S31">
-        <v>723.753662109375</v>
+        <v>721.850463867188</v>
       </c>
       <c r="T31">
-        <v>-3.45428466796875</v>
+        <v>3.1436767578125</v>
       </c>
       <c r="U31">
-        <v>-4.69085693359375</v>
+        <v>-0.0123291015625</v>
       </c>
       <c r="V31">
-        <v>12.7364501953125</v>
+        <v>10.7860107421875</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="2">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B32">
-        <v>1.6483154296875</v>
+        <v>-3.747802734375</v>
       </c>
       <c r="C32">
-        <v>11.2158203125</v>
+        <v>-2.68170166015625</v>
       </c>
       <c r="D32">
-        <v>5.11346435546875</v>
+        <v>-3.40606689453125</v>
       </c>
       <c r="E32">
-        <v>742.02001953125</v>
+        <v>725.580017089844</v>
       </c>
       <c r="F32">
-        <v>745.450012207031</v>
+        <v>730.830017089844</v>
       </c>
       <c r="G32">
-        <v>734.390014648438</v>
+        <v>707.559997558594</v>
       </c>
       <c r="H32">
-        <v>737.950012207031</v>
+        <v>712.599975585938</v>
       </c>
       <c r="I32">
-        <v>741.215698242188</v>
+        <v>718.628479003906</v>
       </c>
       <c r="J32">
-        <v>733.294921875</v>
+        <v>705.427856445313</v>
       </c>
       <c r="K32">
-        <v>43518500</v>
+        <v>51086000</v>
       </c>
       <c r="L32">
-        <v>-1.16618704795837</v>
+        <v>-2.74999117851257</v>
       </c>
       <c r="M32">
-        <v>73.3134765625</v>
+        <v>67.7827301025391</v>
       </c>
       <c r="N32">
-        <v>5.07466554641724</v>
+        <v>14.6252498626709</v>
       </c>
       <c r="O32" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P32">
-        <v>19.3256072998047</v>
+        <v>-52.3691177368164</v>
       </c>
       <c r="Q32">
-        <v>735.138427734375</v>
+        <v>719.125122070313</v>
       </c>
       <c r="R32">
-        <v>730.110168457031</v>
+        <v>720.899353027344</v>
       </c>
       <c r="S32">
-        <v>725.110412597656</v>
+        <v>721.46142578125</v>
       </c>
       <c r="T32">
-        <v>-4.23431396484375</v>
+        <v>-12.2015380859375</v>
       </c>
       <c r="U32">
-        <v>-1.0950927734375</v>
+        <v>-2.13214111328125</v>
       </c>
       <c r="V32">
-        <v>7.9207763671875</v>
+        <v>13.2006225585938</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="2">
-        <v>46191</v>
+        <v>46204</v>
       </c>
       <c r="B33">
-        <v>3.2733154296875</v>
+        <v>5.48199462890625</v>
       </c>
       <c r="C33">
-        <v>11.8580932617188</v>
+        <v>1.29547119140625</v>
       </c>
       <c r="D33">
-        <v>2.6954345703125</v>
+        <v>1.181640625</v>
       </c>
       <c r="E33">
-        <v>737.200012207031</v>
+        <v>729.190002441406</v>
       </c>
       <c r="F33">
-        <v>741.820007324219</v>
+        <v>731.919982910156</v>
       </c>
       <c r="G33">
-        <v>732.510009765625</v>
+        <v>724.599975585938</v>
       </c>
       <c r="H33">
-        <v>740.619995117188</v>
+        <v>725.169982910156</v>
       </c>
       <c r="I33">
-        <v>743.136840820313</v>
+        <v>731.202941894531</v>
       </c>
       <c r="J33">
-        <v>735.426635742188</v>
+        <v>721.92822265625</v>
       </c>
       <c r="K33">
-        <v>50154500</v>
+        <v>40803700</v>
       </c>
       <c r="L33">
-        <v>-0.598089337348938</v>
+        <v>-1.9528489112854</v>
       </c>
       <c r="M33">
-        <v>69.7727432250977</v>
+        <v>59.134204864502</v>
       </c>
       <c r="N33">
-        <v>0.589374721050262</v>
+        <v>25.8970050811768</v>
       </c>
       <c r="O33" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P33">
-        <v>37.9242057800293</v>
+        <v>-6.59338569641113</v>
       </c>
       <c r="Q33">
-        <v>732.823364257813</v>
+        <v>726.038452148438</v>
       </c>
       <c r="R33">
-        <v>727.787353515625</v>
+        <v>723.370727539063</v>
       </c>
       <c r="S33">
-        <v>723.4755859375</v>
+        <v>722.493774414063</v>
       </c>
       <c r="T33">
-        <v>1.31683349609375</v>
+        <v>-0.717041015625</v>
       </c>
       <c r="U33">
-        <v>2.9166259765625</v>
+        <v>-2.6717529296875</v>
       </c>
       <c r="V33">
-        <v>7.710205078125</v>
+        <v>9.27471923828125</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="2">
-        <v>46190</v>
+        <v>46203</v>
       </c>
       <c r="B34">
-        <v>-1.5975341796875</v>
+        <v>10.5760498046875</v>
       </c>
       <c r="C34">
-        <v>5.6368408203125</v>
+        <v>1.1090087890625</v>
       </c>
       <c r="D34">
-        <v>-1.7880859375</v>
+        <v>2.15655517578125</v>
       </c>
       <c r="E34">
-        <v>735.190002441406</v>
+        <v>724.179992675781</v>
       </c>
       <c r="F34">
-        <v>735.679992675781</v>
+        <v>737.619995117188</v>
       </c>
       <c r="G34">
-        <v>720.849975585938</v>
+        <v>723.909973144531</v>
       </c>
       <c r="H34">
-        <v>722.510009765625</v>
+        <v>736.400024414063</v>
       </c>
       <c r="I34">
-        <v>728.564636230469</v>
+        <v>740.130432128906</v>
       </c>
       <c r="J34">
-        <v>716.205810546875</v>
+        <v>729.166198730469</v>
       </c>
       <c r="K34">
-        <v>51669300</v>
+        <v>42121800</v>
       </c>
       <c r="L34">
-        <v>-0.679039359092712</v>
+        <v>-1.489990234375</v>
       </c>
       <c r="M34">
-        <v>69.3639297485352</v>
+        <v>46.9703025817871</v>
       </c>
       <c r="N34">
-        <v>10.1039295196533</v>
+        <v>-18.5084857940674</v>
       </c>
       <c r="O34" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P34">
-        <v>-31.3353672027588</v>
+        <v>57.9281425476074</v>
       </c>
       <c r="Q34">
-        <v>725.923095703125</v>
+        <v>725.990234375</v>
       </c>
       <c r="R34">
-        <v>724.027099609375</v>
+        <v>723.10791015625</v>
       </c>
       <c r="S34">
-        <v>721.264404296875</v>
+        <v>722.2724609375</v>
       </c>
       <c r="T34">
-        <v>-7.1153564453125</v>
+        <v>2.51043701171875</v>
       </c>
       <c r="U34">
-        <v>-4.6441650390625</v>
+        <v>5.2562255859375</v>
       </c>
       <c r="V34">
-        <v>12.3588256835938</v>
+        <v>10.9642333984375</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
       <c r="A35" s="2">
-        <v>46189</v>
+        <v>46202</v>
       </c>
       <c r="B35">
-        <v>10.0441284179688</v>
+        <v>3.40582275390625</v>
       </c>
       <c r="C35">
-        <v>5.4068603515625</v>
+        <v>-7.25604248046875</v>
       </c>
       <c r="D35">
-        <v>-1.7308349609375</v>
+        <v>-1.9508056640625</v>
       </c>
       <c r="E35">
-        <v>742.25</v>
+        <v>713.989990234375</v>
       </c>
       <c r="F35">
-        <v>744.219970703125</v>
+        <v>724.580017089844</v>
       </c>
       <c r="G35">
-        <v>729.640014648438</v>
+        <v>705.171997070313</v>
       </c>
       <c r="H35">
-        <v>729.859985351563</v>
+        <v>724.080017089844</v>
       </c>
       <c r="I35">
-        <v>734.100280761719</v>
+        <v>725.809997558594</v>
       </c>
       <c r="J35">
-        <v>724.563842773438</v>
+        <v>714.771484375</v>
       </c>
       <c r="K35">
-        <v>45348600</v>
+        <v>44939000</v>
       </c>
       <c r="L35">
-        <v>-0.344752728939056</v>
+        <v>-2.04951691627502</v>
       </c>
       <c r="M35">
-        <v>62.9985961914063</v>
+        <v>57.6382751464844</v>
       </c>
       <c r="N35">
-        <v>18.2906303405762</v>
+        <v>-16.8400115966797</v>
       </c>
       <c r="O35" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P35">
-        <v>-8.74789142608643</v>
+        <v>20.9863204956055</v>
       </c>
       <c r="Q35">
-        <v>729.420532226563</v>
+        <v>716.725952148438</v>
       </c>
       <c r="R35">
-        <v>724.500549316406</v>
+        <v>719.314147949219</v>
       </c>
       <c r="S35">
-        <v>720.938659667969</v>
+        <v>720.439880371094</v>
       </c>
       <c r="T35">
-        <v>-10.1196899414063</v>
+        <v>1.22998046875</v>
       </c>
       <c r="U35">
-        <v>-5.076171875</v>
+        <v>9.5994873046875</v>
       </c>
       <c r="V35">
-        <v>9.53643798828125</v>
+        <v>11.0385131835938</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="2">
-        <v>46188</v>
+        <v>46199</v>
       </c>
       <c r="B36">
-        <v>17.9420166015625</v>
+        <v>-7.16119384765625</v>
       </c>
       <c r="C36">
-        <v>2.38287353515625</v>
+        <v>-10.2252807617188</v>
       </c>
       <c r="D36">
-        <v>-3.092041015625</v>
+        <v>-2.2767333984375</v>
       </c>
       <c r="E36">
-        <v>738.099975585938</v>
+        <v>707.130004882813</v>
       </c>
       <c r="F36">
-        <v>744.759887695313</v>
+        <v>715.554992675781</v>
       </c>
       <c r="G36">
-        <v>737.380004882813</v>
+        <v>702.809997558594</v>
       </c>
       <c r="H36">
-        <v>744</v>
+        <v>706.52001953125</v>
       </c>
       <c r="I36">
-        <v>746.012329101563</v>
+        <v>714.332336425781</v>
       </c>
       <c r="J36">
-        <v>740.643737792969</v>
+        <v>700.900329589844</v>
       </c>
       <c r="K36">
-        <v>46710200</v>
+        <v>47081800</v>
       </c>
       <c r="L36">
-        <v>0.187627881765366</v>
+        <v>-2.25047087669373</v>
       </c>
       <c r="M36">
-        <v>53.2574691772461</v>
+        <v>69.3101043701172</v>
       </c>
       <c r="N36">
-        <v>-9.68106651306152</v>
+        <v>-0.319649010896683</v>
       </c>
       <c r="O36" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P36">
-        <v>69.9155349731445</v>
+        <v>-17.0330448150635</v>
       </c>
       <c r="Q36">
-        <v>729.329650878906</v>
+        <v>711.891967773438</v>
       </c>
       <c r="R36">
-        <v>723.061889648438</v>
+        <v>718.471069335938</v>
       </c>
       <c r="S36">
-        <v>719.975463867188</v>
+        <v>720.244934082031</v>
       </c>
       <c r="T36">
-        <v>1.25244140625</v>
+        <v>-1.22265625</v>
       </c>
       <c r="U36">
-        <v>3.26373291015625</v>
+        <v>-1.90966796875</v>
       </c>
       <c r="V36">
-        <v>5.36859130859375</v>
+        <v>13.4320068359375</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
       <c r="A37" s="2">
-        <v>46185</v>
+        <v>46198</v>
       </c>
       <c r="B37">
-        <v>5.90203857421875</v>
+        <v>-8.75091552734375</v>
       </c>
       <c r="C37">
-        <v>-8.1749267578125</v>
+        <v>-6.632568359375</v>
       </c>
       <c r="D37">
-        <v>-8.9888916015625</v>
+        <v>-0.59619140625</v>
       </c>
       <c r="E37">
-        <v>717.609985351563</v>
+        <v>725.900024414063</v>
       </c>
       <c r="F37">
-        <v>724.010009765625</v>
+        <v>726.830017089844</v>
       </c>
       <c r="G37">
-        <v>711.280029296875</v>
+        <v>705.299987792969</v>
       </c>
       <c r="H37">
-        <v>721.340026855469</v>
+        <v>716.380004882813</v>
       </c>
       <c r="I37">
-        <v>727.374450683594</v>
+        <v>721.428955078125</v>
       </c>
       <c r="J37">
-        <v>713.639892578125</v>
+        <v>708.903259277344</v>
       </c>
       <c r="K37">
-        <v>51236000</v>
+        <v>50144000</v>
       </c>
       <c r="L37">
-        <v>0.152864009141922</v>
+        <v>-2.38856720924377</v>
       </c>
       <c r="M37">
-        <v>58.966007232666</v>
+        <v>69.5323638916016</v>
       </c>
       <c r="N37">
-        <v>0.648391544818878</v>
+        <v>-7.88510894775391</v>
       </c>
       <c r="O37" t="s">
         <v>1</v>
       </c>
       <c r="P37">
-        <v>46.5396575927734</v>
+        <v>7.70187902450562</v>
       </c>
       <c r="Q37">
-        <v>715.103759765625</v>
+        <v>716.514770507813</v>
       </c>
       <c r="R37">
-        <v>717.614929199219</v>
+        <v>721.650451660156</v>
       </c>
       <c r="S37">
-        <v>717.106567382813</v>
+        <v>721.85107421875</v>
       </c>
       <c r="T37">
-        <v>3.36444091796875</v>
+        <v>-5.40106201171875</v>
       </c>
       <c r="U37">
-        <v>2.35986328125</v>
+        <v>3.603271484375</v>
       </c>
       <c r="V37">
-        <v>13.7345581054688</v>
+        <v>12.5256958007813</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="2">
-        <v>46184</v>
+        <v>46197</v>
       </c>
       <c r="B38">
-        <v>1.81298828125</v>
+        <v>-10.9425048828125</v>
       </c>
       <c r="C38">
-        <v>-14.1453247070313</v>
+        <v>-3.42388916015625</v>
       </c>
       <c r="D38">
-        <v>-10.99951171875</v>
+        <v>-0.86822509765625</v>
       </c>
       <c r="E38">
-        <v>699.289978027344</v>
+        <v>715.369995117188</v>
       </c>
       <c r="F38">
-        <v>718.372009277344</v>
+        <v>719.929992675781</v>
       </c>
       <c r="G38">
-        <v>695</v>
+        <v>704.450012207031</v>
       </c>
       <c r="H38">
-        <v>717.119995117188</v>
+        <v>710.619995117188</v>
       </c>
       <c r="I38">
-        <v>719.705078125</v>
+        <v>716.792297363281</v>
       </c>
       <c r="J38">
-        <v>706.693298339844</v>
+        <v>704.093078613281</v>
       </c>
       <c r="K38">
-        <v>71798800</v>
+        <v>52480400</v>
       </c>
       <c r="L38">
-        <v>0.201433449983597</v>
+        <v>-1.72951829433441</v>
       </c>
       <c r="M38">
-        <v>58.5861396789551</v>
+        <v>75.4843902587891</v>
       </c>
       <c r="N38">
-        <v>-17.4295921325684</v>
+        <v>5.82126092910767</v>
       </c>
       <c r="O38" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P38">
-        <v>35.6000556945801</v>
+        <v>-41.3770904541016</v>
       </c>
       <c r="Q38">
-        <v>709.418640136719</v>
+        <v>717.46728515625</v>
       </c>
       <c r="R38">
-        <v>716.472106933594</v>
+        <v>722.873840332031</v>
       </c>
       <c r="S38">
-        <v>716.43017578125</v>
+        <v>722.430297851563</v>
       </c>
       <c r="T38">
-        <v>1.33306884765625</v>
+        <v>-3.1376953125</v>
       </c>
       <c r="U38">
-        <v>11.6932983398438</v>
+        <v>-0.35693359375</v>
       </c>
       <c r="V38">
-        <v>13.0117797851563</v>
+        <v>12.69921875</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
       <c r="A39" s="2">
-        <v>46183</v>
+        <v>46196</v>
       </c>
       <c r="B39">
-        <v>-12.3649291992188</v>
+        <v>-7.54193115234375</v>
       </c>
       <c r="C39">
-        <v>-18.3779907226563</v>
+        <v>2.93658447265625</v>
       </c>
       <c r="D39">
-        <v>-11.3324584960938</v>
+        <v>1.19757080078125</v>
       </c>
       <c r="E39">
-        <v>701.659973144531</v>
+        <v>715.739990234375</v>
       </c>
       <c r="F39">
-        <v>711.280029296875</v>
+        <v>723.609985351563</v>
       </c>
       <c r="G39">
-        <v>692.929992675781</v>
+        <v>712.110107421875</v>
       </c>
       <c r="H39">
-        <v>693.690002441406</v>
+        <v>713.650024414063</v>
       </c>
       <c r="I39">
-        <v>708.005310058594</v>
+        <v>720.155700683594</v>
       </c>
       <c r="J39">
-        <v>686.054260253906</v>
+        <v>707.419250488281</v>
       </c>
       <c r="K39">
-        <v>65334200</v>
+        <v>53354100</v>
       </c>
       <c r="L39">
-        <v>-0.694280743598938</v>
+        <v>-1.52856731414795</v>
       </c>
       <c r="M39">
-        <v>70.9529495239258</v>
+        <v>71.3319702148438</v>
       </c>
       <c r="N39">
-        <v>12.8500566482544</v>
+        <v>-2.70278596878052</v>
       </c>
       <c r="O39" t="s">
         <v>23</v>
       </c>
       <c r="P39">
-        <v>-34.9611358642578</v>
+        <v>-68.6438598632813</v>
       </c>
       <c r="Q39">
-        <v>704.325805664063</v>
+        <v>724.445922851563</v>
       </c>
       <c r="R39">
-        <v>717.002075195313</v>
+        <v>726.346984863281</v>
       </c>
       <c r="S39">
-        <v>716.467102050781</v>
+        <v>723.753662109375</v>
       </c>
       <c r="T39">
-        <v>-3.27471923828125</v>
+        <v>-3.45428466796875</v>
       </c>
       <c r="U39">
-        <v>-6.875732421875</v>
+        <v>-4.69085693359375</v>
       </c>
       <c r="V39">
-        <v>21.9510498046875</v>
+        <v>12.7364501953125</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="2">
-        <v>46182</v>
+        <v>46195</v>
       </c>
       <c r="B40">
-        <v>-13.7294921875</v>
+        <v>1.6483154296875</v>
       </c>
       <c r="C40">
-        <v>-13.2486572265625</v>
+        <v>11.2158203125</v>
       </c>
       <c r="D40">
-        <v>-4.69677734375</v>
+        <v>5.11346435546875</v>
       </c>
       <c r="E40">
-        <v>722.97998046875</v>
+        <v>742.02001953125</v>
       </c>
       <c r="F40">
-        <v>725.659973144531</v>
+        <v>745.450012207031</v>
       </c>
       <c r="G40">
-        <v>686.369995117188</v>
+        <v>734.390014648438</v>
       </c>
       <c r="H40">
-        <v>707.830017089844</v>
+        <v>737.950012207031</v>
       </c>
       <c r="I40">
-        <v>712.016662597656</v>
+        <v>741.215698242188</v>
       </c>
       <c r="J40">
-        <v>693.914184570313</v>
+        <v>733.294921875</v>
       </c>
       <c r="K40">
-        <v>91932096</v>
+        <v>43518500</v>
       </c>
       <c r="L40">
-        <v>-0.175234839320183</v>
+        <v>-1.16618704795837</v>
       </c>
       <c r="M40">
-        <v>62.873649597168</v>
+        <v>73.3134765625</v>
       </c>
       <c r="N40">
-        <v>33.6117057800293</v>
+        <v>5.07466554641724</v>
       </c>
       <c r="O40" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P40">
-        <v>-26.2471084594727</v>
+        <v>19.3256072998047</v>
       </c>
       <c r="Q40">
-        <v>712.73583984375</v>
+        <v>735.138427734375</v>
       </c>
       <c r="R40">
-        <v>723.062622070313</v>
+        <v>730.110168457031</v>
       </c>
       <c r="S40">
-        <v>718.90283203125</v>
+        <v>725.110412597656</v>
       </c>
       <c r="T40">
-        <v>-13.643310546875</v>
+        <v>-4.23431396484375</v>
       </c>
       <c r="U40">
-        <v>7.544189453125</v>
+        <v>-1.0950927734375</v>
       </c>
       <c r="V40">
-        <v>18.1024780273438</v>
+        <v>7.9207763671875</v>
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="2">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B41">
-        <v>-12.5181274414063</v>
+        <v>3.2733154296875</v>
       </c>
       <c r="C41">
-        <v>-9.29669189453125</v>
+        <v>11.8580932617188</v>
       </c>
       <c r="D41">
-        <v>1.19342041015625</v>
+        <v>2.6954345703125</v>
       </c>
       <c r="E41">
-        <v>717.809997558594</v>
+        <v>737.200012207031</v>
       </c>
       <c r="F41">
-        <v>723.030029296875</v>
+        <v>741.820007324219</v>
       </c>
       <c r="G41">
-        <v>713.070007324219</v>
+        <v>732.510009765625</v>
       </c>
       <c r="H41">
-        <v>716.070007324219</v>
+        <v>740.619995117188</v>
       </c>
       <c r="I41">
-        <v>725.028442382813</v>
+        <v>743.136840820313</v>
       </c>
       <c r="J41">
-        <v>712.784912109375</v>
+        <v>735.426635742188</v>
       </c>
       <c r="K41">
-        <v>47401400</v>
+        <v>50154500</v>
       </c>
       <c r="L41">
-        <v>1.08476328849792</v>
+        <v>-0.598089337348938</v>
       </c>
       <c r="M41">
-        <v>47.0569915771484</v>
+        <v>69.7727432250977</v>
       </c>
       <c r="N41">
-        <v>6.76580238342285</v>
+        <v>0.589374721050262</v>
       </c>
       <c r="O41" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P41">
-        <v>-11.8436107635498</v>
+        <v>37.9242057800293</v>
       </c>
       <c r="Q41">
-        <v>720.873657226563</v>
+        <v>732.823364257813</v>
       </c>
       <c r="R41">
-        <v>727.351684570313</v>
+        <v>727.787353515625</v>
       </c>
       <c r="S41">
-        <v>720.332763671875</v>
+        <v>723.4755859375</v>
       </c>
       <c r="T41">
-        <v>1.9984130859375</v>
+        <v>1.31683349609375</v>
       </c>
       <c r="U41">
-        <v>-0.28509521484375</v>
+        <v>2.9166259765625</v>
       </c>
       <c r="V41">
-        <v>12.2435302734375</v>
+        <v>7.710205078125</v>
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="2">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B42">
-        <v>-17.9691162109375</v>
+        <v>-1.5975341796875</v>
       </c>
       <c r="C42">
-        <v>-5.5330810546875</v>
+        <v>5.6368408203125</v>
       </c>
       <c r="D42">
-        <v>4.83697509765625</v>
+        <v>-1.7880859375</v>
       </c>
       <c r="E42">
-        <v>730.059997558594</v>
+        <v>735.190002441406</v>
       </c>
       <c r="F42">
-        <v>731.690002441406</v>
+        <v>735.679992675781</v>
       </c>
       <c r="G42">
-        <v>704.320007324219</v>
+        <v>720.849975585938</v>
       </c>
       <c r="H42">
-        <v>705.059997558594</v>
+        <v>722.510009765625</v>
       </c>
       <c r="I42">
-        <v>715.396240234375</v>
+        <v>728.564636230469</v>
       </c>
       <c r="J42">
-        <v>697.439208984375</v>
+        <v>716.205810546875</v>
       </c>
       <c r="K42">
-        <v>99606496</v>
+        <v>51669300</v>
       </c>
       <c r="L42">
-        <v>1.08952403068542</v>
+        <v>-0.679039359092712</v>
       </c>
       <c r="M42">
-        <v>44.0749664306641</v>
+        <v>69.3639297485352</v>
       </c>
       <c r="N42">
-        <v>81.4434432983398</v>
+        <v>10.1039295196533</v>
       </c>
       <c r="O42" t="s">
         <v>23</v>
       </c>
       <c r="P42">
-        <v>-100</v>
+        <v>-31.3353672027588</v>
       </c>
       <c r="Q42">
-        <v>723.7822265625</v>
+        <v>725.923095703125</v>
       </c>
       <c r="R42">
-        <v>730.068542480469</v>
+        <v>724.027099609375</v>
       </c>
       <c r="S42">
-        <v>720.43701171875</v>
+        <v>721.264404296875</v>
       </c>
       <c r="T42">
-        <v>-16.2937622070313</v>
+        <v>-7.1153564453125</v>
       </c>
       <c r="U42">
-        <v>-6.88079833984375</v>
+        <v>-4.6441650390625</v>
       </c>
       <c r="V42">
-        <v>17.95703125</v>
+        <v>12.3588256835938</v>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="2">
-        <v>46177</v>
+        <v>46189</v>
       </c>
       <c r="B43">
-        <v>-0.975341796875</v>
+        <v>10.0441284179688</v>
       </c>
       <c r="C43">
-        <v>7.42987060546875</v>
+        <v>5.4068603515625</v>
       </c>
       <c r="D43">
-        <v>13.647216796875</v>
+        <v>-1.7308349609375</v>
       </c>
       <c r="E43">
-        <v>735.47998046875</v>
+        <v>742.25</v>
       </c>
       <c r="F43">
-        <v>743.498779296875</v>
+        <v>744.219970703125</v>
       </c>
       <c r="G43">
-        <v>732.619995117188</v>
+        <v>729.640014648438</v>
       </c>
       <c r="H43">
-        <v>740.609985351563</v>
+        <v>729.859985351563</v>
       </c>
       <c r="I43">
-        <v>743.850280761719</v>
+        <v>734.100280761719</v>
       </c>
       <c r="J43">
-        <v>735.677795410156</v>
+        <v>724.563842773438</v>
       </c>
       <c r="K43">
-        <v>40782500</v>
+        <v>45348600</v>
       </c>
       <c r="L43">
-        <v>2.66047596931458</v>
+        <v>-0.344752728939056</v>
       </c>
       <c r="M43">
-        <v>24.2912979125977</v>
+        <v>62.9985961914063</v>
       </c>
       <c r="N43">
-        <v>-21.1195449829102</v>
+        <v>18.2906303405762</v>
       </c>
       <c r="O43" t="s">
         <v>23</v>
       </c>
       <c r="P43">
-        <v>-44.857349395752</v>
+        <v>-8.74789142608643</v>
       </c>
       <c r="Q43">
-        <v>741.598266601563</v>
+        <v>729.420532226563</v>
       </c>
       <c r="R43">
-        <v>736.733764648438</v>
+        <v>724.500549316406</v>
       </c>
       <c r="S43">
-        <v>722.236206054688</v>
+        <v>720.938659667969</v>
       </c>
       <c r="T43">
-        <v>0.35150146484375</v>
+        <v>-10.1196899414063</v>
       </c>
       <c r="U43">
-        <v>3.05780029296875</v>
+        <v>-5.076171875</v>
       </c>
       <c r="V43">
-        <v>8.1724853515625</v>
+        <v>9.53643798828125</v>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="2">
-        <v>46176</v>
+        <v>46188</v>
       </c>
       <c r="B44">
-        <v>2.79071044921875</v>
+        <v>17.9420166015625</v>
       </c>
       <c r="C44">
-        <v>10.7752685546875</v>
+        <v>2.38287353515625</v>
       </c>
       <c r="D44">
-        <v>15.354248046875</v>
+        <v>-3.092041015625</v>
       </c>
       <c r="E44">
-        <v>747.309997558594</v>
+        <v>738.099975585938</v>
       </c>
       <c r="F44">
-        <v>748.650024414063</v>
+        <v>744.759887695313</v>
       </c>
       <c r="G44">
-        <v>741.010009765625</v>
+        <v>737.380004882813</v>
       </c>
       <c r="H44">
-        <v>744.210021972656</v>
+        <v>744</v>
       </c>
       <c r="I44">
-        <v>747.804443359375</v>
+        <v>746.012329101563</v>
       </c>
       <c r="J44">
-        <v>741.140686035156</v>
+        <v>740.643737792969</v>
       </c>
       <c r="K44">
-        <v>40270100</v>
+        <v>46710200</v>
       </c>
       <c r="L44">
-        <v>2.5899977684021</v>
+        <v>0.187627881765366</v>
       </c>
       <c r="M44">
-        <v>30.7950782775879</v>
+        <v>53.2574691772461</v>
       </c>
       <c r="N44">
-        <v>33.6207160949707</v>
+        <v>-9.68106651306152</v>
       </c>
       <c r="O44" t="s">
         <v>1</v>
       </c>
       <c r="P44">
-        <v>6.92222166061401</v>
+        <v>69.9155349731445</v>
       </c>
       <c r="Q44">
-        <v>743.139709472656</v>
+        <v>729.329650878906</v>
       </c>
       <c r="R44">
-        <v>735.671081542969</v>
+        <v>723.061889648438</v>
       </c>
       <c r="S44">
-        <v>720.251708984375</v>
+        <v>719.975463867188</v>
       </c>
       <c r="T44">
-        <v>-0.8455810546875</v>
+        <v>1.25244140625</v>
       </c>
       <c r="U44">
-        <v>0.13067626953125</v>
+        <v>3.26373291015625</v>
       </c>
       <c r="V44">
-        <v>6.66375732421875</v>
+        <v>5.36859130859375</v>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="2">
-        <v>46175</v>
+        <v>46185</v>
       </c>
       <c r="B45">
-        <v>5.36004638671875</v>
+        <v>5.90203857421875</v>
       </c>
       <c r="C45">
-        <v>13.5048828125</v>
+        <v>-8.1749267578125</v>
       </c>
       <c r="D45">
-        <v>15.9636840820313</v>
+        <v>-8.9888916015625</v>
       </c>
       <c r="E45">
-        <v>742.400024414063</v>
+        <v>717.609985351563</v>
       </c>
       <c r="F45">
-        <v>746.440002441406</v>
+        <v>724.010009765625</v>
       </c>
       <c r="G45">
-        <v>739.22998046875</v>
+        <v>711.280029296875</v>
       </c>
       <c r="H45">
-        <v>746.159973144531</v>
+        <v>721.340026855469</v>
       </c>
       <c r="I45">
-        <v>748.724243164063</v>
+        <v>727.374450683594</v>
       </c>
       <c r="J45">
-        <v>741.950927734375</v>
+        <v>713.639892578125</v>
       </c>
       <c r="K45">
-        <v>30085200</v>
+        <v>51236000</v>
       </c>
       <c r="L45">
-        <v>2.65285539627075</v>
+        <v>0.152864009141922</v>
       </c>
       <c r="M45">
-        <v>23.0466346740723</v>
+        <v>58.966007232666</v>
       </c>
       <c r="N45">
-        <v>-0.185056746006012</v>
+        <v>0.648391544818878</v>
       </c>
       <c r="O45" t="s">
         <v>1</v>
       </c>
       <c r="P45">
-        <v>47.4610328674316</v>
+        <v>46.5396575927734</v>
       </c>
       <c r="Q45">
-        <v>741.898193359375</v>
+        <v>715.103759765625</v>
       </c>
       <c r="R45">
-        <v>733.174987792969</v>
+        <v>717.614929199219</v>
       </c>
       <c r="S45">
-        <v>717.529174804688</v>
+        <v>717.106567382813</v>
       </c>
       <c r="T45">
-        <v>2.28424072265625</v>
+        <v>3.36444091796875</v>
       </c>
       <c r="U45">
-        <v>2.720947265625</v>
+        <v>2.35986328125</v>
       </c>
       <c r="V45">
-        <v>6.7733154296875</v>
+        <v>13.7345581054688</v>
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1">
       <c r="A46" s="2">
-        <v>46174</v>
+        <v>46184</v>
       </c>
       <c r="B46">
-        <v>4.9361572265625</v>
+        <v>1.81298828125</v>
       </c>
       <c r="C46">
-        <v>13.6161499023438</v>
+        <v>-14.1453247070313</v>
       </c>
       <c r="D46">
-        <v>14.2886962890625</v>
+        <v>-10.99951171875</v>
       </c>
       <c r="E46">
-        <v>737.039978027344</v>
+        <v>699.289978027344</v>
       </c>
       <c r="F46">
-        <v>745.650024414063</v>
+        <v>718.372009277344</v>
       </c>
       <c r="G46">
-        <v>735.989990234375</v>
+        <v>695</v>
       </c>
       <c r="H46">
-        <v>742.739990234375</v>
+        <v>717.119995117188</v>
       </c>
       <c r="I46">
-        <v>744.594055175781</v>
+        <v>719.705078125</v>
       </c>
       <c r="J46">
-        <v>738.999633789063</v>
+        <v>706.693298339844</v>
       </c>
       <c r="K46">
-        <v>33890500</v>
+        <v>71798800</v>
       </c>
       <c r="L46">
-        <v>2.7114315032959</v>
+        <v>0.201433449983597</v>
       </c>
       <c r="M46">
-        <v>23.0893630981445</v>
+        <v>58.5861396789551</v>
       </c>
       <c r="N46">
-        <v>-23.5814037322998</v>
+        <v>-17.4295921325684</v>
       </c>
       <c r="O46" t="s">
         <v>1</v>
       </c>
       <c r="P46">
-        <v>39.6027374267578</v>
+        <v>35.6000556945801</v>
       </c>
       <c r="Q46">
-        <v>738.188171386719</v>
+        <v>709.418640136719</v>
       </c>
       <c r="R46">
-        <v>729.403381347656</v>
+        <v>716.472106933594</v>
       </c>
       <c r="S46">
-        <v>714.000061035156</v>
+        <v>716.43017578125</v>
       </c>
       <c r="T46">
-        <v>-1.05596923828125</v>
+        <v>1.33306884765625</v>
       </c>
       <c r="U46">
-        <v>3.0096435546875</v>
+        <v>11.6932983398438</v>
       </c>
       <c r="V46">
-        <v>5.59442138671875</v>
+        <v>13.0117797851563</v>
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="2">
-        <v>46171</v>
+        <v>46183</v>
       </c>
       <c r="B47">
-        <v>6.173095703125</v>
+        <v>-12.3649291992188</v>
       </c>
       <c r="C47">
-        <v>13.0711059570313</v>
+        <v>-18.3779907226563</v>
       </c>
       <c r="D47">
-        <v>12.3822021484375</v>
+        <v>-11.3324584960938</v>
       </c>
       <c r="E47">
-        <v>737.840026855469</v>
+        <v>701.659973144531</v>
       </c>
       <c r="F47">
-        <v>741.630004882813</v>
+        <v>711.280029296875</v>
       </c>
       <c r="G47">
-        <v>735.25</v>
+        <v>692.929992675781</v>
       </c>
       <c r="H47">
-        <v>738.309997558594</v>
+        <v>693.690002441406</v>
       </c>
       <c r="I47">
-        <v>741.804931640625</v>
+        <v>708.005310058594</v>
       </c>
       <c r="J47">
-        <v>735.491088867188</v>
+        <v>686.054260253906</v>
       </c>
       <c r="K47">
-        <v>37541600</v>
+        <v>65334200</v>
       </c>
       <c r="L47">
-        <v>2.55381274223328</v>
+        <v>-0.694280743598938</v>
       </c>
       <c r="M47">
-        <v>30.2143249511719</v>
+        <v>70.9529495239258</v>
       </c>
       <c r="N47">
-        <v>7.9931526184082</v>
+        <v>12.8500566482544</v>
       </c>
       <c r="O47" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P47">
-        <v>50.9271125793457</v>
+        <v>-34.9611358642578</v>
       </c>
       <c r="Q47">
-        <v>734.275756835938</v>
+        <v>704.325805664063</v>
       </c>
       <c r="R47">
-        <v>725.6787109375</v>
+        <v>717.002075195313</v>
       </c>
       <c r="S47">
-        <v>710.529968261719</v>
+        <v>716.467102050781</v>
       </c>
       <c r="T47">
-        <v>0.1749267578125</v>
+        <v>-3.27471923828125</v>
       </c>
       <c r="U47">
-        <v>0.2410888671875</v>
+        <v>-6.875732421875</v>
       </c>
       <c r="V47">
-        <v>6.3138427734375</v>
+        <v>21.9510498046875</v>
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1">
       <c r="A48" s="2">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="B48">
-        <v>6.68243408203125</v>
+        <v>-13.7294921875</v>
       </c>
       <c r="C48">
-        <v>10.8438720703125</v>
+        <v>-13.2486572265625</v>
       </c>
       <c r="D48">
-        <v>11.2130737304688</v>
+        <v>-4.69677734375</v>
       </c>
       <c r="E48">
-        <v>729.72998046875</v>
+        <v>722.97998046875</v>
       </c>
       <c r="F48">
-        <v>736.599975585938</v>
+        <v>725.659973144531</v>
       </c>
       <c r="G48">
-        <v>726.409973144531</v>
+        <v>686.369995117188</v>
       </c>
       <c r="H48">
-        <v>735.599975585938</v>
+        <v>707.830017089844</v>
       </c>
       <c r="I48">
-        <v>737.163879394531</v>
+        <v>712.016662597656</v>
       </c>
       <c r="J48">
-        <v>730.400512695313</v>
+        <v>693.914184570313</v>
       </c>
       <c r="K48">
-        <v>32839900</v>
+        <v>91932096</v>
       </c>
       <c r="L48">
-        <v>2.67143321037292</v>
+        <v>-0.175234839320183</v>
       </c>
       <c r="M48">
-        <v>27.9780006408691</v>
+        <v>62.873649597168</v>
       </c>
       <c r="N48">
-        <v>14.7109880447388</v>
+        <v>33.6117057800293</v>
       </c>
       <c r="O48" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P48">
-        <v>30.5366401672363</v>
+        <v>-26.2471084594727</v>
       </c>
       <c r="Q48">
-        <v>730.010498046875</v>
+        <v>712.73583984375</v>
       </c>
       <c r="R48">
-        <v>721.977111816406</v>
+        <v>723.062622070313</v>
       </c>
       <c r="S48">
-        <v>707.040832519531</v>
+        <v>718.90283203125</v>
       </c>
       <c r="T48">
-        <v>0.56390380859375</v>
+        <v>-13.643310546875</v>
       </c>
       <c r="U48">
-        <v>3.99053955078125</v>
+        <v>7.544189453125</v>
       </c>
       <c r="V48">
-        <v>6.76336669921875</v>
+        <v>18.1024780273438</v>
       </c>
     </row>
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="2">
-        <v>46169</v>
+        <v>46181</v>
       </c>
       <c r="B49">
-        <v>6.714599609375</v>
+        <v>-12.5181274414063</v>
       </c>
       <c r="C49">
-        <v>8.61016845703125</v>
+        <v>-9.29669189453125</v>
       </c>
       <c r="D49">
-        <v>9.88421630859375</v>
+        <v>1.19342041015625</v>
       </c>
       <c r="E49">
-        <v>732.960021972656</v>
+        <v>717.809997558594</v>
       </c>
       <c r="F49">
-        <v>733.320007324219</v>
+        <v>723.030029296875</v>
       </c>
       <c r="G49">
-        <v>725.440002441406</v>
+        <v>713.070007324219</v>
       </c>
       <c r="H49">
-        <v>729.450012207031</v>
+        <v>716.070007324219</v>
       </c>
       <c r="I49">
-        <v>731.802978515625</v>
+        <v>725.028442382813</v>
       </c>
       <c r="J49">
-        <v>725.548645019531</v>
+        <v>712.784912109375</v>
       </c>
       <c r="K49">
-        <v>35148600</v>
+        <v>47401400</v>
       </c>
       <c r="L49">
-        <v>2.39857697486877</v>
+        <v>1.08476328849792</v>
       </c>
       <c r="M49">
-        <v>24.3899917602539</v>
+        <v>47.0569915771484</v>
       </c>
       <c r="N49">
-        <v>5.44436931610107</v>
+        <v>6.76580238342285</v>
       </c>
       <c r="O49" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P49">
-        <v>31.0160350799561</v>
+        <v>-11.8436107635498</v>
       </c>
       <c r="Q49">
-        <v>725.62451171875</v>
+        <v>720.873657226563</v>
       </c>
       <c r="R49">
-        <v>718.259155273438</v>
+        <v>727.351684570313</v>
       </c>
       <c r="S49">
-        <v>703.721618652344</v>
+        <v>720.332763671875</v>
       </c>
       <c r="T49">
-        <v>-1.51702880859375</v>
+        <v>1.9984130859375</v>
       </c>
       <c r="U49">
-        <v>0.108642578125</v>
+        <v>-0.28509521484375</v>
       </c>
       <c r="V49">
-        <v>6.25433349609375</v>
+        <v>12.2435302734375</v>
       </c>
     </row>
     <row r="50" ht="19.5" customHeight="1">
       <c r="A50" s="2">
-        <v>46168</v>
+        <v>46178</v>
       </c>
       <c r="B50">
-        <v>9.8369140625</v>
+        <v>-17.9691162109375</v>
       </c>
       <c r="C50">
-        <v>7.07666015625</v>
+        <v>-5.5330810546875</v>
       </c>
       <c r="D50">
-        <v>9.6522216796875</v>
+        <v>4.83697509765625</v>
       </c>
       <c r="E50">
-        <v>725.960021972656</v>
+        <v>730.059997558594</v>
       </c>
       <c r="F50">
-        <v>731.169982910156</v>
+        <v>731.690002441406</v>
       </c>
       <c r="G50">
-        <v>724.159973144531</v>
+        <v>704.320007324219</v>
       </c>
       <c r="H50">
-        <v>730.280029296875</v>
+        <v>705.059997558594</v>
       </c>
       <c r="I50">
-        <v>731.322998046875</v>
+        <v>715.396240234375</v>
       </c>
       <c r="J50">
-        <v>727.299133300781</v>
+        <v>697.439208984375</v>
       </c>
       <c r="K50">
-        <v>34254600</v>
+        <v>99606496</v>
       </c>
       <c r="L50">
-        <v>2.60524201393127</v>
+        <v>1.08952403068542</v>
       </c>
       <c r="M50">
-        <v>23.130672454834</v>
+        <v>44.0749664306641</v>
       </c>
       <c r="N50">
-        <v>14.2258224487305</v>
+        <v>81.4434432983398</v>
       </c>
       <c r="O50" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P50">
-        <v>87.9896697998047</v>
+        <v>-100</v>
       </c>
       <c r="Q50">
-        <v>722.322204589844</v>
+        <v>723.7822265625</v>
       </c>
       <c r="R50">
-        <v>714.923095703125</v>
+        <v>730.068542480469</v>
       </c>
       <c r="S50">
-        <v>700.607604980469</v>
+        <v>720.43701171875</v>
       </c>
       <c r="T50">
-        <v>0.15301513671875</v>
+        <v>-16.2937622070313</v>
       </c>
       <c r="U50">
-        <v>3.13916015625</v>
+        <v>-6.88079833984375</v>
       </c>
       <c r="V50">
-        <v>4.02386474609375</v>
+        <v>17.95703125</v>
       </c>
     </row>
     <row r="51" ht="19.5" customHeight="1">
       <c r="A51" s="2">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="B51">
-        <v>5.9239501953125</v>
+        <v>-0.975341796875</v>
       </c>
       <c r="C51">
-        <v>2.3765869140625</v>
+        <v>7.42987060546875</v>
       </c>
       <c r="D51">
-        <v>8.29400634765625</v>
+        <v>13.647216796875</v>
       </c>
       <c r="E51">
-        <v>718.070007324219</v>
+        <v>735.47998046875</v>
       </c>
       <c r="F51">
-        <v>722.119995117188</v>
+        <v>743.498779296875</v>
       </c>
       <c r="G51">
-        <v>715.950012207031</v>
+        <v>732.619995117188</v>
       </c>
       <c r="H51">
-        <v>717.539978027344</v>
+        <v>740.609985351563</v>
       </c>
       <c r="I51">
-        <v>721.849426269531</v>
+        <v>743.850280761719</v>
       </c>
       <c r="J51">
-        <v>715.4404296875</v>
+        <v>735.677795410156</v>
       </c>
       <c r="K51">
-        <v>33118500</v>
+        <v>40782500</v>
       </c>
       <c r="L51">
-        <v>2.6552414894104</v>
+        <v>2.66047596931458</v>
       </c>
       <c r="M51">
-        <v>20.2499504089355</v>
+        <v>24.2912979125977</v>
       </c>
       <c r="N51">
-        <v>16.8341026306152</v>
+        <v>-21.1195449829102</v>
       </c>
       <c r="O51" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P51">
-        <v>35.0146331787109</v>
+        <v>-44.857349395752</v>
       </c>
       <c r="Q51">
-        <v>715.006958007813</v>
+        <v>741.598266601563</v>
       </c>
       <c r="R51">
-        <v>710.620239257813</v>
+        <v>736.733764648438</v>
       </c>
       <c r="S51">
-        <v>697.047485351563</v>
+        <v>722.236206054688</v>
       </c>
       <c r="T51">
-        <v>-0.27056884765625</v>
+        <v>0.35150146484375</v>
       </c>
       <c r="U51">
-        <v>-0.50958251953125</v>
+        <v>3.05780029296875</v>
       </c>
       <c r="V51">
-        <v>6.40899658203125</v>
+        <v>8.1724853515625</v>
       </c>
     </row>
     <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="2">
-        <v>46163</v>
+        <v>46176</v>
       </c>
       <c r="B52">
-        <v>3.9808349609375</v>
+        <v>2.79071044921875</v>
       </c>
       <c r="C52">
-        <v>0.52301025390625</v>
+        <v>10.7752685546875</v>
       </c>
       <c r="D52">
-        <v>8.81036376953125</v>
+        <v>15.354248046875</v>
       </c>
       <c r="E52">
-        <v>708.989990234375</v>
+        <v>747.309997558594</v>
       </c>
       <c r="F52">
-        <v>717.119995117188</v>
+        <v>748.650024414063</v>
       </c>
       <c r="G52">
-        <v>706.77001953125</v>
+        <v>741.010009765625</v>
       </c>
       <c r="H52">
-        <v>714.510009765625</v>
+        <v>744.210021972656</v>
       </c>
       <c r="I52">
-        <v>717.848571777344</v>
+        <v>747.804443359375</v>
       </c>
       <c r="J52">
-        <v>710.158569335938</v>
+        <v>741.140686035156</v>
       </c>
       <c r="K52">
-        <v>36415300</v>
+        <v>40270100</v>
       </c>
       <c r="L52">
-        <v>2.57905220985413</v>
+        <v>2.5899977684021</v>
       </c>
       <c r="M52">
-        <v>17.3322257995605</v>
+        <v>30.7950782775879</v>
       </c>
       <c r="N52">
-        <v>-23.8569393157959</v>
+        <v>33.6207160949707</v>
       </c>
       <c r="O52" t="s">
         <v>1</v>
       </c>
       <c r="P52">
-        <v>50.2529411315918</v>
+        <v>6.92222166061401</v>
       </c>
       <c r="Q52">
-        <v>711.722900390625</v>
+        <v>743.139709472656</v>
       </c>
       <c r="R52">
-        <v>708.550659179688</v>
+        <v>735.671081542969</v>
       </c>
       <c r="S52">
-        <v>694.449829101563</v>
+        <v>720.251708984375</v>
       </c>
       <c r="T52">
-        <v>0.72857666015625</v>
+        <v>-0.8455810546875</v>
       </c>
       <c r="U52">
-        <v>3.3885498046875</v>
+        <v>0.13067626953125</v>
       </c>
       <c r="V52">
-        <v>7.69000244140625</v>
+        <v>6.66375732421875</v>
       </c>
     </row>
     <row r="53" ht="19.5" customHeight="1">
       <c r="A53" s="2">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="B53">
-        <v>0.1451416015625</v>
+        <v>5.36004638671875</v>
       </c>
       <c r="C53">
-        <v>0.3658447265625</v>
+        <v>13.5048828125</v>
       </c>
       <c r="D53">
-        <v>9.87542724609375</v>
+        <v>15.9636840820313</v>
       </c>
       <c r="E53">
-        <v>705.289978027344</v>
+        <v>742.400024414063</v>
       </c>
       <c r="F53">
-        <v>713.150024414063</v>
+        <v>746.440002441406</v>
       </c>
       <c r="G53">
-        <v>703.789978027344</v>
+        <v>739.22998046875</v>
       </c>
       <c r="H53">
-        <v>713.150024414063</v>
+        <v>746.159973144531</v>
       </c>
       <c r="I53">
-        <v>716.50341796875</v>
+        <v>748.724243164063</v>
       </c>
       <c r="J53">
-        <v>709.490905761719</v>
+        <v>741.950927734375</v>
       </c>
       <c r="K53">
-        <v>36779200</v>
+        <v>30085200</v>
       </c>
       <c r="L53">
-        <v>2.55238270759583</v>
+        <v>2.65285539627075</v>
       </c>
       <c r="M53">
-        <v>22.7627124786377</v>
+        <v>23.0466346740723</v>
       </c>
       <c r="N53">
-        <v>-7.18874406814575</v>
+        <v>-0.185056746006012</v>
       </c>
       <c r="O53" t="s">
         <v>1</v>
       </c>
       <c r="P53">
-        <v>56.4056205749512</v>
+        <v>47.4610328674316</v>
       </c>
       <c r="Q53">
-        <v>709.273071289063</v>
+        <v>741.898193359375</v>
       </c>
       <c r="R53">
-        <v>706.804809570313</v>
+        <v>733.174987792969</v>
       </c>
       <c r="S53">
-        <v>691.875183105469</v>
+        <v>717.529174804688</v>
       </c>
       <c r="T53">
-        <v>3.3533935546875</v>
+        <v>2.28424072265625</v>
       </c>
       <c r="U53">
-        <v>5.700927734375</v>
+        <v>2.720947265625</v>
       </c>
       <c r="V53">
-        <v>7.01251220703125</v>
+        <v>6.7733154296875</v>
       </c>
     </row>
     <row r="54" ht="19.5" customHeight="1">
       <c r="A54" s="2">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="B54">
-        <v>-6.26214599609375</v>
+        <v>4.9361572265625</v>
       </c>
       <c r="C54">
-        <v>-0.5784912109375</v>
+        <v>13.6161499023438</v>
       </c>
       <c r="D54">
-        <v>11.0665283203125</v>
+        <v>14.2886962890625</v>
       </c>
       <c r="E54">
-        <v>699.809997558594</v>
+        <v>737.039978027344</v>
       </c>
       <c r="F54">
-        <v>706.489990234375</v>
+        <v>745.650024414063</v>
       </c>
       <c r="G54">
-        <v>695.25</v>
+        <v>735.989990234375</v>
       </c>
       <c r="H54">
-        <v>701.530029296875</v>
+        <v>742.739990234375</v>
       </c>
       <c r="I54">
-        <v>707.353698730469</v>
+        <v>744.594055175781</v>
       </c>
       <c r="J54">
-        <v>696.877746582031</v>
+        <v>738.999633789063</v>
       </c>
       <c r="K54">
-        <v>46827500</v>
+        <v>33890500</v>
       </c>
       <c r="L54">
-        <v>1.98381114006042</v>
+        <v>2.7114315032959</v>
       </c>
       <c r="M54">
-        <v>24.5258102416992</v>
+        <v>23.0893630981445</v>
       </c>
       <c r="N54">
-        <v>2.26992583274841</v>
+        <v>-23.5814037322998</v>
       </c>
       <c r="O54" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P54">
-        <v>-31.003755569458</v>
+        <v>39.6027374267578</v>
       </c>
       <c r="Q54">
-        <v>705.485595703125</v>
+        <v>738.188171386719</v>
       </c>
       <c r="R54">
-        <v>704.908386230469</v>
+        <v>729.403381347656</v>
       </c>
       <c r="S54">
-        <v>689.250915527344</v>
+        <v>714.000061035156</v>
       </c>
       <c r="T54">
-        <v>0.86370849609375</v>
+        <v>-1.05596923828125</v>
       </c>
       <c r="U54">
-        <v>1.62774658203125</v>
+        <v>3.0096435546875</v>
       </c>
       <c r="V54">
-        <v>10.4759521484375</v>
+        <v>5.59442138671875</v>
       </c>
     </row>
     <row r="55" ht="19.5" customHeight="1">
       <c r="A55" s="2">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="B55">
-        <v>-3.43994140625</v>
+        <v>6.173095703125</v>
       </c>
       <c r="C55">
-        <v>4.18682861328125</v>
+        <v>13.0711059570313</v>
       </c>
       <c r="D55">
-        <v>15.6046142578125</v>
+        <v>12.3822021484375</v>
       </c>
       <c r="E55">
-        <v>711.539978027344</v>
+        <v>737.840026855469</v>
       </c>
       <c r="F55">
-        <v>712.070007324219</v>
+        <v>741.630004882813</v>
       </c>
       <c r="G55">
-        <v>698.849975585938</v>
+        <v>735.25</v>
       </c>
       <c r="H55">
-        <v>705.880004882813</v>
+        <v>738.309997558594</v>
       </c>
       <c r="I55">
-        <v>710.798767089844</v>
+        <v>741.804931640625</v>
       </c>
       <c r="J55">
-        <v>700.581359863281</v>
+        <v>735.491088867188</v>
       </c>
       <c r="K55">
-        <v>49834500</v>
+        <v>37541600</v>
       </c>
       <c r="L55">
-        <v>1.84238111972809</v>
+        <v>2.55381274223328</v>
       </c>
       <c r="M55">
-        <v>23.9814491271973</v>
+        <v>30.2143249511719</v>
       </c>
       <c r="N55">
-        <v>62.2379379272461</v>
+        <v>7.9931526184082</v>
       </c>
       <c r="O55" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P55">
-        <v>-50.4282302856445</v>
+        <v>50.9271125793457</v>
       </c>
       <c r="Q55">
-        <v>709.042114257813</v>
+        <v>734.275756835938</v>
       </c>
       <c r="R55">
-        <v>705.54296875</v>
+        <v>725.6787109375</v>
       </c>
       <c r="S55">
-        <v>687.760314941406</v>
+        <v>710.529968261719</v>
       </c>
       <c r="T55">
-        <v>-1.271240234375</v>
+        <v>0.1749267578125</v>
       </c>
       <c r="U55">
-        <v>1.73138427734375</v>
+        <v>0.2410888671875</v>
       </c>
       <c r="V55">
-        <v>10.2174072265625</v>
+        <v>6.3138427734375</v>
       </c>
     </row>
     <row r="56" ht="19.5" customHeight="1">
       <c r="A56" s="2">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="B56">
-        <v>-0.6888427734375</v>
+        <v>6.68243408203125</v>
       </c>
       <c r="C56">
-        <v>9.64984130859375</v>
+        <v>10.8438720703125</v>
       </c>
       <c r="D56">
-        <v>19.1634521484375</v>
+        <v>11.2130737304688</v>
       </c>
       <c r="E56">
-        <v>710.140014648438</v>
+        <v>729.72998046875</v>
       </c>
       <c r="F56">
-        <v>715.130004882813</v>
+        <v>736.599975585938</v>
       </c>
       <c r="G56">
-        <v>705.549987792969</v>
+        <v>726.409973144531</v>
       </c>
       <c r="H56">
-        <v>708.929992675781</v>
+        <v>735.599975585938</v>
       </c>
       <c r="I56">
-        <v>713.73095703125</v>
+        <v>737.163879394531</v>
       </c>
       <c r="J56">
-        <v>705.546264648438</v>
+        <v>730.400512695313</v>
       </c>
       <c r="K56">
-        <v>51792600</v>
+        <v>32839900</v>
       </c>
       <c r="L56">
-        <v>2.26713919639587</v>
+        <v>2.67143321037292</v>
       </c>
       <c r="M56">
-        <v>14.7816534042358</v>
+        <v>27.9780006408691</v>
       </c>
       <c r="N56">
-        <v>17.9724540710449</v>
+        <v>14.7109880447388</v>
       </c>
       <c r="O56" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P56">
-        <v>-41.642879486084</v>
+        <v>30.5366401672363</v>
       </c>
       <c r="Q56">
-        <v>712.332336425781</v>
+        <v>730.010498046875</v>
       </c>
       <c r="R56">
-        <v>705.323608398438</v>
+        <v>721.977111816406</v>
       </c>
       <c r="S56">
-        <v>685.609130859375</v>
+        <v>707.040832519531</v>
       </c>
       <c r="T56">
-        <v>-1.3990478515625</v>
+        <v>0.56390380859375</v>
       </c>
       <c r="U56">
-        <v>-0.00372314453125</v>
+        <v>3.99053955078125</v>
       </c>
       <c r="V56">
-        <v>8.1846923828125</v>
+        <v>6.76336669921875</v>
       </c>
     </row>
     <row r="57" ht="19.5" customHeight="1">
       <c r="A57" s="2">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="B57">
-        <v>4.2469482421875</v>
+        <v>6.714599609375</v>
       </c>
       <c r="C57">
-        <v>14.796142578125</v>
+        <v>8.61016845703125</v>
       </c>
       <c r="D57">
-        <v>22.1717529296875</v>
+        <v>9.88421630859375</v>
       </c>
       <c r="E57">
-        <v>714.619995117188</v>
+        <v>732.960021972656</v>
       </c>
       <c r="F57">
-        <v>722.030029296875</v>
+        <v>733.320007324219</v>
       </c>
       <c r="G57">
-        <v>714.219970703125</v>
+        <v>725.440002441406</v>
       </c>
       <c r="H57">
-        <v>719.789978027344</v>
+        <v>729.450012207031</v>
       </c>
       <c r="I57">
-        <v>723.651184082031</v>
+        <v>731.802978515625</v>
       </c>
       <c r="J57">
-        <v>717.320251464844</v>
+        <v>725.548645019531</v>
       </c>
       <c r="K57">
-        <v>33327500</v>
+        <v>35148600</v>
       </c>
       <c r="L57">
-        <v>2.38475680351257</v>
+        <v>2.39857697486877</v>
       </c>
       <c r="M57">
-        <v>12.5297498703003</v>
+        <v>24.3899917602539</v>
       </c>
       <c r="N57">
-        <v>-18.7818870544434</v>
+        <v>5.44436931610107</v>
       </c>
       <c r="O57" t="s">
         <v>1</v>
       </c>
       <c r="P57">
-        <v>63.4685020446777</v>
+        <v>31.0160350799561</v>
       </c>
       <c r="Q57">
-        <v>715.2548828125</v>
+        <v>725.62451171875</v>
       </c>
       <c r="R57">
-        <v>704.195434570313</v>
+        <v>718.259155273438</v>
       </c>
       <c r="S57">
-        <v>682.877746582031</v>
+        <v>703.721618652344</v>
       </c>
       <c r="T57">
-        <v>1.62115478515625</v>
+        <v>-1.51702880859375</v>
       </c>
       <c r="U57">
-        <v>3.10028076171875</v>
+        <v>0.108642578125</v>
       </c>
       <c r="V57">
-        <v>6.3309326171875</v>
+        <v>6.25433349609375</v>
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1">
       <c r="A58" s="2">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B58">
-        <v>3.7032470703125</v>
+        <v>9.8369140625</v>
       </c>
       <c r="C58">
-        <v>15.423828125</v>
+        <v>7.07666015625</v>
       </c>
       <c r="D58">
-        <v>22.1091918945313</v>
+        <v>9.6522216796875</v>
       </c>
       <c r="E58">
-        <v>709.960021972656</v>
+        <v>725.960021972656</v>
       </c>
       <c r="F58">
-        <v>716.650024414063</v>
+        <v>731.169982910156</v>
       </c>
       <c r="G58">
-        <v>704.830017089844</v>
+        <v>724.159973144531</v>
       </c>
       <c r="H58">
-        <v>714.710021972656</v>
+        <v>730.280029296875</v>
       </c>
       <c r="I58">
-        <v>718.768737792969</v>
+        <v>731.322998046875</v>
       </c>
       <c r="J58">
-        <v>709.555847167969</v>
+        <v>727.299133300781</v>
       </c>
       <c r="K58">
-        <v>40012500</v>
+        <v>34254600</v>
       </c>
       <c r="L58">
-        <v>2.5347580909729</v>
+        <v>2.60524201393127</v>
       </c>
       <c r="M58">
-        <v>15.427285194397</v>
+        <v>23.130672454834</v>
       </c>
       <c r="N58">
-        <v>1.57026052474976</v>
+        <v>14.2258224487305</v>
       </c>
       <c r="O58" t="s">
         <v>1</v>
       </c>
       <c r="P58">
-        <v>24.8097915649414</v>
+        <v>87.9896697998047</v>
       </c>
       <c r="Q58">
-        <v>710.250854492188</v>
+        <v>722.322204589844</v>
       </c>
       <c r="R58">
-        <v>699.560852050781</v>
+        <v>714.923095703125</v>
       </c>
       <c r="S58">
-        <v>678.413146972656</v>
+        <v>700.607604980469</v>
       </c>
       <c r="T58">
-        <v>2.11871337890625</v>
+        <v>0.15301513671875</v>
       </c>
       <c r="U58">
-        <v>4.725830078125</v>
+        <v>3.13916015625</v>
       </c>
       <c r="V58">
-        <v>9.212890625</v>
+        <v>4.02386474609375</v>
       </c>
     </row>
     <row r="59" ht="19.5" customHeight="1">
       <c r="A59" s="2">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B59">
-        <v>2.77252197265625</v>
+        <v>5.9239501953125</v>
       </c>
       <c r="C59">
-        <v>16.5220336914063</v>
+        <v>2.3765869140625</v>
       </c>
       <c r="D59">
-        <v>21.4488525390625</v>
+        <v>8.29400634765625</v>
       </c>
       <c r="E59">
-        <v>708.219970703125</v>
+        <v>718.070007324219</v>
       </c>
       <c r="F59">
-        <v>710.179992675781</v>
+        <v>722.119995117188</v>
       </c>
       <c r="G59">
-        <v>696.640014648438</v>
+        <v>715.950012207031</v>
       </c>
       <c r="H59">
-        <v>707.239990234375</v>
+        <v>717.539978027344</v>
       </c>
       <c r="I59">
-        <v>709.478881835938</v>
+        <v>721.849426269531</v>
       </c>
       <c r="J59">
-        <v>700.918579101563</v>
+        <v>715.4404296875</v>
       </c>
       <c r="K59">
-        <v>45873000</v>
+        <v>33118500</v>
       </c>
       <c r="L59">
-        <v>2.7076153755188</v>
+        <v>2.6552414894104</v>
       </c>
       <c r="M59">
-        <v>15.1887817382813</v>
+        <v>20.2499504089355</v>
       </c>
       <c r="N59">
-        <v>2.39614534378052</v>
+        <v>16.8341026306152</v>
       </c>
       <c r="O59" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P59">
-        <v>-41.1354179382324</v>
+        <v>35.0146331787109</v>
       </c>
       <c r="Q59">
-        <v>706.15283203125</v>
+        <v>715.006958007813</v>
       </c>
       <c r="R59">
-        <v>695.097351074219</v>
+        <v>710.620239257813</v>
       </c>
       <c r="S59">
-        <v>674.054138183594</v>
+        <v>697.047485351563</v>
       </c>
       <c r="T59">
-        <v>-0.70111083984375</v>
+        <v>-0.27056884765625</v>
       </c>
       <c r="U59">
-        <v>4.278564453125</v>
+        <v>-0.50958251953125</v>
       </c>
       <c r="V59">
-        <v>8.560302734375</v>
+        <v>6.40899658203125</v>
       </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
       <c r="A60" s="2">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B60">
-        <v>10.6698608398438</v>
+        <v>3.9808349609375</v>
       </c>
       <c r="C60">
-        <v>20.4730834960938</v>
+        <v>0.52301025390625</v>
       </c>
       <c r="D60">
-        <v>23.3697509765625</v>
+        <v>8.81036376953125</v>
       </c>
       <c r="E60">
-        <v>710.359985351563</v>
+        <v>708.989990234375</v>
       </c>
       <c r="F60">
-        <v>714.590026855469</v>
+        <v>717.119995117188</v>
       </c>
       <c r="G60">
-        <v>708.909973144531</v>
+        <v>706.77001953125</v>
       </c>
       <c r="H60">
-        <v>713.289978027344</v>
+        <v>714.510009765625</v>
       </c>
       <c r="I60">
-        <v>716.151489257813</v>
+        <v>717.848571777344</v>
       </c>
       <c r="J60">
-        <v>709.742797851563</v>
+        <v>710.158569335938</v>
       </c>
       <c r="K60">
-        <v>36019100</v>
+        <v>36415300</v>
       </c>
       <c r="L60">
-        <v>3.1309494972229</v>
+        <v>2.57905220985413</v>
       </c>
       <c r="M60">
-        <v>14.8333530426025</v>
+        <v>17.3322257995605</v>
       </c>
       <c r="N60">
-        <v>3.09983611106873</v>
+        <v>-23.8569393157959</v>
       </c>
       <c r="O60" t="s">
         <v>1</v>
       </c>
       <c r="P60">
-        <v>72.1022109985352</v>
+        <v>50.2529411315918</v>
       </c>
       <c r="Q60">
-        <v>706.43310546875</v>
+        <v>711.722900390625</v>
       </c>
       <c r="R60">
-        <v>691.961669921875</v>
+        <v>708.550659179688</v>
       </c>
       <c r="S60">
-        <v>670.397583007813</v>
+        <v>694.449829101563</v>
       </c>
       <c r="T60">
-        <v>1.56146240234375</v>
+        <v>0.72857666015625</v>
       </c>
       <c r="U60">
-        <v>0.83282470703125</v>
+        <v>3.3885498046875</v>
       </c>
       <c r="V60">
-        <v>6.40869140625</v>
+        <v>7.69000244140625</v>
       </c>
     </row>
     <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="2">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B61">
-        <v>12.7025756835938</v>
+        <v>0.1451416015625</v>
       </c>
       <c r="C61">
-        <v>18.71240234375</v>
+        <v>0.3658447265625</v>
       </c>
       <c r="D61">
-        <v>21.1535034179688</v>
+        <v>9.87542724609375</v>
       </c>
       <c r="E61">
-        <v>699.919982910156</v>
+        <v>705.289978027344</v>
       </c>
       <c r="F61">
-        <v>711.22998046875</v>
+        <v>713.150024414063</v>
       </c>
       <c r="G61">
-        <v>699.5</v>
+        <v>703.789978027344</v>
       </c>
       <c r="H61">
-        <v>711.22998046875</v>
+        <v>713.150024414063</v>
       </c>
       <c r="I61">
-        <v>711.517028808594</v>
+        <v>716.50341796875</v>
       </c>
       <c r="J61">
-        <v>705.886596679688</v>
+        <v>709.490905761719</v>
       </c>
       <c r="K61">
-        <v>44320400</v>
+        <v>36779200</v>
       </c>
       <c r="L61">
-        <v>2.95475840568542</v>
+        <v>2.55238270759583</v>
       </c>
       <c r="M61">
-        <v>14.3873682022095</v>
+        <v>22.7627124786377</v>
       </c>
       <c r="N61">
-        <v>-47.2159576416016</v>
+        <v>-7.18874406814575</v>
       </c>
       <c r="O61" t="s">
         <v>1</v>
       </c>
       <c r="P61">
-        <v>88.1968688964844</v>
+        <v>56.4056205749512</v>
       </c>
       <c r="Q61">
-        <v>699.804077148438</v>
+        <v>709.273071289063</v>
       </c>
       <c r="R61">
-        <v>685.7802734375</v>
+        <v>706.804809570313</v>
       </c>
       <c r="S61">
-        <v>665.220947265625</v>
+        <v>691.875183105469</v>
       </c>
       <c r="T61">
-        <v>0.28704833984375</v>
+        <v>3.3533935546875</v>
       </c>
       <c r="U61">
-        <v>6.3865966796875</v>
+        <v>5.700927734375</v>
       </c>
       <c r="V61">
-        <v>5.63043212890625</v>
+        <v>7.01251220703125</v>
       </c>
     </row>
     <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="2">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B62">
-        <v>9.004638671875</v>
+        <v>-6.26214599609375</v>
       </c>
       <c r="C62">
-        <v>14.4951782226563</v>
+        <v>-0.5784912109375</v>
       </c>
       <c r="D62">
-        <v>17.3780517578125</v>
+        <v>11.0665283203125</v>
       </c>
       <c r="E62">
-        <v>696.580017089844</v>
+        <v>699.809997558594</v>
       </c>
       <c r="F62">
-        <v>701.239990234375</v>
+        <v>706.489990234375</v>
       </c>
       <c r="G62">
-        <v>691.77001953125</v>
+        <v>695.25</v>
       </c>
       <c r="H62">
-        <v>694.940002441406</v>
+        <v>701.530029296875</v>
       </c>
       <c r="I62">
-        <v>697.951477050781</v>
+        <v>707.353698730469</v>
       </c>
       <c r="J62">
-        <v>691.369689941406</v>
+        <v>696.877746582031</v>
       </c>
       <c r="K62">
-        <v>43779000</v>
+        <v>46827500</v>
       </c>
       <c r="L62">
-        <v>2.6190447807312</v>
+        <v>1.98381114006042</v>
       </c>
       <c r="M62">
-        <v>27.2570400238037</v>
+        <v>24.5258102416992</v>
       </c>
       <c r="N62">
-        <v>3.84556341171265</v>
+        <v>2.26992583274841</v>
       </c>
       <c r="O62" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P62">
-        <v>35.6822090148926</v>
+        <v>-31.003755569458</v>
       </c>
       <c r="Q62">
-        <v>690.051330566406</v>
+        <v>705.485595703125</v>
       </c>
       <c r="R62">
-        <v>678.704833984375</v>
+        <v>704.908386230469</v>
       </c>
       <c r="S62">
-        <v>659.928588867188</v>
+        <v>689.250915527344</v>
       </c>
       <c r="T62">
-        <v>-3.28851318359375</v>
+        <v>0.86370849609375</v>
       </c>
       <c r="U62">
-        <v>-0.40032958984375</v>
+        <v>1.62774658203125</v>
       </c>
       <c r="V62">
-        <v>6.581787109375</v>
+        <v>10.4759521484375</v>
       </c>
     </row>
     <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="2">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B63">
-        <v>10.6896362304688</v>
+        <v>-3.43994140625</v>
       </c>
       <c r="C63">
-        <v>13.9320068359375</v>
+        <v>4.18682861328125</v>
       </c>
       <c r="D63">
-        <v>16.2178955078125</v>
+        <v>15.6046142578125</v>
       </c>
       <c r="E63">
-        <v>687.780029296875</v>
+        <v>711.539978027344</v>
       </c>
       <c r="F63">
-        <v>695.929992675781</v>
+        <v>712.070007324219</v>
       </c>
       <c r="G63">
-        <v>686.47998046875</v>
+        <v>698.849975585938</v>
       </c>
       <c r="H63">
-        <v>695.77001953125</v>
+        <v>705.880004882813</v>
       </c>
       <c r="I63">
-        <v>695.783569335938</v>
+        <v>710.798767089844</v>
       </c>
       <c r="J63">
-        <v>691.690246582031</v>
+        <v>700.581359863281</v>
       </c>
       <c r="K63">
-        <v>38778400</v>
+        <v>49834500</v>
       </c>
       <c r="L63">
-        <v>2.57237887382507</v>
+        <v>1.84238111972809</v>
       </c>
       <c r="M63">
-        <v>26.2476692199707</v>
+        <v>23.9814491271973</v>
       </c>
       <c r="N63">
-        <v>-13.2630796432495</v>
+        <v>62.2379379272461</v>
       </c>
       <c r="O63" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P63">
-        <v>92.3367462158203</v>
+        <v>-50.4282302856445</v>
       </c>
       <c r="Q63">
-        <v>685.352661132813</v>
+        <v>709.042114257813</v>
       </c>
       <c r="R63">
-        <v>673.965087890625</v>
+        <v>705.54296875</v>
       </c>
       <c r="S63">
-        <v>655.84326171875</v>
+        <v>687.760314941406</v>
       </c>
       <c r="T63">
-        <v>-0.14642333984375</v>
+        <v>-1.271240234375</v>
       </c>
       <c r="U63">
-        <v>5.21026611328125</v>
+        <v>1.73138427734375</v>
       </c>
       <c r="V63">
-        <v>4.09332275390625</v>
+        <v>10.2174072265625</v>
       </c>
     </row>
     <row r="64" ht="19.5" customHeight="1">
       <c r="A64" s="2">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B64">
-        <v>6.93927001953125</v>
+        <v>-0.6888427734375</v>
       </c>
       <c r="C64">
-        <v>9.5572509765625</v>
+        <v>9.64984130859375</v>
       </c>
       <c r="D64">
-        <v>12.9378662109375</v>
+        <v>19.1634521484375</v>
       </c>
       <c r="E64">
-        <v>677.960021972656</v>
+        <v>710.140014648438</v>
       </c>
       <c r="F64">
-        <v>682.773376464844</v>
+        <v>715.130004882813</v>
       </c>
       <c r="G64">
-        <v>677.510009765625</v>
+        <v>705.549987792969</v>
       </c>
       <c r="H64">
-        <v>681.609985351563</v>
+        <v>708.929992675781</v>
       </c>
       <c r="I64">
-        <v>684.007507324219</v>
+        <v>713.73095703125</v>
       </c>
       <c r="J64">
-        <v>679.232299804688</v>
+        <v>705.546264648438</v>
       </c>
       <c r="K64">
-        <v>37101000</v>
+        <v>51792600</v>
       </c>
       <c r="L64">
-        <v>2.33238005638123</v>
+        <v>2.26713919639587</v>
       </c>
       <c r="M64">
-        <v>30.2612419128418</v>
+        <v>14.7816534042358</v>
       </c>
       <c r="N64">
-        <v>-6.39617967605591</v>
+        <v>17.9724540710449</v>
       </c>
       <c r="O64" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P64">
-        <v>49.00048828125</v>
+        <v>-41.642879486084</v>
       </c>
       <c r="Q64">
-        <v>676.280883789063</v>
+        <v>712.332336425781</v>
       </c>
       <c r="R64">
-        <v>667.738586425781</v>
+        <v>705.323608398438</v>
       </c>
       <c r="S64">
-        <v>651.146240234375</v>
+        <v>685.609130859375</v>
       </c>
       <c r="T64">
-        <v>1.234130859375</v>
+        <v>-1.3990478515625</v>
       </c>
       <c r="U64">
-        <v>1.7222900390625</v>
+        <v>-0.00372314453125</v>
       </c>
       <c r="V64">
-        <v>4.77520751953125</v>
+        <v>8.1846923828125</v>
       </c>
     </row>
     <row r="65" ht="19.5" customHeight="1">
       <c r="A65" s="2">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B65">
-        <v>5.57098388671875</v>
+        <v>4.2469482421875</v>
       </c>
       <c r="C65">
-        <v>8.4202880859375</v>
+        <v>14.796142578125</v>
       </c>
       <c r="D65">
-        <v>12.0945434570313</v>
+        <v>22.1717529296875</v>
       </c>
       <c r="E65">
-        <v>674.659973144531</v>
+        <v>714.619995117188</v>
       </c>
       <c r="F65">
-        <v>676.72998046875</v>
+        <v>722.030029296875</v>
       </c>
       <c r="G65">
-        <v>668.900024414063</v>
+        <v>714.219970703125</v>
       </c>
       <c r="H65">
-        <v>672.880004882813</v>
+        <v>719.789978027344</v>
       </c>
       <c r="I65">
-        <v>675.945739746094</v>
+        <v>723.651184082031</v>
       </c>
       <c r="J65">
-        <v>669.984497070313</v>
+        <v>717.320251464844</v>
       </c>
       <c r="K65">
-        <v>34541900</v>
+        <v>33327500</v>
       </c>
       <c r="L65">
-        <v>2.26666831970215</v>
+        <v>2.38475680351257</v>
       </c>
       <c r="M65">
-        <v>32.3290672302246</v>
+        <v>12.5297498703003</v>
       </c>
       <c r="N65">
-        <v>48.4614944458008</v>
+        <v>-18.7818870544434</v>
       </c>
       <c r="O65" t="s">
         <v>1</v>
       </c>
       <c r="P65">
+        <v>63.4685020446777</v>
+      </c>
+      <c r="Q65">
+        <v>715.2548828125</v>
+      </c>
+      <c r="R65">
+        <v>704.195434570313</v>
+      </c>
+      <c r="S65">
+        <v>682.877746582031</v>
+      </c>
+      <c r="T65">
+        <v>1.62115478515625</v>
+      </c>
+      <c r="U65">
+        <v>3.10028076171875</v>
+      </c>
+      <c r="V65">
+        <v>6.3309326171875</v>
+      </c>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B66">
+        <v>3.7032470703125</v>
+      </c>
+      <c r="C66">
+        <v>15.423828125</v>
+      </c>
+      <c r="D66">
+        <v>22.1091918945313</v>
+      </c>
+      <c r="E66">
+        <v>709.960021972656</v>
+      </c>
+      <c r="F66">
+        <v>716.650024414063</v>
+      </c>
+      <c r="G66">
+        <v>704.830017089844</v>
+      </c>
+      <c r="H66">
+        <v>714.710021972656</v>
+      </c>
+      <c r="I66">
+        <v>718.768737792969</v>
+      </c>
+      <c r="J66">
+        <v>709.555847167969</v>
+      </c>
+      <c r="K66">
+        <v>40012500</v>
+      </c>
+      <c r="L66">
+        <v>2.5347580909729</v>
+      </c>
+      <c r="M66">
+        <v>15.427285194397</v>
+      </c>
+      <c r="N66">
+        <v>1.57026052474976</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>24.8097915649414</v>
+      </c>
+      <c r="Q66">
+        <v>710.250854492188</v>
+      </c>
+      <c r="R66">
+        <v>699.560852050781</v>
+      </c>
+      <c r="S66">
+        <v>678.413146972656</v>
+      </c>
+      <c r="T66">
+        <v>2.11871337890625</v>
+      </c>
+      <c r="U66">
+        <v>4.725830078125</v>
+      </c>
+      <c r="V66">
+        <v>9.212890625</v>
+      </c>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="A67" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B67">
+        <v>2.77252197265625</v>
+      </c>
+      <c r="C67">
+        <v>16.5220336914063</v>
+      </c>
+      <c r="D67">
+        <v>21.4488525390625</v>
+      </c>
+      <c r="E67">
+        <v>708.219970703125</v>
+      </c>
+      <c r="F67">
+        <v>710.179992675781</v>
+      </c>
+      <c r="G67">
+        <v>696.640014648438</v>
+      </c>
+      <c r="H67">
+        <v>707.239990234375</v>
+      </c>
+      <c r="I67">
+        <v>709.478881835938</v>
+      </c>
+      <c r="J67">
+        <v>700.918579101563</v>
+      </c>
+      <c r="K67">
+        <v>45873000</v>
+      </c>
+      <c r="L67">
+        <v>2.7076153755188</v>
+      </c>
+      <c r="M67">
+        <v>15.1887817382813</v>
+      </c>
+      <c r="N67">
+        <v>2.39614534378052</v>
+      </c>
+      <c r="O67" t="s">
+        <v>23</v>
+      </c>
+      <c r="P67">
+        <v>-41.1354179382324</v>
+      </c>
+      <c r="Q67">
+        <v>706.15283203125</v>
+      </c>
+      <c r="R67">
+        <v>695.097351074219</v>
+      </c>
+      <c r="S67">
+        <v>674.054138183594</v>
+      </c>
+      <c r="T67">
+        <v>-0.70111083984375</v>
+      </c>
+      <c r="U67">
+        <v>4.278564453125</v>
+      </c>
+      <c r="V67">
+        <v>8.560302734375</v>
+      </c>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B68">
+        <v>10.6698608398438</v>
+      </c>
+      <c r="C68">
+        <v>20.4730834960938</v>
+      </c>
+      <c r="D68">
+        <v>23.3697509765625</v>
+      </c>
+      <c r="E68">
+        <v>710.359985351563</v>
+      </c>
+      <c r="F68">
+        <v>714.590026855469</v>
+      </c>
+      <c r="G68">
+        <v>708.909973144531</v>
+      </c>
+      <c r="H68">
+        <v>713.289978027344</v>
+      </c>
+      <c r="I68">
+        <v>716.151489257813</v>
+      </c>
+      <c r="J68">
+        <v>709.742797851563</v>
+      </c>
+      <c r="K68">
+        <v>36019100</v>
+      </c>
+      <c r="L68">
+        <v>3.1309494972229</v>
+      </c>
+      <c r="M68">
+        <v>14.8333530426025</v>
+      </c>
+      <c r="N68">
+        <v>3.09983611106873</v>
+      </c>
+      <c r="O68" t="s">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>72.1022109985352</v>
+      </c>
+      <c r="Q68">
+        <v>706.43310546875</v>
+      </c>
+      <c r="R68">
+        <v>691.961669921875</v>
+      </c>
+      <c r="S68">
+        <v>670.397583007813</v>
+      </c>
+      <c r="T68">
+        <v>1.56146240234375</v>
+      </c>
+      <c r="U68">
+        <v>0.83282470703125</v>
+      </c>
+      <c r="V68">
+        <v>6.40869140625</v>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B69">
+        <v>12.7025756835938</v>
+      </c>
+      <c r="C69">
+        <v>18.71240234375</v>
+      </c>
+      <c r="D69">
+        <v>21.1535034179688</v>
+      </c>
+      <c r="E69">
+        <v>699.919982910156</v>
+      </c>
+      <c r="F69">
+        <v>711.22998046875</v>
+      </c>
+      <c r="G69">
+        <v>699.5</v>
+      </c>
+      <c r="H69">
+        <v>711.22998046875</v>
+      </c>
+      <c r="I69">
+        <v>711.517028808594</v>
+      </c>
+      <c r="J69">
+        <v>705.886596679688</v>
+      </c>
+      <c r="K69">
+        <v>44320400</v>
+      </c>
+      <c r="L69">
+        <v>2.95475840568542</v>
+      </c>
+      <c r="M69">
+        <v>14.3873682022095</v>
+      </c>
+      <c r="N69">
+        <v>-47.2159576416016</v>
+      </c>
+      <c r="O69" t="s">
+        <v>1</v>
+      </c>
+      <c r="P69">
+        <v>88.1968688964844</v>
+      </c>
+      <c r="Q69">
+        <v>699.804077148438</v>
+      </c>
+      <c r="R69">
+        <v>685.7802734375</v>
+      </c>
+      <c r="S69">
+        <v>665.220947265625</v>
+      </c>
+      <c r="T69">
+        <v>0.28704833984375</v>
+      </c>
+      <c r="U69">
+        <v>6.3865966796875</v>
+      </c>
+      <c r="V69">
+        <v>5.63043212890625</v>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="2">
+        <v>46149</v>
+      </c>
+      <c r="B70">
+        <v>9.004638671875</v>
+      </c>
+      <c r="C70">
+        <v>14.4951782226563</v>
+      </c>
+      <c r="D70">
+        <v>17.3780517578125</v>
+      </c>
+      <c r="E70">
+        <v>696.580017089844</v>
+      </c>
+      <c r="F70">
+        <v>701.239990234375</v>
+      </c>
+      <c r="G70">
+        <v>691.77001953125</v>
+      </c>
+      <c r="H70">
+        <v>694.940002441406</v>
+      </c>
+      <c r="I70">
+        <v>697.951477050781</v>
+      </c>
+      <c r="J70">
+        <v>691.369689941406</v>
+      </c>
+      <c r="K70">
+        <v>43779000</v>
+      </c>
+      <c r="L70">
+        <v>2.6190447807312</v>
+      </c>
+      <c r="M70">
+        <v>27.2570400238037</v>
+      </c>
+      <c r="N70">
+        <v>3.84556341171265</v>
+      </c>
+      <c r="O70" t="s">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>35.6822090148926</v>
+      </c>
+      <c r="Q70">
+        <v>690.051330566406</v>
+      </c>
+      <c r="R70">
+        <v>678.704833984375</v>
+      </c>
+      <c r="S70">
+        <v>659.928588867188</v>
+      </c>
+      <c r="T70">
+        <v>-3.28851318359375</v>
+      </c>
+      <c r="U70">
+        <v>-0.40032958984375</v>
+      </c>
+      <c r="V70">
+        <v>6.581787109375</v>
+      </c>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="A71" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B71">
+        <v>10.6896362304688</v>
+      </c>
+      <c r="C71">
+        <v>13.9320068359375</v>
+      </c>
+      <c r="D71">
+        <v>16.2178955078125</v>
+      </c>
+      <c r="E71">
+        <v>687.780029296875</v>
+      </c>
+      <c r="F71">
+        <v>695.929992675781</v>
+      </c>
+      <c r="G71">
+        <v>686.47998046875</v>
+      </c>
+      <c r="H71">
+        <v>695.77001953125</v>
+      </c>
+      <c r="I71">
+        <v>695.783569335938</v>
+      </c>
+      <c r="J71">
+        <v>691.690246582031</v>
+      </c>
+      <c r="K71">
+        <v>38778400</v>
+      </c>
+      <c r="L71">
+        <v>2.57237887382507</v>
+      </c>
+      <c r="M71">
+        <v>26.2476692199707</v>
+      </c>
+      <c r="N71">
+        <v>-13.2630796432495</v>
+      </c>
+      <c r="O71" t="s">
+        <v>1</v>
+      </c>
+      <c r="P71">
+        <v>92.3367462158203</v>
+      </c>
+      <c r="Q71">
+        <v>685.352661132813</v>
+      </c>
+      <c r="R71">
+        <v>673.965087890625</v>
+      </c>
+      <c r="S71">
+        <v>655.84326171875</v>
+      </c>
+      <c r="T71">
+        <v>-0.14642333984375</v>
+      </c>
+      <c r="U71">
+        <v>5.21026611328125</v>
+      </c>
+      <c r="V71">
+        <v>4.09332275390625</v>
+      </c>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="2">
+        <v>46147</v>
+      </c>
+      <c r="B72">
+        <v>6.93927001953125</v>
+      </c>
+      <c r="C72">
+        <v>9.5572509765625</v>
+      </c>
+      <c r="D72">
+        <v>12.9378662109375</v>
+      </c>
+      <c r="E72">
+        <v>677.960021972656</v>
+      </c>
+      <c r="F72">
+        <v>682.773376464844</v>
+      </c>
+      <c r="G72">
+        <v>677.510009765625</v>
+      </c>
+      <c r="H72">
+        <v>681.609985351563</v>
+      </c>
+      <c r="I72">
+        <v>684.007507324219</v>
+      </c>
+      <c r="J72">
+        <v>679.232299804688</v>
+      </c>
+      <c r="K72">
+        <v>37101000</v>
+      </c>
+      <c r="L72">
+        <v>2.33238005638123</v>
+      </c>
+      <c r="M72">
+        <v>30.2612419128418</v>
+      </c>
+      <c r="N72">
+        <v>-6.39617967605591</v>
+      </c>
+      <c r="O72" t="s">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>49.00048828125</v>
+      </c>
+      <c r="Q72">
+        <v>676.280883789063</v>
+      </c>
+      <c r="R72">
+        <v>667.738586425781</v>
+      </c>
+      <c r="S72">
+        <v>651.146240234375</v>
+      </c>
+      <c r="T72">
+        <v>1.234130859375</v>
+      </c>
+      <c r="U72">
+        <v>1.7222900390625</v>
+      </c>
+      <c r="V72">
+        <v>4.77520751953125</v>
+      </c>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
+      <c r="A73" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B73">
+        <v>5.57098388671875</v>
+      </c>
+      <c r="C73">
+        <v>8.4202880859375</v>
+      </c>
+      <c r="D73">
+        <v>12.0945434570313</v>
+      </c>
+      <c r="E73">
+        <v>674.659973144531</v>
+      </c>
+      <c r="F73">
+        <v>676.72998046875</v>
+      </c>
+      <c r="G73">
+        <v>668.900024414063</v>
+      </c>
+      <c r="H73">
+        <v>672.880004882813</v>
+      </c>
+      <c r="I73">
+        <v>675.945739746094</v>
+      </c>
+      <c r="J73">
+        <v>669.984497070313</v>
+      </c>
+      <c r="K73">
+        <v>34541900</v>
+      </c>
+      <c r="L73">
+        <v>2.26666831970215</v>
+      </c>
+      <c r="M73">
+        <v>32.3290672302246</v>
+      </c>
+      <c r="N73">
+        <v>48.4614944458008</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1</v>
+      </c>
+      <c r="P73">
         <v>19.435884475708</v>
       </c>
-      <c r="Q65">
+      <c r="Q73">
         <v>670.946899414063</v>
       </c>
-      <c r="R65">
+      <c r="R73">
         <v>663.71630859375</v>
       </c>
-      <c r="S65">
+      <c r="S73">
         <v>647.596252441406</v>
       </c>
-      <c r="T65">
+      <c r="T73">
         <v>-0.78424072265625</v>
       </c>
-      <c r="U65">
+      <c r="U73">
         <v>1.08447265625</v>
       </c>
-      <c r="V65">
+      <c r="V73">
         <v>5.96124267578125</v>
+      </c>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="A74" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B74">
+        <v>6.1273193359375</v>
+      </c>
+      <c r="C74">
+        <v>9.0289306640625</v>
+      </c>
+      <c r="D74">
+        <v>13.4712524414063</v>
+      </c>
+      <c r="E74">
+        <v>669.159973144531</v>
+      </c>
+      <c r="F74">
+        <v>675.969970703125</v>
+      </c>
+      <c r="G74">
+        <v>668.799987792969</v>
+      </c>
+      <c r="H74">
+        <v>674.150024414063</v>
+      </c>
+      <c r="I74">
+        <v>677.464965820313</v>
+      </c>
+      <c r="J74">
+        <v>671.490234375</v>
+      </c>
+      <c r="K74">
+        <v>39172600</v>
+      </c>
+      <c r="L74">
+        <v>2.87571501731873</v>
+      </c>
+      <c r="M74">
+        <v>21.7760620117188</v>
+      </c>
+      <c r="N74">
+        <v>14.8360757827759</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1</v>
+      </c>
+      <c r="P74">
+        <v>54.8995056152344</v>
+      </c>
+      <c r="Q74">
+        <v>668.959167480469</v>
+      </c>
+      <c r="R74">
+        <v>661.122253417969</v>
+      </c>
+      <c r="S74">
+        <v>644.647705078125</v>
+      </c>
+      <c r="T74">
+        <v>1.4949951171875</v>
+      </c>
+      <c r="U74">
+        <v>2.69024658203125</v>
+      </c>
+      <c r="V74">
+        <v>5.9747314453125</v>
+      </c>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="A75" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B75">
+        <v>1.79058837890625</v>
+      </c>
+      <c r="C75">
+        <v>6.85638427734375</v>
+      </c>
+      <c r="D75">
+        <v>13.5128784179688</v>
+      </c>
+      <c r="E75">
+        <v>665.349975585938</v>
+      </c>
+      <c r="F75">
+        <v>668.900024414063</v>
+      </c>
+      <c r="G75">
+        <v>657.559997558594</v>
+      </c>
+      <c r="H75">
+        <v>667.739990234375</v>
+      </c>
+      <c r="I75">
+        <v>669.269714355469</v>
+      </c>
+      <c r="J75">
+        <v>663.364929199219</v>
+      </c>
+      <c r="K75">
+        <v>40622200</v>
+      </c>
+      <c r="L75">
+        <v>2.77285623550415</v>
+      </c>
+      <c r="M75">
+        <v>18.9627361297607</v>
+      </c>
+      <c r="N75">
+        <v>23.3116474151611</v>
+      </c>
+      <c r="O75" t="s">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>36.5470085144043</v>
+      </c>
+      <c r="Q75">
+        <v>663.541748046875</v>
+      </c>
+      <c r="R75">
+        <v>657.160400390625</v>
+      </c>
+      <c r="S75">
+        <v>641.122802734375</v>
+      </c>
+      <c r="T75">
+        <v>0.36968994140625</v>
+      </c>
+      <c r="U75">
+        <v>5.804931640625</v>
+      </c>
+      <c r="V75">
+        <v>5.90478515625</v>
+      </c>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="A76" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B76">
+        <v>1.04156494140625</v>
+      </c>
+      <c r="C76">
+        <v>6.22894287109375</v>
+      </c>
+      <c r="D76">
+        <v>14.5377197265625</v>
+      </c>
+      <c r="E76">
+        <v>658.630004882813</v>
+      </c>
+      <c r="F76">
+        <v>661.719970703125</v>
+      </c>
+      <c r="G76">
+        <v>656.589904785156</v>
+      </c>
+      <c r="H76">
+        <v>661.570007324219</v>
+      </c>
+      <c r="I76">
+        <v>664.388793945313</v>
+      </c>
+      <c r="J76">
+        <v>658.765319824219</v>
+      </c>
+      <c r="K76">
+        <v>31724800</v>
+      </c>
+      <c r="L76">
+        <v>3.27285623550415</v>
+      </c>
+      <c r="M76">
+        <v>15.3778953552246</v>
+      </c>
+      <c r="N76">
+        <v>-18.059850692749</v>
+      </c>
+      <c r="O76" t="s">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>10.946436882019</v>
+      </c>
+      <c r="Q76">
+        <v>660.288208007813</v>
+      </c>
+      <c r="R76">
+        <v>654.080627441406</v>
+      </c>
+      <c r="S76">
+        <v>638.112609863281</v>
+      </c>
+      <c r="T76">
+        <v>2.6688232421875</v>
+      </c>
+      <c r="U76">
+        <v>2.1754150390625</v>
+      </c>
+      <c r="V76">
+        <v>5.62347412109375</v>
+      </c>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="A77" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B77">
+        <v>0.7283935546875</v>
+      </c>
+      <c r="C77">
+        <v>7.16204833984375</v>
+      </c>
+      <c r="D77">
+        <v>16.3717041015625</v>
+      </c>
+      <c r="E77">
+        <v>657.409973144531</v>
+      </c>
+      <c r="F77">
+        <v>659.640014648438</v>
+      </c>
+      <c r="G77">
+        <v>653.809997558594</v>
+      </c>
+      <c r="H77">
+        <v>657.549987792969</v>
+      </c>
+      <c r="I77">
+        <v>660.511840820313</v>
+      </c>
+      <c r="J77">
+        <v>654.294311523438</v>
+      </c>
+      <c r="K77">
+        <v>34147900</v>
+      </c>
+      <c r="L77">
+        <v>2.69952392578125</v>
+      </c>
+      <c r="M77">
+        <v>18.7672290802002</v>
+      </c>
+      <c r="N77">
+        <v>36.0515403747559</v>
+      </c>
+      <c r="O77" t="s">
+        <v>23</v>
+      </c>
+      <c r="P77">
+        <v>-33.8857536315918</v>
+      </c>
+      <c r="Q77">
+        <v>658.99365234375</v>
+      </c>
+      <c r="R77">
+        <v>651.902954101563</v>
+      </c>
+      <c r="S77">
+        <v>635.307250976563</v>
+      </c>
+      <c r="T77">
+        <v>0.871826171875</v>
+      </c>
+      <c r="U77">
+        <v>0.48431396484375</v>
+      </c>
+      <c r="V77">
+        <v>6.217529296875</v>
+      </c>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B78">
+        <v>6.79742431640625</v>
+      </c>
+      <c r="C78">
+        <v>10.7206420898438</v>
+      </c>
+      <c r="D78">
+        <v>20.2769165039063</v>
+      </c>
+      <c r="E78">
+        <v>663.400024414063</v>
+      </c>
+      <c r="F78">
+        <v>664.429992675781</v>
+      </c>
+      <c r="G78">
+        <v>660.690002441406</v>
+      </c>
+      <c r="H78">
+        <v>664.22998046875</v>
+      </c>
+      <c r="I78">
+        <v>666.801818847656</v>
+      </c>
+      <c r="J78">
+        <v>661.616271972656</v>
+      </c>
+      <c r="K78">
+        <v>32717000</v>
+      </c>
+      <c r="L78">
+        <v>2.30095267295837</v>
+      </c>
+      <c r="M78">
+        <v>13.7942056655884</v>
+      </c>
+      <c r="N78">
+        <v>-35.9787635803223</v>
+      </c>
+      <c r="O78" t="s">
+        <v>1</v>
+      </c>
+      <c r="P78">
+        <v>39.8378639221191</v>
+      </c>
+      <c r="Q78">
+        <v>660.523315429688</v>
+      </c>
+      <c r="R78">
+        <v>650.454040527344</v>
+      </c>
+      <c r="S78">
+        <v>632.769226074219</v>
+      </c>
+      <c r="T78">
+        <v>2.371826171875</v>
+      </c>
+      <c r="U78">
+        <v>0.92626953125</v>
+      </c>
+      <c r="V78">
+        <v>5.185546875</v>
+      </c>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B79">
+        <v>7.03436279296875</v>
+      </c>
+      <c r="C79">
+        <v>11.798095703125</v>
+      </c>
+      <c r="D79">
+        <v>21.4058227539063</v>
+      </c>
+      <c r="E79">
+        <v>658.510009765625</v>
+      </c>
+      <c r="F79">
+        <v>664.510009765625</v>
+      </c>
+      <c r="G79">
+        <v>656.530090332031</v>
+      </c>
+      <c r="H79">
+        <v>663.880004882813</v>
+      </c>
+      <c r="I79">
+        <v>666.281188964844</v>
+      </c>
+      <c r="J79">
+        <v>660.232360839844</v>
+      </c>
+      <c r="K79">
+        <v>45563000</v>
+      </c>
+      <c r="L79">
+        <v>1.84190726280212</v>
+      </c>
+      <c r="M79">
+        <v>21.5462970733643</v>
+      </c>
+      <c r="N79">
+        <v>-7.11980152130127</v>
+      </c>
+      <c r="O79" t="s">
+        <v>1</v>
+      </c>
+      <c r="P79">
+        <v>59.7641868591309</v>
+      </c>
+      <c r="Q79">
+        <v>656.826293945313</v>
+      </c>
+      <c r="R79">
+        <v>646.504333496094</v>
+      </c>
+      <c r="S79">
+        <v>629.033874511719</v>
+      </c>
+      <c r="T79">
+        <v>1.77117919921875</v>
+      </c>
+      <c r="U79">
+        <v>3.7022705078125</v>
+      </c>
+      <c r="V79">
+        <v>6.048828125</v>
+      </c>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="2">
+        <v>46135</v>
+      </c>
+      <c r="B80">
+        <v>1.7882080078125</v>
+      </c>
+      <c r="C80">
+        <v>11.3400268554688</v>
+      </c>
+      <c r="D80">
+        <v>21.3622436523438</v>
+      </c>
+      <c r="E80">
+        <v>653.549987792969</v>
+      </c>
+      <c r="F80">
+        <v>656.919982910156</v>
+      </c>
+      <c r="G80">
+        <v>645.52001953125</v>
+      </c>
+      <c r="H80">
+        <v>651.419982910156</v>
+      </c>
+      <c r="I80">
+        <v>654.339294433594</v>
+      </c>
+      <c r="J80">
+        <v>646.905456542969</v>
+      </c>
+      <c r="K80">
+        <v>40099800</v>
+      </c>
+      <c r="L80">
+        <v>1.52333581447601</v>
+      </c>
+      <c r="M80">
+        <v>23.1979446411133</v>
+      </c>
+      <c r="N80">
+        <v>29.6571006774902</v>
+      </c>
+      <c r="O80" t="s">
+        <v>1</v>
+      </c>
+      <c r="P80">
+        <v>6.74149131774902</v>
+      </c>
+      <c r="Q80">
+        <v>650.186157226563</v>
+      </c>
+      <c r="R80">
+        <v>641.589233398438</v>
+      </c>
+      <c r="S80">
+        <v>624.953247070313</v>
+      </c>
+      <c r="T80">
+        <v>-2.5806884765625</v>
+      </c>
+      <c r="U80">
+        <v>1.38543701171875</v>
+      </c>
+      <c r="V80">
+        <v>7.433837890625</v>
+      </c>
+    </row>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B81">
+        <v>4.37249755859375</v>
+      </c>
+      <c r="C81">
+        <v>13.8749389648438</v>
+      </c>
+      <c r="D81">
+        <v>23.7278442382813</v>
+      </c>
+      <c r="E81">
+        <v>650.150024414063</v>
+      </c>
+      <c r="F81">
+        <v>655.330017089844</v>
+      </c>
+      <c r="G81">
+        <v>648.52001953125</v>
+      </c>
+      <c r="H81">
+        <v>655.109985351563</v>
+      </c>
+      <c r="I81">
+        <v>656.893493652344</v>
+      </c>
+      <c r="J81">
+        <v>652.103942871094</v>
+      </c>
+      <c r="K81">
+        <v>37368400</v>
+      </c>
+      <c r="L81">
+        <v>1.58524000644684</v>
+      </c>
+      <c r="M81">
+        <v>17.8917655944824</v>
+      </c>
+      <c r="N81">
+        <v>36.6983070373535</v>
+      </c>
+      <c r="O81" t="s">
+        <v>1</v>
+      </c>
+      <c r="P81">
+        <v>45.2194404602051</v>
+      </c>
+      <c r="Q81">
+        <v>649.481323242188</v>
+      </c>
+      <c r="R81">
+        <v>638.628540039063</v>
+      </c>
+      <c r="S81">
+        <v>621.925659179688</v>
+      </c>
+      <c r="T81">
+        <v>1.5634765625</v>
+      </c>
+      <c r="U81">
+        <v>3.58392333984375</v>
+      </c>
+      <c r="V81">
+        <v>4.78955078125</v>
+      </c>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="2">
+        <v>46133</v>
+      </c>
+      <c r="B82">
+        <v>1.47247314453125</v>
+      </c>
+      <c r="C82">
+        <v>13.73583984375</v>
+      </c>
+      <c r="D82">
+        <v>24.22509765625</v>
+      </c>
+      <c r="E82">
+        <v>648.409973144531</v>
+      </c>
+      <c r="F82">
+        <v>650.200012207031</v>
+      </c>
+      <c r="G82">
+        <v>642.210021972656</v>
+      </c>
+      <c r="H82">
+        <v>644.330017089844</v>
+      </c>
+      <c r="I82">
+        <v>647.991271972656</v>
+      </c>
+      <c r="J82">
+        <v>641.484252929688</v>
+      </c>
+      <c r="K82">
+        <v>39580500</v>
+      </c>
+      <c r="L82">
+        <v>1.22905039787292</v>
+      </c>
+      <c r="M82">
+        <v>13.0885057449341</v>
+      </c>
+      <c r="N82">
+        <v>73.2676239013672</v>
+      </c>
+      <c r="O82" t="s">
+        <v>23</v>
+      </c>
+      <c r="P82">
+        <v>-8.90367984771729</v>
+      </c>
+      <c r="Q82">
+        <v>644.241577148438</v>
+      </c>
+      <c r="R82">
+        <v>633.866394042969</v>
+      </c>
+      <c r="S82">
+        <v>618.085083007813</v>
+      </c>
+      <c r="T82">
+        <v>-2.208740234375</v>
+      </c>
+      <c r="U82">
+        <v>-0.72576904296875</v>
+      </c>
+      <c r="V82">
+        <v>6.50701904296875</v>
+      </c>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B83">
+        <v>5.4947509765625</v>
+      </c>
+      <c r="C83">
+        <v>18.0436401367188</v>
+      </c>
+      <c r="D83">
+        <v>27.7374267578125</v>
+      </c>
+      <c r="E83">
+        <v>648.039978027344</v>
+      </c>
+      <c r="F83">
+        <v>648.760009765625</v>
+      </c>
+      <c r="G83">
+        <v>642.52001953125</v>
+      </c>
+      <c r="H83">
+        <v>646.789978027344</v>
+      </c>
+      <c r="I83">
+        <v>649.096313476563</v>
+      </c>
+      <c r="J83">
+        <v>643.505310058594</v>
+      </c>
+      <c r="K83">
+        <v>37138500</v>
+      </c>
+      <c r="L83">
+        <v>0.994762599468231</v>
+      </c>
+      <c r="M83">
+        <v>7.55392456054688</v>
+      </c>
+      <c r="N83" t="str">
+        <v>∞</v>
+      </c>
+      <c r="O83" t="s">
+        <v>1</v>
+      </c>
+      <c r="P83">
+        <v>14.9626502990723</v>
+      </c>
+      <c r="Q83">
+        <v>643.88232421875</v>
+      </c>
+      <c r="R83">
+        <v>630.762756347656</v>
+      </c>
+      <c r="S83">
+        <v>615.004699707031</v>
+      </c>
+      <c r="T83">
+        <v>0.3363037109375</v>
+      </c>
+      <c r="U83">
+        <v>0.98529052734375</v>
+      </c>
+      <c r="V83">
+        <v>5.59100341796875</v>
+      </c>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B84">
+        <v>10.2792358398438</v>
+      </c>
+      <c r="C84">
+        <v>20.33642578125</v>
+      </c>
+      <c r="D84">
+        <v>29.184326171875</v>
+      </c>
+      <c r="E84">
+        <v>645.590026855469</v>
+      </c>
+      <c r="F84">
+        <v>650</v>
+      </c>
+      <c r="G84">
+        <v>644.070007324219</v>
+      </c>
+      <c r="H84">
+        <v>648.849975585938</v>
+      </c>
+      <c r="I84">
+        <v>650.599853515625</v>
+      </c>
+      <c r="J84">
+        <v>646.129821777344</v>
+      </c>
+      <c r="K84">
+        <v>53488800</v>
+      </c>
+      <c r="L84">
+        <v>1.22142970561981</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>-100</v>
+      </c>
+      <c r="O84" t="s">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>57.443717956543</v>
+      </c>
+      <c r="Q84">
+        <v>641.294921875</v>
+      </c>
+      <c r="R84">
+        <v>626.195495605469</v>
+      </c>
+      <c r="S84">
+        <v>611.291931152344</v>
+      </c>
+      <c r="T84">
+        <v>0.599853515625</v>
+      </c>
+      <c r="U84">
+        <v>2.059814453125</v>
+      </c>
+      <c r="V84">
+        <v>4.47003173828125</v>
+      </c>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="2">
+        <v>46128</v>
+      </c>
+      <c r="B85">
+        <v>10.4158325195313</v>
+      </c>
+      <c r="C85">
+        <v>19.7139892578125</v>
+      </c>
+      <c r="D85">
+        <v>27.5108642578125</v>
+      </c>
+      <c r="E85">
+        <v>639.210021972656</v>
+      </c>
+      <c r="F85">
+        <v>642.179992675781</v>
+      </c>
+      <c r="G85">
+        <v>635.255004882813</v>
+      </c>
+      <c r="H85">
+        <v>640.469970703125</v>
+      </c>
+      <c r="I85">
+        <v>643.084899902344</v>
+      </c>
+      <c r="J85">
+        <v>636.8671875</v>
+      </c>
+      <c r="K85">
+        <v>42320500</v>
+      </c>
+      <c r="L85">
+        <v>0.752386212348938</v>
+      </c>
+      <c r="M85">
+        <v>2.54076743125916</v>
+      </c>
+      <c r="N85">
+        <v>-78.9348220825195</v>
+      </c>
+      <c r="O85" t="s">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>47.1683578491211</v>
+      </c>
+      <c r="Q85">
+        <v>634.064819335938</v>
+      </c>
+      <c r="R85">
+        <v>619.81298828125</v>
+      </c>
+      <c r="S85">
+        <v>606.845275878906</v>
+      </c>
+      <c r="T85">
+        <v>0.9049072265625</v>
+      </c>
+      <c r="U85">
+        <v>1.6121826171875</v>
+      </c>
+      <c r="V85">
+        <v>6.21771240234375</v>
+      </c>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B86">
+        <v>10.99462890625</v>
+      </c>
+      <c r="C86">
+        <v>19.3135986328125</v>
+      </c>
+      <c r="D86">
+        <v>24.78662109375</v>
+      </c>
+      <c r="E86">
+        <v>629.080017089844</v>
+      </c>
+      <c r="F86">
+        <v>637.830017089844</v>
+      </c>
+      <c r="G86">
+        <v>628.200012207031</v>
+      </c>
+      <c r="H86">
+        <v>637.400024414063</v>
+      </c>
+      <c r="I86">
+        <v>638.631774902344</v>
+      </c>
+      <c r="J86">
+        <v>632.78515625</v>
+      </c>
+      <c r="K86">
+        <v>50102300</v>
+      </c>
+      <c r="L86">
+        <v>0.700483024120331</v>
+      </c>
+      <c r="M86">
+        <v>12.0614595413208</v>
+      </c>
+      <c r="N86">
+        <v>-55.6365509033203</v>
+      </c>
+      <c r="O86" t="s">
+        <v>1</v>
+      </c>
+      <c r="P86">
+        <v>71.8697662353516</v>
+      </c>
+      <c r="Q86">
+        <v>627.980712890625</v>
+      </c>
+      <c r="R86">
+        <v>613.994995117188</v>
+      </c>
+      <c r="S86">
+        <v>602.761535644531</v>
+      </c>
+      <c r="T86">
+        <v>0.8017578125</v>
+      </c>
+      <c r="U86">
+        <v>4.58514404296875</v>
+      </c>
+      <c r="V86">
+        <v>5.84661865234375</v>
+      </c>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="2">
+        <v>46126</v>
+      </c>
+      <c r="B87">
+        <v>8.55841064453125</v>
+      </c>
+      <c r="C87">
+        <v>17.686767578125</v>
+      </c>
+      <c r="D87">
+        <v>21.0980834960938</v>
+      </c>
+      <c r="E87">
+        <v>620.219970703125</v>
+      </c>
+      <c r="F87">
+        <v>628.599975585938</v>
+      </c>
+      <c r="G87">
+        <v>620.099975585938</v>
+      </c>
+      <c r="H87">
+        <v>628.599975585938</v>
+      </c>
+      <c r="I87">
+        <v>631.561584472656</v>
+      </c>
+      <c r="J87">
+        <v>623.819458007813</v>
+      </c>
+      <c r="K87">
+        <v>49921000</v>
+      </c>
+      <c r="L87">
+        <v>0.320483982563019</v>
+      </c>
+      <c r="M87">
+        <v>27.1878299713135</v>
+      </c>
+      <c r="N87">
+        <v>-22.1617641448975</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1</v>
+      </c>
+      <c r="P87">
+        <v>77.5935440063477</v>
+      </c>
+      <c r="Q87">
+        <v>619.67236328125</v>
+      </c>
+      <c r="R87">
+        <v>607.568969726563</v>
+      </c>
+      <c r="S87">
+        <v>598.7236328125</v>
+      </c>
+      <c r="T87">
+        <v>2.96160888671875</v>
+      </c>
+      <c r="U87">
+        <v>3.719482421875</v>
+      </c>
+      <c r="V87">
+        <v>7.74212646484375</v>
+      </c>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B88">
+        <v>7.0267333984375</v>
+      </c>
+      <c r="C88">
+        <v>16.8212280273438</v>
+      </c>
+      <c r="D88">
+        <v>16.500732421875</v>
+      </c>
+      <c r="E88">
+        <v>609.47998046875</v>
+      </c>
+      <c r="F88">
+        <v>626.739990234375</v>
+      </c>
+      <c r="G88">
+        <v>608.109985351563</v>
+      </c>
+      <c r="H88">
+        <v>617.390014648438</v>
+      </c>
+      <c r="I88">
+        <v>618.624267578125</v>
+      </c>
+      <c r="J88">
+        <v>611.269104003906</v>
+      </c>
+      <c r="K88">
+        <v>32972100</v>
+      </c>
+      <c r="L88">
+        <v>-0.36475482583046</v>
+      </c>
+      <c r="M88">
+        <v>34.9286308288574</v>
+      </c>
+      <c r="N88">
+        <v>-16.8072910308838</v>
+      </c>
+      <c r="O88" t="s">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>27.9681758880615</v>
+      </c>
+      <c r="Q88">
+        <v>611.355529785156</v>
+      </c>
+      <c r="R88">
+        <v>601.406066894531</v>
+      </c>
+      <c r="S88">
+        <v>595.072631835938</v>
+      </c>
+      <c r="T88">
+        <v>-8.11572265625</v>
+      </c>
+      <c r="U88">
+        <v>3.15911865234375</v>
+      </c>
+      <c r="V88">
+        <v>7.35516357421875</v>
+      </c>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B89">
+        <v>8.66387939453125</v>
+      </c>
+      <c r="C89">
+        <v>17.2860107421875</v>
+      </c>
+      <c r="D89">
+        <v>13.759521484375</v>
+      </c>
+      <c r="E89">
+        <v>611.840026855469</v>
+      </c>
+      <c r="F89">
+        <v>613.669982910156</v>
+      </c>
+      <c r="G89">
+        <v>609.580017089844</v>
+      </c>
+      <c r="H89">
+        <v>611.070007324219</v>
+      </c>
+      <c r="I89">
+        <v>614.052368164063</v>
+      </c>
+      <c r="J89">
+        <v>608.650024414063</v>
+      </c>
+      <c r="K89">
+        <v>34038500</v>
+      </c>
+      <c r="L89">
+        <v>-1.0033278465271</v>
+      </c>
+      <c r="M89">
+        <v>41.9852066040039</v>
+      </c>
+      <c r="N89">
+        <v>-4.00322008132935</v>
+      </c>
+      <c r="O89" t="s">
+        <v>1</v>
+      </c>
+      <c r="P89">
+        <v>24.7126922607422</v>
+      </c>
+      <c r="Q89">
+        <v>606.960266113281</v>
+      </c>
+      <c r="R89">
+        <v>596.961547851563</v>
+      </c>
+      <c r="S89">
+        <v>592.481872558594</v>
+      </c>
+      <c r="T89">
+        <v>0.38238525390625</v>
+      </c>
+      <c r="U89">
+        <v>-0.92999267578125</v>
+      </c>
+      <c r="V89">
+        <v>5.40234375</v>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="2">
+        <v>46121</v>
+      </c>
+      <c r="B90">
+        <v>10.4630737304688</v>
+      </c>
+      <c r="C90">
+        <v>16.5682373046875</v>
+      </c>
+      <c r="D90">
+        <v>10.3148803710938</v>
+      </c>
+      <c r="E90">
+        <v>605.929992675781</v>
+      </c>
+      <c r="F90">
+        <v>610.5</v>
+      </c>
+      <c r="G90">
+        <v>603.030029296875</v>
+      </c>
+      <c r="H90">
+        <v>610.190002441406</v>
+      </c>
+      <c r="I90">
+        <v>611.073303222656</v>
+      </c>
+      <c r="J90">
+        <v>606.381469726563</v>
+      </c>
+      <c r="K90">
+        <v>37837500</v>
+      </c>
+      <c r="L90">
+        <v>-1.02666068077087</v>
+      </c>
+      <c r="M90">
+        <v>43.7360572814941</v>
+      </c>
+      <c r="N90">
+        <v>-20.2031288146973</v>
+      </c>
+      <c r="O90" t="s">
+        <v>1</v>
+      </c>
+      <c r="P90">
+        <v>59.6479415893555</v>
+      </c>
+      <c r="Q90">
+        <v>602.6767578125</v>
+      </c>
+      <c r="R90">
+        <v>592.900268554688</v>
+      </c>
+      <c r="S90">
+        <v>590.263977050781</v>
+      </c>
+      <c r="T90">
+        <v>0.57330322265625</v>
+      </c>
+      <c r="U90">
+        <v>3.3514404296875</v>
+      </c>
+      <c r="V90">
+        <v>4.69183349609375</v>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
+      <c r="A91" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B91">
+        <v>9.4776611328125</v>
+      </c>
+      <c r="C91">
+        <v>12.3314819335938</v>
+      </c>
+      <c r="D91">
+        <v>6.017578125</v>
+      </c>
+      <c r="E91">
+        <v>608.710021972656</v>
+      </c>
+      <c r="F91">
+        <v>609.900024414063</v>
+      </c>
+      <c r="G91">
+        <v>602.119995117188</v>
+      </c>
+      <c r="H91">
+        <v>606.090026855469</v>
+      </c>
+      <c r="I91">
+        <v>609.036804199219</v>
+      </c>
+      <c r="J91">
+        <v>604.196960449219</v>
+      </c>
+      <c r="K91">
+        <v>63085900</v>
+      </c>
+      <c r="L91">
+        <v>-1.22999501228333</v>
+      </c>
+      <c r="M91">
+        <v>54.8092384338379</v>
+      </c>
+      <c r="N91">
+        <v>9.53201103210449</v>
+      </c>
+      <c r="O91" t="s">
+        <v>1</v>
+      </c>
+      <c r="P91">
+        <v>100</v>
+      </c>
+      <c r="Q91">
+        <v>596.135131835938</v>
+      </c>
+      <c r="R91">
+        <v>588.070434570313</v>
+      </c>
+      <c r="S91">
+        <v>588.185424804688</v>
+      </c>
+      <c r="T91">
+        <v>-0.86322021484375</v>
+      </c>
+      <c r="U91">
+        <v>2.07696533203125</v>
+      </c>
+      <c r="V91">
+        <v>4.83984375</v>
+      </c>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="2">
+        <v>46119</v>
+      </c>
+      <c r="B92">
+        <v>2.32537841796875</v>
+      </c>
+      <c r="C92">
+        <v>5.6502685546875</v>
+      </c>
+      <c r="D92">
+        <v>-0.60986328125</v>
+      </c>
+      <c r="E92">
+        <v>585.640014648438</v>
+      </c>
+      <c r="F92">
+        <v>588.97998046875</v>
+      </c>
+      <c r="G92">
+        <v>578.400085449219</v>
+      </c>
+      <c r="H92">
+        <v>588.590026855469</v>
+      </c>
+      <c r="I92">
+        <v>590.392333984375</v>
+      </c>
+      <c r="J92">
+        <v>583.304321289063</v>
+      </c>
+      <c r="K92">
+        <v>49948100</v>
+      </c>
+      <c r="L92">
+        <v>-0.460707902908325</v>
+      </c>
+      <c r="M92">
+        <v>50.0394706726074</v>
+      </c>
+      <c r="N92">
+        <v>-14.8211450576782</v>
+      </c>
+      <c r="O92" t="s">
+        <v>1</v>
+      </c>
+      <c r="P92">
+        <v>9.68646144866943</v>
+      </c>
+      <c r="Q92">
+        <v>585.83349609375</v>
+      </c>
+      <c r="R92">
+        <v>582.721496582031</v>
+      </c>
+      <c r="S92">
+        <v>586.038208007813</v>
+      </c>
+      <c r="T92">
+        <v>1.412353515625</v>
+      </c>
+      <c r="U92">
+        <v>4.90423583984375</v>
+      </c>
+      <c r="V92">
+        <v>7.0880126953125</v>
+      </c>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B93">
+        <v>7.61083984375</v>
+      </c>
+      <c r="C93">
+        <v>3.872314453125</v>
+      </c>
+      <c r="D93">
+        <v>-3.007080078125</v>
+      </c>
+      <c r="E93">
+        <v>586.22998046875</v>
+      </c>
+      <c r="F93">
+        <v>590.609985351563</v>
+      </c>
+      <c r="G93">
+        <v>584.690002441406</v>
+      </c>
+      <c r="H93">
+        <v>588.5</v>
+      </c>
+      <c r="I93">
+        <v>593.00048828125</v>
+      </c>
+      <c r="J93">
+        <v>584.235107421875</v>
+      </c>
+      <c r="K93">
+        <v>35108400</v>
+      </c>
+      <c r="L93">
+        <v>-0.627851188182831</v>
+      </c>
+      <c r="M93">
+        <v>58.7463531494141</v>
+      </c>
+      <c r="N93">
+        <v>-3.20517110824585</v>
+      </c>
+      <c r="O93" t="s">
+        <v>1</v>
+      </c>
+      <c r="P93">
+        <v>38.3831024169922</v>
+      </c>
+      <c r="Q93">
+        <v>584.231689453125</v>
+      </c>
+      <c r="R93">
+        <v>581.388244628906</v>
+      </c>
+      <c r="S93">
+        <v>585.921752929688</v>
+      </c>
+      <c r="T93">
+        <v>2.3905029296875</v>
+      </c>
+      <c r="U93">
+        <v>-0.45489501953125</v>
+      </c>
+      <c r="V93">
+        <v>8.765380859375</v>
+      </c>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="2">
+        <v>46114</v>
+      </c>
+      <c r="B94">
+        <v>8.1578369140625</v>
+      </c>
+      <c r="C94">
+        <v>0.8564453125</v>
+      </c>
+      <c r="D94">
+        <v>-6.3797607421875</v>
+      </c>
+      <c r="E94">
+        <v>573.969970703125</v>
+      </c>
+      <c r="F94">
+        <v>586.049987792969</v>
+      </c>
+      <c r="G94">
+        <v>571.919982910156</v>
+      </c>
+      <c r="H94">
+        <v>584.97998046875</v>
+      </c>
+      <c r="I94">
+        <v>585.762145996094</v>
+      </c>
+      <c r="J94">
+        <v>577.023620605469</v>
+      </c>
+      <c r="K94">
+        <v>50941700</v>
+      </c>
+      <c r="L94">
+        <v>-0.664045035839081</v>
+      </c>
+      <c r="M94">
+        <v>60.6916236877441</v>
+      </c>
+      <c r="N94">
+        <v>-14.6080570220947</v>
+      </c>
+      <c r="O94" t="s">
+        <v>1</v>
+      </c>
+      <c r="P94">
+        <v>12.8151226043701</v>
+      </c>
+      <c r="Q94">
+        <v>579.894714355469</v>
+      </c>
+      <c r="R94">
+        <v>579.3681640625</v>
+      </c>
+      <c r="S94">
+        <v>585.555725097656</v>
+      </c>
+      <c r="T94">
+        <v>-0.287841796875</v>
+      </c>
+      <c r="U94">
+        <v>5.1036376953125</v>
+      </c>
+      <c r="V94">
+        <v>8.738525390625</v>
+      </c>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B95">
+        <v>8.46844482421875</v>
+      </c>
+      <c r="C95">
+        <v>-2.25048828125</v>
+      </c>
+      <c r="D95">
+        <v>-8.62542724609375</v>
+      </c>
+      <c r="E95">
+        <v>581.47998046875</v>
+      </c>
+      <c r="F95">
+        <v>587.739013671875</v>
+      </c>
+      <c r="G95">
+        <v>580.419982910156</v>
+      </c>
+      <c r="H95">
+        <v>584.309997558594</v>
+      </c>
+      <c r="I95">
+        <v>587.581420898438</v>
+      </c>
+      <c r="J95">
+        <v>580.318786621094</v>
+      </c>
+      <c r="K95">
+        <v>79435104</v>
+      </c>
+      <c r="L95">
+        <v>-0.874520421028137</v>
+      </c>
+      <c r="M95">
+        <v>71.0741806030273</v>
+      </c>
+      <c r="N95">
+        <v>-10.2984085083008</v>
+      </c>
+      <c r="O95" t="s">
+        <v>1</v>
+      </c>
+      <c r="P95">
+        <v>100</v>
+      </c>
+      <c r="Q95">
+        <v>577.203186035156</v>
+      </c>
+      <c r="R95">
+        <v>578.467956542969</v>
+      </c>
+      <c r="S95">
+        <v>585.986755371094</v>
+      </c>
+      <c r="T95">
+        <v>-0.1575927734375</v>
+      </c>
+      <c r="U95">
+        <v>-0.1011962890625</v>
+      </c>
+      <c r="V95">
+        <v>7.26263427734375</v>
+      </c>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="2">
+        <v>46112</v>
+      </c>
+      <c r="B96">
+        <v>-0.9837646484375</v>
+      </c>
+      <c r="C96">
+        <v>-8.33758544921875</v>
+      </c>
+      <c r="D96">
+        <v>-13.2415161132813</v>
+      </c>
+      <c r="E96">
+        <v>564.289978027344</v>
+      </c>
+      <c r="F96">
+        <v>578.640014648438</v>
+      </c>
+      <c r="G96">
+        <v>564.210021972656</v>
+      </c>
+      <c r="H96">
+        <v>577.179992675781</v>
+      </c>
+      <c r="I96">
+        <v>578.816528320313</v>
+      </c>
+      <c r="J96">
+        <v>570.715209960938</v>
+      </c>
+      <c r="K96">
+        <v>95878000</v>
+      </c>
+      <c r="L96">
+        <v>-0.759283185005188</v>
+      </c>
+      <c r="M96">
+        <v>79.2340240478516</v>
+      </c>
+      <c r="N96">
+        <v>-20.7659759521484</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>72.8060150146484</v>
+      </c>
+      <c r="Q96">
+        <v>570.344604492188</v>
+      </c>
+      <c r="R96">
+        <v>576.778625488281</v>
+      </c>
+      <c r="S96">
+        <v>586.180114746094</v>
+      </c>
+      <c r="T96">
+        <v>0.176513671875</v>
+      </c>
+      <c r="U96">
+        <v>6.50518798828125</v>
+      </c>
+      <c r="V96">
+        <v>8.101318359375</v>
+      </c>
+    </row>
+    <row r="97" ht="19.5" customHeight="1">
+      <c r="A97" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B97">
+        <v>-11.5879516601563</v>
+      </c>
+      <c r="C97">
+        <v>-14.5079345703125</v>
+      </c>
+      <c r="D97">
+        <v>-16.4674682617188</v>
+      </c>
+      <c r="E97">
+        <v>567.380004882813</v>
+      </c>
+      <c r="F97">
+        <v>568.049987792969</v>
+      </c>
+      <c r="G97">
+        <v>555.599975585938</v>
+      </c>
+      <c r="H97">
+        <v>558.280029296875</v>
+      </c>
+      <c r="I97">
+        <v>563.784790039063</v>
+      </c>
+      <c r="J97">
+        <v>553.487731933594</v>
+      </c>
+      <c r="K97">
+        <v>70602600</v>
+      </c>
+      <c r="L97">
+        <v>-0.933567583560944</v>
+      </c>
+      <c r="M97">
+        <v>100</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>23</v>
+      </c>
+      <c r="P97">
+        <v>-67.6669998168945</v>
+      </c>
+      <c r="Q97">
+        <v>565.116455078125</v>
+      </c>
+      <c r="R97">
+        <v>576.673156738281</v>
+      </c>
+      <c r="S97">
+        <v>587.265014648438</v>
+      </c>
+      <c r="T97">
+        <v>-4.26519775390625</v>
+      </c>
+      <c r="U97">
+        <v>-2.11224365234375</v>
+      </c>
+      <c r="V97">
+        <v>10.2970581054688</v>
+      </c>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="A98" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B98">
+        <v>-11.1616821289063</v>
+      </c>
+      <c r="C98">
+        <v>-12.4930419921875</v>
+      </c>
+      <c r="D98">
+        <v>-13.975341796875</v>
+      </c>
+      <c r="E98">
+        <v>570.809997558594</v>
+      </c>
+      <c r="F98">
+        <v>571.02001953125</v>
+      </c>
+      <c r="G98">
+        <v>561.570007324219</v>
+      </c>
+      <c r="H98">
+        <v>562.580017089844</v>
+      </c>
+      <c r="I98">
+        <v>568.643432617188</v>
+      </c>
+      <c r="J98">
+        <v>557.943237304688</v>
+      </c>
+      <c r="K98">
+        <v>82702200</v>
+      </c>
+      <c r="L98">
+        <v>-0.294997453689575</v>
+      </c>
+      <c r="M98">
+        <v>100</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>23</v>
+      </c>
+      <c r="P98">
+        <v>-100</v>
+      </c>
+      <c r="Q98">
+        <v>571.708740234375</v>
+      </c>
+      <c r="R98">
+        <v>581.766662597656</v>
+      </c>
+      <c r="S98">
+        <v>590.659973144531</v>
+      </c>
+      <c r="T98">
+        <v>-2.3765869140625</v>
+      </c>
+      <c r="U98">
+        <v>-3.62677001953125</v>
+      </c>
+      <c r="V98">
+        <v>10.7001953125</v>
+      </c>
+    </row>
+    <row r="99" ht="19.5" customHeight="1">
+      <c r="A99" s="2">
+        <v>46107</v>
+      </c>
+      <c r="B99">
+        <v>-5.02020263671875</v>
+      </c>
+      <c r="C99">
+        <v>-7.90576171875</v>
+      </c>
+      <c r="D99">
+        <v>-10.25732421875</v>
+      </c>
+      <c r="E99">
+        <v>582.599975585938</v>
+      </c>
+      <c r="F99">
+        <v>584.630004882813</v>
+      </c>
+      <c r="G99">
+        <v>573.429992675781</v>
+      </c>
+      <c r="H99">
+        <v>573.789978027344</v>
+      </c>
+      <c r="I99">
+        <v>578.346923828125</v>
+      </c>
+      <c r="J99">
+        <v>569.010070800781</v>
+      </c>
+      <c r="K99">
+        <v>81492096</v>
+      </c>
+      <c r="L99">
+        <v>-0.205476313829422</v>
+      </c>
+      <c r="M99">
+        <v>100</v>
+      </c>
+      <c r="N99">
+        <v>27.9781036376953</v>
+      </c>
+      <c r="O99" t="s">
+        <v>23</v>
+      </c>
+      <c r="P99">
+        <v>-100</v>
+      </c>
+      <c r="Q99">
+        <v>580.365600585938</v>
+      </c>
+      <c r="R99">
+        <v>587.105346679688</v>
+      </c>
+      <c r="S99">
+        <v>594.019104003906</v>
+      </c>
+      <c r="T99">
+        <v>-6.2830810546875</v>
+      </c>
+      <c r="U99">
+        <v>-4.419921875</v>
+      </c>
+      <c r="V99">
+        <v>9.33685302734375</v>
+      </c>
+    </row>
+    <row r="100" ht="19.5" customHeight="1">
+      <c r="A100" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B100">
+        <v>-0.07891845703125</v>
+      </c>
+      <c r="C100">
+        <v>-4.77423095703125</v>
+      </c>
+      <c r="D100">
+        <v>-8.05267333984375</v>
+      </c>
+      <c r="E100">
+        <v>589.140014648438</v>
+      </c>
+      <c r="F100">
+        <v>591.369995117188</v>
+      </c>
+      <c r="G100">
+        <v>585.690002441406</v>
+      </c>
+      <c r="H100">
+        <v>587.820007324219</v>
+      </c>
+      <c r="I100">
+        <v>590.69873046875</v>
+      </c>
+      <c r="J100">
+        <v>584.533447265625</v>
+      </c>
+      <c r="K100">
+        <v>60475400</v>
+      </c>
+      <c r="L100">
+        <v>0.481189548969269</v>
+      </c>
+      <c r="M100">
+        <v>78.1383666992188</v>
+      </c>
+      <c r="N100">
+        <v>1.90570878982544</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>10.483452796936</v>
+      </c>
+      <c r="Q100">
+        <v>587.025817871094</v>
+      </c>
+      <c r="R100">
+        <v>590.837646484375</v>
+      </c>
+      <c r="S100">
+        <v>596.479248046875</v>
+      </c>
+      <c r="T100">
+        <v>-0.6712646484375</v>
+      </c>
+      <c r="U100">
+        <v>-1.15655517578125</v>
+      </c>
+      <c r="V100">
+        <v>6.165283203125</v>
+      </c>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="A101" s="2">
+        <v>46105</v>
+      </c>
+      <c r="B101">
+        <v>-3.072021484375</v>
+      </c>
+      <c r="C101">
+        <v>-6.796142578125</v>
+      </c>
+      <c r="D101">
+        <v>-8.98480224609375</v>
+      </c>
+      <c r="E101">
+        <v>584.809997558594</v>
+      </c>
+      <c r="F101">
+        <v>587.929992675781</v>
+      </c>
+      <c r="G101">
+        <v>581.929992675781</v>
+      </c>
+      <c r="H101">
+        <v>583.97998046875</v>
+      </c>
+      <c r="I101">
+        <v>587.765441894531</v>
+      </c>
+      <c r="J101">
+        <v>580.502624511719</v>
+      </c>
+      <c r="K101">
+        <v>57750800</v>
+      </c>
+      <c r="L101">
+        <v>0.804521858692169</v>
+      </c>
+      <c r="M101">
+        <v>76.6771240234375</v>
+      </c>
+      <c r="N101">
+        <v>4.78999519348145</v>
+      </c>
+      <c r="O101" t="s">
+        <v>23</v>
+      </c>
+      <c r="P101">
+        <v>-11.4117641448975</v>
+      </c>
+      <c r="Q101">
+        <v>586.368286132813</v>
+      </c>
+      <c r="R101">
+        <v>591.758422851563</v>
+      </c>
+      <c r="S101">
+        <v>597.509460449219</v>
+      </c>
+      <c r="T101">
+        <v>-0.16455078125</v>
+      </c>
+      <c r="U101">
+        <v>-1.4273681640625</v>
+      </c>
+      <c r="V101">
+        <v>7.2628173828125</v>
+      </c>
+    </row>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B102">
+        <v>-4.4617919921875</v>
+      </c>
+      <c r="C102">
+        <v>-6.875732421875</v>
+      </c>
+      <c r="D102">
+        <v>-7.85919189453125</v>
+      </c>
+      <c r="E102">
+        <v>590.52001953125</v>
+      </c>
+      <c r="F102">
+        <v>595.080017089844</v>
+      </c>
+      <c r="G102">
+        <v>585.960021972656</v>
+      </c>
+      <c r="H102">
+        <v>588</v>
+      </c>
+      <c r="I102">
+        <v>592.959594726563</v>
+      </c>
+      <c r="J102">
+        <v>585.150817871094</v>
+      </c>
+      <c r="K102">
+        <v>89936096</v>
+      </c>
+      <c r="L102">
+        <v>0.596903502941132</v>
+      </c>
+      <c r="M102">
+        <v>73.1721801757813</v>
+      </c>
+      <c r="N102">
+        <v>18.1049270629883</v>
+      </c>
+      <c r="O102" t="s">
+        <v>1</v>
+      </c>
+      <c r="P102">
+        <v>6.22351598739624</v>
+      </c>
+      <c r="Q102">
+        <v>588.650634765625</v>
+      </c>
+      <c r="R102">
+        <v>593.893920898438</v>
+      </c>
+      <c r="S102">
+        <v>599.146240234375</v>
+      </c>
+      <c r="T102">
+        <v>-2.12042236328125</v>
+      </c>
+      <c r="U102">
+        <v>-0.8092041015625</v>
+      </c>
+      <c r="V102">
+        <v>7.80877685546875</v>
+      </c>
+    </row>
+    <row r="103" ht="19.5" customHeight="1">
+      <c r="A103" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B103">
+        <v>-8.74755859375</v>
+      </c>
+      <c r="C103">
+        <v>-7.90264892578125</v>
+      </c>
+      <c r="D103">
+        <v>-7.92803955078125</v>
+      </c>
+      <c r="E103">
+        <v>591.059997558594</v>
+      </c>
+      <c r="F103">
+        <v>591.169982910156</v>
+      </c>
+      <c r="G103">
+        <v>578.539978027344</v>
+      </c>
+      <c r="H103">
+        <v>582.059997558594</v>
+      </c>
+      <c r="I103">
+        <v>587.389038085938</v>
+      </c>
+      <c r="J103">
+        <v>576.735656738281</v>
+      </c>
+      <c r="K103">
+        <v>91964600</v>
+      </c>
+      <c r="L103">
+        <v>1.13071405887604</v>
+      </c>
+      <c r="M103">
+        <v>61.9552307128906</v>
+      </c>
+      <c r="N103">
+        <v>39.9198112487793</v>
+      </c>
+      <c r="O103" t="s">
+        <v>23</v>
+      </c>
+      <c r="P103">
+        <v>-89.0887069702148</v>
+      </c>
+      <c r="Q103">
+        <v>588.592895507813</v>
+      </c>
+      <c r="R103">
+        <v>595.440246582031</v>
+      </c>
+      <c r="S103">
+        <v>600.366516113281</v>
+      </c>
+      <c r="T103">
+        <v>-3.78094482421875</v>
+      </c>
+      <c r="U103">
+        <v>-1.8043212890625</v>
+      </c>
+      <c r="V103">
+        <v>10.6533813476563</v>
+      </c>
+    </row>
+    <row r="104" ht="19.5" customHeight="1">
+      <c r="A104" s="2">
+        <v>46100</v>
+      </c>
+      <c r="B104">
+        <v>-3.22943115234375</v>
+      </c>
+      <c r="C104">
+        <v>-4.10040283203125</v>
+      </c>
+      <c r="D104">
+        <v>-5.2415771484375</v>
+      </c>
+      <c r="E104">
+        <v>589.510009765625</v>
+      </c>
+      <c r="F104">
+        <v>595.799987792969</v>
+      </c>
+      <c r="G104">
+        <v>587.080017089844</v>
+      </c>
+      <c r="H104">
+        <v>593.02001953125</v>
+      </c>
+      <c r="I104">
+        <v>596.09130859375</v>
+      </c>
+      <c r="J104">
+        <v>587.52880859375</v>
+      </c>
+      <c r="K104">
+        <v>75597504</v>
+      </c>
+      <c r="L104">
+        <v>1.59071278572083</v>
+      </c>
+      <c r="M104">
+        <v>44.2790985107422</v>
+      </c>
+      <c r="N104">
+        <v>17.5172424316406</v>
+      </c>
+      <c r="O104" t="s">
+        <v>23</v>
+      </c>
+      <c r="P104">
+        <v>-58.9277153015137</v>
+      </c>
+      <c r="Q104">
+        <v>595.13232421875</v>
+      </c>
+      <c r="R104">
+        <v>599.120544433594</v>
+      </c>
+      <c r="S104">
+        <v>602.500244140625</v>
+      </c>
+      <c r="T104">
+        <v>0.29132080078125</v>
+      </c>
+      <c r="U104">
+        <v>0.44879150390625</v>
+      </c>
+      <c r="V104">
+        <v>8.5625</v>
+      </c>
+    </row>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B105">
+        <v>-0.83233642578125</v>
+      </c>
+      <c r="C105">
+        <v>-3.1614990234375</v>
+      </c>
+      <c r="D105">
+        <v>-4.36083984375</v>
+      </c>
+      <c r="E105">
+        <v>601.489990234375</v>
+      </c>
+      <c r="F105">
+        <v>603.159973144531</v>
+      </c>
+      <c r="G105">
+        <v>594.559997558594</v>
+      </c>
+      <c r="H105">
+        <v>594.900024414063</v>
+      </c>
+      <c r="I105">
+        <v>598.179748535156</v>
+      </c>
+      <c r="J105">
+        <v>590.862060546875</v>
+      </c>
+      <c r="K105">
+        <v>56127900</v>
+      </c>
+      <c r="L105">
+        <v>1.59880721569061</v>
+      </c>
+      <c r="M105">
+        <v>37.6788101196289</v>
+      </c>
+      <c r="N105">
+        <v>56.3617248535156</v>
+      </c>
+      <c r="O105" t="s">
+        <v>23</v>
+      </c>
+      <c r="P105">
+        <v>-49.392406463623</v>
+      </c>
+      <c r="Q105">
+        <v>598.053466796875</v>
+      </c>
+      <c r="R105">
+        <v>600.962890625</v>
+      </c>
+      <c r="S105">
+        <v>603.624938964844</v>
+      </c>
+      <c r="T105">
+        <v>-4.980224609375</v>
+      </c>
+      <c r="U105">
+        <v>-3.69793701171875</v>
+      </c>
+      <c r="V105">
+        <v>7.31768798828125</v>
+      </c>
+    </row>
+    <row r="106" ht="19.5" customHeight="1">
+      <c r="A106" s="2">
+        <v>46098</v>
+      </c>
+      <c r="B106">
+        <v>1.47601318359375</v>
+      </c>
+      <c r="C106">
+        <v>-1.9788818359375</v>
+      </c>
+      <c r="D106">
+        <v>-3.63250732421875</v>
+      </c>
+      <c r="E106">
+        <v>603.140014648438</v>
+      </c>
+      <c r="F106">
+        <v>605.900024414063</v>
+      </c>
+      <c r="G106">
+        <v>601.869995117188</v>
+      </c>
+      <c r="H106">
+        <v>603.309997558594</v>
+      </c>
+      <c r="I106">
+        <v>605.331604003906</v>
+      </c>
+      <c r="J106">
+        <v>600.914245605469</v>
+      </c>
+      <c r="K106">
+        <v>47106600</v>
+      </c>
+      <c r="L106">
+        <v>2.0516619682312</v>
+      </c>
+      <c r="M106">
+        <v>24.0972080230713</v>
+      </c>
+      <c r="N106">
+        <v>-27.737325668335</v>
+      </c>
+      <c r="O106" t="s">
+        <v>1</v>
+      </c>
+      <c r="P106">
+        <v>45.7941589355469</v>
+      </c>
+      <c r="Q106">
+        <v>601.450073242188</v>
+      </c>
+      <c r="R106">
+        <v>602.713195800781</v>
+      </c>
+      <c r="S106">
+        <v>604.767333984375</v>
+      </c>
+      <c r="T106">
+        <v>-0.56842041015625</v>
+      </c>
+      <c r="U106">
+        <v>-0.95574951171875</v>
+      </c>
+      <c r="V106">
+        <v>4.4173583984375</v>
+      </c>
+    </row>
+    <row r="107" ht="19.5" customHeight="1">
+      <c r="A107" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B107">
+        <v>-1.88677978515625</v>
+      </c>
+      <c r="C107">
+        <v>-2.9676513671875</v>
+      </c>
+      <c r="D107">
+        <v>-4.3924560546875</v>
+      </c>
+      <c r="E107">
+        <v>600.039978027344</v>
+      </c>
+      <c r="F107">
+        <v>603.859985351563</v>
+      </c>
+      <c r="G107">
+        <v>599.109985351563</v>
+      </c>
+      <c r="H107">
+        <v>600.380004882813</v>
+      </c>
+      <c r="I107">
+        <v>604.193298339844</v>
+      </c>
+      <c r="J107">
+        <v>598.251770019531</v>
+      </c>
+      <c r="K107">
+        <v>49077100</v>
+      </c>
+      <c r="L107">
+        <v>2.11451935768127</v>
+      </c>
+      <c r="M107">
+        <v>33.3466873168945</v>
+      </c>
+      <c r="N107">
+        <v>23.6528778076172</v>
+      </c>
+      <c r="O107" t="s">
+        <v>1</v>
+      </c>
+      <c r="P107">
+        <v>36.7083129882813</v>
+      </c>
+      <c r="Q107">
+        <v>599.720581054688</v>
+      </c>
+      <c r="R107">
+        <v>602.531311035156</v>
+      </c>
+      <c r="S107">
+        <v>604.991027832031</v>
+      </c>
+      <c r="T107">
+        <v>0.33331298828125</v>
+      </c>
+      <c r="U107">
+        <v>-0.85821533203125</v>
+      </c>
+      <c r="V107">
+        <v>5.9415283203125</v>
+      </c>
+    </row>
+    <row r="108" ht="19.5" customHeight="1">
+      <c r="A108" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B108">
+        <v>-6.2906494140625</v>
+      </c>
+      <c r="C108">
+        <v>-4.3099365234375</v>
+      </c>
+      <c r="D108">
+        <v>-4.50537109375</v>
+      </c>
+      <c r="E108">
+        <v>599.72998046875</v>
+      </c>
+      <c r="F108">
+        <v>603.599914550781</v>
+      </c>
+      <c r="G108">
+        <v>592.570007324219</v>
+      </c>
+      <c r="H108">
+        <v>593.719970703125</v>
+      </c>
+      <c r="I108">
+        <v>598.737670898438</v>
+      </c>
+      <c r="J108">
+        <v>590.017272949219</v>
+      </c>
+      <c r="K108">
+        <v>63145400</v>
+      </c>
+      <c r="L108">
+        <v>1.42832732200623</v>
+      </c>
+      <c r="M108">
+        <v>26.9679832458496</v>
+      </c>
+      <c r="N108">
+        <v>108.110664367676</v>
+      </c>
+      <c r="O108" t="s">
+        <v>23</v>
+      </c>
+      <c r="P108">
+        <v>-68.1894226074219</v>
+      </c>
+      <c r="Q108">
+        <v>598.499633789063</v>
+      </c>
+      <c r="R108">
+        <v>602.82861328125</v>
+      </c>
+      <c r="S108">
+        <v>605.39111328125</v>
+      </c>
+      <c r="T108">
+        <v>-4.86224365234375</v>
+      </c>
+      <c r="U108">
+        <v>-2.552734375</v>
+      </c>
+      <c r="V108">
+        <v>8.72039794921875</v>
+      </c>
+    </row>
+    <row r="109" ht="19.5" customHeight="1">
+      <c r="A109" s="2">
+        <v>46093</v>
+      </c>
+      <c r="B109">
+        <v>-2.71917724609375</v>
+      </c>
+      <c r="C109">
+        <v>-2.031982421875</v>
+      </c>
+      <c r="D109">
+        <v>-2.4580078125</v>
+      </c>
+      <c r="E109">
+        <v>602.760009765625</v>
+      </c>
+      <c r="F109">
+        <v>604.140014648438</v>
+      </c>
+      <c r="G109">
+        <v>597.049987792969</v>
+      </c>
+      <c r="H109">
+        <v>597.260009765625</v>
+      </c>
+      <c r="I109">
+        <v>602.464965820313</v>
+      </c>
+      <c r="J109">
+        <v>593.995727539063</v>
+      </c>
+      <c r="K109">
+        <v>71836600</v>
+      </c>
+      <c r="L109">
+        <v>1.55880296230316</v>
+      </c>
+      <c r="M109">
+        <v>12.9584817886353</v>
+      </c>
+      <c r="N109">
+        <v>5.27650356292725</v>
+      </c>
+      <c r="O109" t="s">
+        <v>23</v>
+      </c>
+      <c r="P109">
+        <v>-75.1064453125</v>
+      </c>
+      <c r="Q109">
+        <v>602.84228515625</v>
+      </c>
+      <c r="R109">
+        <v>605.212097167969</v>
+      </c>
+      <c r="S109">
+        <v>606.760559082031</v>
+      </c>
+      <c r="T109">
+        <v>-1.675048828125</v>
+      </c>
+      <c r="U109">
+        <v>-3.05426025390625</v>
+      </c>
+      <c r="V109">
+        <v>8.46923828125</v>
+      </c>
+    </row>
+    <row r="110" ht="19.5" customHeight="1">
+      <c r="A110" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B110">
+        <v>1.79345703125</v>
+      </c>
+      <c r="C110">
+        <v>0.50250244140625</v>
+      </c>
+      <c r="D110">
+        <v>-0.02239990234375</v>
+      </c>
+      <c r="E110">
+        <v>608.950012207031</v>
+      </c>
+      <c r="F110">
+        <v>612.429992675781</v>
+      </c>
+      <c r="G110">
+        <v>605.030029296875</v>
+      </c>
+      <c r="H110">
+        <v>607.690002441406</v>
+      </c>
+      <c r="I110">
+        <v>611.635070800781</v>
+      </c>
+      <c r="J110">
+        <v>605.768981933594</v>
+      </c>
+      <c r="K110">
+        <v>60114800</v>
+      </c>
+      <c r="L110">
+        <v>1.63808763027191</v>
+      </c>
+      <c r="M110">
+        <v>12.3089971542358</v>
+      </c>
+      <c r="N110">
+        <v>548.756103515625</v>
+      </c>
+      <c r="O110" t="s">
+        <v>1</v>
+      </c>
+      <c r="P110">
+        <v>9.48142051696777</v>
+      </c>
+      <c r="Q110">
+        <v>607.785278320313</v>
+      </c>
+      <c r="R110">
+        <v>607.242858886719</v>
+      </c>
+      <c r="S110">
+        <v>607.89599609375</v>
+      </c>
+      <c r="T110">
+        <v>-0.794921875</v>
+      </c>
+      <c r="U110">
+        <v>0.73895263671875</v>
+      </c>
+      <c r="V110">
+        <v>5.8660888671875</v>
+      </c>
+    </row>
+    <row r="111" ht="19.5" customHeight="1">
+      <c r="A111" s="2">
+        <v>46091</v>
+      </c>
+      <c r="B111">
+        <v>0.79107666015625</v>
+      </c>
+      <c r="C111">
+        <v>-0.33258056640625</v>
+      </c>
+      <c r="D111">
+        <v>0.225830078125</v>
+      </c>
+      <c r="E111">
+        <v>607.780029296875</v>
+      </c>
+      <c r="F111">
+        <v>613.289978027344</v>
+      </c>
+      <c r="G111">
+        <v>605.419982910156</v>
+      </c>
+      <c r="H111">
+        <v>607.77001953125</v>
+      </c>
+      <c r="I111">
+        <v>614.615173339844</v>
+      </c>
+      <c r="J111">
+        <v>605.000793457031</v>
+      </c>
+      <c r="K111">
+        <v>64078800</v>
+      </c>
+      <c r="L111">
+        <v>2.02094674110413</v>
+      </c>
+      <c r="M111">
+        <v>1.89732277393341</v>
+      </c>
+      <c r="N111" t="str">
+        <v>∞</v>
+      </c>
+      <c r="O111" t="s">
+        <v>1</v>
+      </c>
+      <c r="P111">
+        <v>57.551643371582</v>
+      </c>
+      <c r="Q111">
+        <v>607.196960449219</v>
+      </c>
+      <c r="R111">
+        <v>607.176208496094</v>
+      </c>
+      <c r="S111">
+        <v>608.05322265625</v>
+      </c>
+      <c r="T111">
+        <v>1.3251953125</v>
+      </c>
+      <c r="U111">
+        <v>-0.419189453125</v>
+      </c>
+      <c r="V111">
+        <v>9.6143798828125</v>
+      </c>
+    </row>
+    <row r="112" ht="19.5" customHeight="1">
+      <c r="A112" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B112">
+        <v>-0.66949462890625</v>
+      </c>
+      <c r="C112">
+        <v>-1.72601318359375</v>
+      </c>
+      <c r="D112">
+        <v>-0.22894287109375</v>
+      </c>
+      <c r="E112">
+        <v>594.224975585938</v>
+      </c>
+      <c r="F112">
+        <v>609.27001953125</v>
+      </c>
+      <c r="G112">
+        <v>591.330017089844</v>
+      </c>
+      <c r="H112">
+        <v>607.760009765625</v>
+      </c>
+      <c r="I112">
+        <v>609.79541015625</v>
+      </c>
+      <c r="J112">
+        <v>600.0810546875</v>
+      </c>
+      <c r="K112">
+        <v>93068096</v>
+      </c>
+      <c r="L112">
+        <v>2.47190046310425</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>-100</v>
+      </c>
+      <c r="O112" t="s">
+        <v>1</v>
+      </c>
+      <c r="P112">
+        <v>9.5173454284668</v>
+      </c>
+      <c r="Q112">
+        <v>605.259887695313</v>
+      </c>
+      <c r="R112">
+        <v>606.543762207031</v>
+      </c>
+      <c r="S112">
+        <v>607.882141113281</v>
+      </c>
+      <c r="T112">
+        <v>0.525390625</v>
+      </c>
+      <c r="U112">
+        <v>8.75103759765625</v>
+      </c>
+      <c r="V112">
+        <v>9.71435546875</v>
+      </c>
+    </row>
+    <row r="113" ht="19.5" customHeight="1">
+      <c r="A113" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B113">
+        <v>-2.3287353515625</v>
+      </c>
+      <c r="C113">
+        <v>-1.9178466796875</v>
+      </c>
+      <c r="D113">
+        <v>-0.6436767578125</v>
+      </c>
+      <c r="E113">
+        <v>600.309997558594</v>
+      </c>
+      <c r="F113">
+        <v>606</v>
+      </c>
+      <c r="G113">
+        <v>598.330017089844</v>
+      </c>
+      <c r="H113">
+        <v>599.75</v>
+      </c>
+      <c r="I113">
+        <v>605.804016113281</v>
+      </c>
+      <c r="J113">
+        <v>596.746765136719</v>
+      </c>
+      <c r="K113">
+        <v>86582152</v>
+      </c>
+      <c r="L113">
+        <v>1.67594695091248</v>
+      </c>
+      <c r="M113">
+        <v>6.43833494186401</v>
+      </c>
+      <c r="N113">
+        <v>231.666488647461</v>
+      </c>
+      <c r="O113" t="s">
+        <v>23</v>
+      </c>
+      <c r="P113">
+        <v>-63.1181983947754</v>
+      </c>
+      <c r="Q113">
+        <v>604.646484375</v>
+      </c>
+      <c r="R113">
+        <v>606.3681640625</v>
+      </c>
+      <c r="S113">
+        <v>607.842468261719</v>
+      </c>
+      <c r="T113">
+        <v>-0.19598388671875</v>
+      </c>
+      <c r="U113">
+        <v>-1.583251953125</v>
+      </c>
+      <c r="V113">
+        <v>9.0572509765625</v>
+      </c>
+    </row>
+    <row r="114" ht="19.5" customHeight="1">
+      <c r="A114" s="2">
+        <v>46086</v>
+      </c>
+      <c r="B114">
+        <v>1.5999755859375</v>
+      </c>
+      <c r="C114">
+        <v>0.41265869140625</v>
+      </c>
+      <c r="D114">
+        <v>1.49920654296875</v>
+      </c>
+      <c r="E114">
+        <v>607.400024414063</v>
+      </c>
+      <c r="F114">
+        <v>612.760009765625</v>
+      </c>
+      <c r="G114">
+        <v>602.260009765625</v>
+      </c>
+      <c r="H114">
+        <v>608.909973144531</v>
+      </c>
+      <c r="I114">
+        <v>612.934875488281</v>
+      </c>
+      <c r="J114">
+        <v>605.246154785156</v>
+      </c>
+      <c r="K114">
+        <v>89602400</v>
+      </c>
+      <c r="L114">
+        <v>1.26118397712708</v>
+      </c>
+      <c r="M114">
+        <v>1.94120764732361</v>
+      </c>
+      <c r="N114">
+        <v>8.71268081665039</v>
+      </c>
+      <c r="O114" t="s">
+        <v>1</v>
+      </c>
+      <c r="P114">
+        <v>19.199670791626</v>
+      </c>
+      <c r="Q114">
+        <v>608.522216796875</v>
+      </c>
+      <c r="R114">
+        <v>608.115112304688</v>
+      </c>
+      <c r="S114">
+        <v>608.756164550781</v>
+      </c>
+      <c r="T114">
+        <v>0.17486572265625</v>
+      </c>
+      <c r="U114">
+        <v>2.98614501953125</v>
+      </c>
+      <c r="V114">
+        <v>7.688720703125</v>
+      </c>
+    </row>
+    <row r="115" ht="19.5" customHeight="1">
+      <c r="A115" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B115">
+        <v>1.31866455078125</v>
+      </c>
+      <c r="C115">
+        <v>0.44085693359375</v>
+      </c>
+      <c r="D115">
+        <v>0.82806396484375</v>
+      </c>
+      <c r="E115">
+        <v>604.159973144531</v>
+      </c>
+      <c r="F115">
+        <v>612.880004882813</v>
+      </c>
+      <c r="G115">
+        <v>603.429992675781</v>
+      </c>
+      <c r="H115">
+        <v>610.75</v>
+      </c>
+      <c r="I115">
+        <v>615.350280761719</v>
+      </c>
+      <c r="J115">
+        <v>607.825317382813</v>
+      </c>
+      <c r="K115">
+        <v>70943800</v>
+      </c>
+      <c r="L115">
+        <v>0.628330767154694</v>
+      </c>
+      <c r="M115">
+        <v>1.78563129901886</v>
+      </c>
+      <c r="N115">
+        <v>-93.9775543212891</v>
+      </c>
+      <c r="O115" t="s">
+        <v>1</v>
+      </c>
+      <c r="P115">
+        <v>49.0849723815918</v>
+      </c>
+      <c r="Q115">
+        <v>608.01611328125</v>
+      </c>
+      <c r="R115">
+        <v>607.777770996094</v>
+      </c>
+      <c r="S115">
+        <v>608.749145507813</v>
+      </c>
+      <c r="T115">
+        <v>2.47027587890625</v>
+      </c>
+      <c r="U115">
+        <v>4.39532470703125</v>
+      </c>
+      <c r="V115">
+        <v>7.52496337890625</v>
+      </c>
+    </row>
+    <row r="116" ht="19.5" customHeight="1">
+      <c r="A116" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B116">
+        <v>-5.06451416015625</v>
+      </c>
+      <c r="C116">
+        <v>-1.15374755859375</v>
+      </c>
+      <c r="D116">
+        <v>-0.720458984375</v>
+      </c>
+      <c r="E116">
+        <v>596.330017089844</v>
+      </c>
+      <c r="F116">
+        <v>603.960021972656</v>
+      </c>
+      <c r="G116">
+        <v>591.869995117188</v>
+      </c>
+      <c r="H116">
+        <v>601.580017089844</v>
+      </c>
+      <c r="I116">
+        <v>606.635620117188</v>
+      </c>
+      <c r="J116">
+        <v>596.072570800781</v>
+      </c>
+      <c r="K116">
+        <v>97015504</v>
+      </c>
+      <c r="L116">
+        <v>0.668805778026581</v>
+      </c>
+      <c r="M116">
+        <v>29.6496028900146</v>
+      </c>
+      <c r="N116">
+        <v>-24.9869384765625</v>
+      </c>
+      <c r="O116" t="s">
+        <v>23</v>
+      </c>
+      <c r="P116">
+        <v>-38.0903396606445</v>
+      </c>
+      <c r="Q116">
+        <v>604.71875</v>
+      </c>
+      <c r="R116">
+        <v>606.854370117188</v>
+      </c>
+      <c r="S116">
+        <v>608.471435546875</v>
+      </c>
+      <c r="T116">
+        <v>2.67559814453125</v>
+      </c>
+      <c r="U116">
+        <v>4.20257568359375</v>
+      </c>
+      <c r="V116">
+        <v>10.5630493164063</v>
+      </c>
+    </row>
+    <row r="117" ht="19.5" customHeight="1">
+      <c r="A117" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B117">
+        <v>-2.15997314453125</v>
+      </c>
+      <c r="C117">
+        <v>1.4659423828125</v>
+      </c>
+      <c r="D117">
+        <v>0.3807373046875</v>
+      </c>
+      <c r="E117">
+        <v>598.859985351563</v>
+      </c>
+      <c r="F117">
+        <v>609.919982910156</v>
+      </c>
+      <c r="G117">
+        <v>597.989990234375</v>
+      </c>
+      <c r="H117">
+        <v>608.090026855469</v>
+      </c>
+      <c r="I117">
+        <v>611.037658691406</v>
+      </c>
+      <c r="J117">
+        <v>602.824035644531</v>
+      </c>
+      <c r="K117">
+        <v>75264600</v>
+      </c>
+      <c r="L117">
+        <v>0.235947385430336</v>
+      </c>
+      <c r="M117">
+        <v>39.5259208679199</v>
+      </c>
+      <c r="N117">
+        <v>-30.274829864502</v>
+      </c>
+      <c r="O117" t="s">
+        <v>23</v>
+      </c>
+      <c r="P117">
+        <v>-6.55408477783203</v>
+      </c>
+      <c r="Q117">
+        <v>608.009399414063</v>
+      </c>
+      <c r="R117">
+        <v>608.254638671875</v>
+      </c>
+      <c r="S117">
+        <v>609.335510253906</v>
+      </c>
+      <c r="T117">
+        <v>1.11767578125</v>
+      </c>
+      <c r="U117">
+        <v>4.83404541015625</v>
+      </c>
+      <c r="V117">
+        <v>8.213623046875</v>
+      </c>
+    </row>
+    <row r="118" ht="19.5" customHeight="1">
+      <c r="A118" s="2">
+        <v>46080</v>
+      </c>
+      <c r="B118">
+        <v>-0.1092529296875</v>
+      </c>
+      <c r="C118">
+        <v>2.3741455078125</v>
+      </c>
+      <c r="D118">
+        <v>0.637939453125</v>
+      </c>
+      <c r="E118">
+        <v>602.97998046875</v>
+      </c>
+      <c r="F118">
+        <v>608.320007324219</v>
+      </c>
+      <c r="G118">
+        <v>602.190002441406</v>
+      </c>
+      <c r="H118">
+        <v>607.289978027344</v>
+      </c>
+      <c r="I118">
+        <v>611.761108398438</v>
+      </c>
+      <c r="J118">
+        <v>603.360107421875</v>
+      </c>
+      <c r="K118">
+        <v>68125104</v>
+      </c>
+      <c r="L118">
+        <v>-0.356913238763809</v>
+      </c>
+      <c r="M118">
+        <v>56.6881675720215</v>
+      </c>
+      <c r="N118">
+        <v>6.14164590835571</v>
+      </c>
+      <c r="O118" t="s">
+        <v>23</v>
+      </c>
+      <c r="P118">
+        <v>-27.6758441925049</v>
+      </c>
+      <c r="Q118">
+        <v>608.700561523438</v>
+      </c>
+      <c r="R118">
+        <v>608.312133789063</v>
+      </c>
+      <c r="S118">
+        <v>609.571350097656</v>
+      </c>
+      <c r="T118">
+        <v>3.44110107421875</v>
+      </c>
+      <c r="U118">
+        <v>1.17010498046875</v>
+      </c>
+      <c r="V118">
+        <v>8.4010009765625</v>
+      </c>
+    </row>
+    <row r="119" ht="19.5" customHeight="1">
+      <c r="A119" s="2">
+        <v>46079</v>
+      </c>
+      <c r="B119">
+        <v>1.42108154296875</v>
+      </c>
+      <c r="C119">
+        <v>3.98968505859375</v>
+      </c>
+      <c r="D119">
+        <v>1.944580078125</v>
+      </c>
+      <c r="E119">
+        <v>615.590026855469</v>
+      </c>
+      <c r="F119">
+        <v>615.590026855469</v>
+      </c>
+      <c r="G119">
+        <v>603.97998046875</v>
+      </c>
+      <c r="H119">
+        <v>609.239990234375</v>
+      </c>
+      <c r="I119">
+        <v>612.52392578125</v>
+      </c>
+      <c r="J119">
+        <v>604.668334960938</v>
+      </c>
+      <c r="K119">
+        <v>96178800</v>
+      </c>
+      <c r="L119">
+        <v>-0.668820321559906</v>
+      </c>
+      <c r="M119">
+        <v>53.4080352783203</v>
+      </c>
+      <c r="N119">
+        <v>63.3723983764648</v>
+      </c>
+      <c r="O119" t="s">
+        <v>23</v>
+      </c>
+      <c r="P119">
+        <v>-16.7778186798096</v>
+      </c>
+      <c r="Q119">
+        <v>609.942016601563</v>
+      </c>
+      <c r="R119">
+        <v>608.568237304688</v>
+      </c>
+      <c r="S119">
+        <v>609.8642578125</v>
+      </c>
+      <c r="T119">
+        <v>-3.06610107421875</v>
+      </c>
+      <c r="U119">
+        <v>0.6883544921875</v>
+      </c>
+      <c r="V119">
+        <v>7.8555908203125</v>
+      </c>
+    </row>
+    <row r="120" ht="19.5" customHeight="1">
+      <c r="A120" s="2">
+        <v>46078</v>
+      </c>
+      <c r="B120">
+        <v>5.400390625</v>
+      </c>
+      <c r="C120">
+        <v>4.06561279296875</v>
+      </c>
+      <c r="D120">
+        <v>2.2808837890625</v>
+      </c>
+      <c r="E120">
+        <v>611.070007324219</v>
+      </c>
+      <c r="F120">
+        <v>616.830017089844</v>
+      </c>
+      <c r="G120">
+        <v>611</v>
+      </c>
+      <c r="H120">
+        <v>616.679992675781</v>
+      </c>
+      <c r="I120">
+        <v>619.286560058594</v>
+      </c>
+      <c r="J120">
+        <v>613.666259765625</v>
+      </c>
+      <c r="K120">
+        <v>55710600</v>
+      </c>
+      <c r="L120">
+        <v>-0.260721832513809</v>
+      </c>
+      <c r="M120">
+        <v>32.6909790039063</v>
+      </c>
+      <c r="N120">
+        <v>-26.4129314422607</v>
+      </c>
+      <c r="O120" t="s">
+        <v>1</v>
+      </c>
+      <c r="P120">
+        <v>77.9614715576172</v>
+      </c>
+      <c r="Q120">
+        <v>611.073120117188</v>
+      </c>
+      <c r="R120">
+        <v>608.434020996094</v>
+      </c>
+      <c r="S120">
+        <v>610.082885742188</v>
+      </c>
+      <c r="T120">
+        <v>2.45654296875</v>
+      </c>
+      <c r="U120">
+        <v>2.666259765625</v>
+      </c>
+      <c r="V120">
+        <v>5.62030029296875</v>
+      </c>
+    </row>
+    <row r="121" ht="19.5" customHeight="1">
+      <c r="A121" s="2">
+        <v>46077</v>
+      </c>
+      <c r="B121">
+        <v>0.58624267578125</v>
+      </c>
+      <c r="C121">
+        <v>-0.08331298828125</v>
+      </c>
+      <c r="D121">
+        <v>-1.04461669921875</v>
+      </c>
+      <c r="E121">
+        <v>602.400024414063</v>
+      </c>
+      <c r="F121">
+        <v>608.989990234375</v>
+      </c>
+      <c r="G121">
+        <v>599.72998046875</v>
+      </c>
+      <c r="H121">
+        <v>607.869995117188</v>
+      </c>
+      <c r="I121">
+        <v>610.628540039063</v>
+      </c>
+      <c r="J121">
+        <v>603.7783203125</v>
+      </c>
+      <c r="K121">
+        <v>55023700</v>
+      </c>
+      <c r="L121">
+        <v>-0.420721143484116</v>
+      </c>
+      <c r="M121">
+        <v>44.4248962402344</v>
+      </c>
+      <c r="N121">
+        <v>-29.6697235107422</v>
+      </c>
+      <c r="O121" t="s">
+        <v>1</v>
+      </c>
+      <c r="P121">
+        <v>19.3525829315186</v>
+      </c>
+      <c r="Q121">
+        <v>605.603149414063</v>
+      </c>
+      <c r="R121">
+        <v>605.946960449219</v>
+      </c>
+      <c r="S121">
+        <v>609.231811523438</v>
+      </c>
+      <c r="T121">
+        <v>1.6385498046875</v>
+      </c>
+      <c r="U121">
+        <v>4.04833984375</v>
+      </c>
+      <c r="V121">
+        <v>6.8502197265625</v>
+      </c>
+    </row>
+    <row r="122" ht="19.5" customHeight="1">
+      <c r="A122" s="2">
+        <v>46076</v>
+      </c>
+      <c r="B122">
+        <v>-0.8330078125</v>
+      </c>
+      <c r="C122">
+        <v>-1.9947509765625</v>
+      </c>
+      <c r="D122">
+        <v>-3.0865478515625</v>
+      </c>
+      <c r="E122">
+        <v>606.599975585938</v>
+      </c>
+      <c r="F122">
+        <v>608.010009765625</v>
+      </c>
+      <c r="G122">
+        <v>599.049987792969</v>
+      </c>
+      <c r="H122">
+        <v>601.409973144531</v>
+      </c>
+      <c r="I122">
+        <v>606.655639648438</v>
+      </c>
+      <c r="J122">
+        <v>597.361145019531</v>
+      </c>
+      <c r="K122">
+        <v>63859100</v>
+      </c>
+      <c r="L122">
+        <v>-0.538815438747406</v>
+      </c>
+      <c r="M122">
+        <v>63.1661033630371</v>
+      </c>
+      <c r="N122">
+        <v>-10.2559614181519</v>
+      </c>
+      <c r="O122" t="s">
+        <v>23</v>
+      </c>
+      <c r="P122">
+        <v>-21.0234394073486</v>
+      </c>
+      <c r="Q122">
+        <v>603.776245117188</v>
+      </c>
+      <c r="R122">
+        <v>605.504089355469</v>
+      </c>
+      <c r="S122">
+        <v>609.43017578125</v>
+      </c>
+      <c r="T122">
+        <v>-1.3543701171875</v>
+      </c>
+      <c r="U122">
+        <v>-1.6888427734375</v>
+      </c>
+      <c r="V122">
+        <v>9.29449462890625</v>
+      </c>
+    </row>
+    <row r="123" ht="19.5" customHeight="1">
+      <c r="A123" s="2">
+        <v>46073</v>
+      </c>
+      <c r="B123">
+        <v>2.0927734375</v>
+      </c>
+      <c r="C123">
+        <v>-1.32574462890625</v>
+      </c>
+      <c r="D123">
+        <v>-3.35784912109375</v>
+      </c>
+      <c r="E123">
+        <v>600.119995117188</v>
+      </c>
+      <c r="F123">
+        <v>610.349975585938</v>
+      </c>
+      <c r="G123">
+        <v>599.22998046875</v>
+      </c>
+      <c r="H123">
+        <v>608.809997558594</v>
+      </c>
+      <c r="I123">
+        <v>610.50732421875</v>
+      </c>
+      <c r="J123">
+        <v>603.380065917969</v>
+      </c>
+      <c r="K123">
+        <v>74127296</v>
+      </c>
+      <c r="L123">
+        <v>-0.367385149002075</v>
+      </c>
+      <c r="M123">
+        <v>70.3847351074219</v>
+      </c>
+      <c r="N123">
+        <v>-2.18664574623108</v>
+      </c>
+      <c r="O123" t="s">
+        <v>1</v>
+      </c>
+      <c r="P123">
+        <v>19.6417331695557</v>
+      </c>
+      <c r="Q123">
+        <v>605.733032226563</v>
+      </c>
+      <c r="R123">
+        <v>606.467041015625</v>
+      </c>
+      <c r="S123">
+        <v>610.366882324219</v>
+      </c>
+      <c r="T123">
+        <v>0.1573486328125</v>
+      </c>
+      <c r="U123">
+        <v>4.15008544921875</v>
+      </c>
+      <c r="V123">
+        <v>7.12725830078125</v>
+      </c>
+    </row>
+    <row r="124" ht="19.5" customHeight="1">
+      <c r="A124" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B124">
+        <v>1.2972412109375</v>
+      </c>
+      <c r="C124">
+        <v>-1.770751953125</v>
+      </c>
+      <c r="D124">
+        <v>-5.62994384765625</v>
+      </c>
+      <c r="E124">
+        <v>602.809997558594</v>
+      </c>
+      <c r="F124">
+        <v>605.815002441406</v>
+      </c>
+      <c r="G124">
+        <v>600.75</v>
+      </c>
+      <c r="H124">
+        <v>603.469970703125</v>
+      </c>
+      <c r="I124">
+        <v>607.241943359375</v>
+      </c>
+      <c r="J124">
+        <v>600.407653808594</v>
+      </c>
+      <c r="K124">
+        <v>60960800</v>
+      </c>
+      <c r="L124">
+        <v>-0.456906259059906</v>
+      </c>
+      <c r="M124">
+        <v>71.9582061767578</v>
+      </c>
+      <c r="N124">
+        <v>-5.97121334075928</v>
+      </c>
+      <c r="O124" t="s">
+        <v>1</v>
+      </c>
+      <c r="P124">
+        <v>5.60849332809448</v>
+      </c>
+      <c r="Q124">
+        <v>603.908081054688</v>
+      </c>
+      <c r="R124">
+        <v>606.029296875</v>
+      </c>
+      <c r="S124">
+        <v>610.654113769531</v>
+      </c>
+      <c r="T124">
+        <v>1.42694091796875</v>
+      </c>
+      <c r="U124">
+        <v>-0.34234619140625</v>
+      </c>
+      <c r="V124">
+        <v>6.83428955078125</v>
+      </c>
+    </row>
+    <row r="125" ht="19.5" customHeight="1">
+      <c r="A125" s="2">
+        <v>46071</v>
+      </c>
+      <c r="B125">
+        <v>-0.203369140625</v>
+      </c>
+      <c r="C125">
+        <v>-1.44842529296875</v>
+      </c>
+      <c r="D125">
+        <v>-6.87493896484375</v>
+      </c>
+      <c r="E125">
+        <v>602.109985351563</v>
+      </c>
+      <c r="F125">
+        <v>609.77099609375</v>
+      </c>
+      <c r="G125">
+        <v>600.719970703125</v>
+      </c>
+      <c r="H125">
+        <v>605.789978027344</v>
+      </c>
+      <c r="I125">
+        <v>609.841613769531</v>
+      </c>
+      <c r="J125">
+        <v>601.817504882813</v>
+      </c>
+      <c r="K125">
+        <v>64250600</v>
+      </c>
+      <c r="L125">
+        <v>-0.605954110622406</v>
+      </c>
+      <c r="M125">
+        <v>76.5278472900391</v>
+      </c>
+      <c r="N125">
+        <v>-8.02982711791992</v>
+      </c>
+      <c r="O125" t="s">
+        <v>1</v>
+      </c>
+      <c r="P125">
+        <v>31.4861221313477</v>
+      </c>
+      <c r="Q125">
+        <v>604.11962890625</v>
+      </c>
+      <c r="R125">
+        <v>606.823425292969</v>
+      </c>
+      <c r="S125">
+        <v>611.538391113281</v>
+      </c>
+      <c r="T125">
+        <v>0.07061767578125</v>
+      </c>
+      <c r="U125">
+        <v>1.0975341796875</v>
+      </c>
+      <c r="V125">
+        <v>8.02410888671875</v>
+      </c>
+    </row>
+    <row r="126" ht="19.5" customHeight="1">
+      <c r="A126" s="2">
+        <v>46070</v>
+      </c>
+      <c r="B126">
+        <v>-4.27978515625</v>
+      </c>
+      <c r="C126">
+        <v>-3.29583740234375</v>
+      </c>
+      <c r="D126">
+        <v>-8.69677734375</v>
+      </c>
+      <c r="E126">
+        <v>598.380004882813</v>
+      </c>
+      <c r="F126">
+        <v>603.950012207031</v>
+      </c>
+      <c r="G126">
+        <v>593.340026855469</v>
+      </c>
+      <c r="H126">
+        <v>601.299987792969</v>
+      </c>
+      <c r="I126">
+        <v>605.134582519531</v>
+      </c>
+      <c r="J126">
+        <v>595.617492675781</v>
+      </c>
+      <c r="K126">
+        <v>69013696</v>
+      </c>
+      <c r="L126">
+        <v>-0.983096182346344</v>
+      </c>
+      <c r="M126">
+        <v>83.2094192504883</v>
+      </c>
+      <c r="N126">
+        <v>-7.39178514480591</v>
+      </c>
+      <c r="O126" t="s">
+        <v>23</v>
+      </c>
+      <c r="P126">
+        <v>-8.04475975036621</v>
+      </c>
+      <c r="Q126">
+        <v>602.432312011719</v>
+      </c>
+      <c r="R126">
+        <v>607.093994140625</v>
+      </c>
+      <c r="S126">
+        <v>612.188293457031</v>
+      </c>
+      <c r="T126">
+        <v>1.1845703125</v>
+      </c>
+      <c r="U126">
+        <v>2.2774658203125</v>
+      </c>
+      <c r="V126">
+        <v>9.51708984375</v>
       </c>
     </row>
   </sheetData>

--- a/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (QQQ)_v3.xlsx
+++ b/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (QQQ)_v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>High
 Price</t>
@@ -67,11 +67,11 @@
 Price</t>
   </si>
   <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>Low
 Price</t>
-  </si>
-  <si>
-    <t>Triple Cross Medium</t>
   </si>
   <si>
     <t>Long
@@ -81,6 +81,9 @@
   <si>
     <t>Close
 Price</t>
+  </si>
+  <si>
+    <t>Long</t>
   </si>
   <si>
     <t>Predicted
@@ -93,6 +96,9 @@
 Difference</t>
   </si>
   <si>
+    <t>Short</t>
+  </si>
+  <si>
     <t>Volume</t>
   </si>
   <si>
@@ -102,17 +108,11 @@
     <t>ROC%</t>
   </si>
   <si>
-    <t>Triple Cross Short</t>
-  </si>
-  <si>
     <t>Williams
 EMAI</t>
   </si>
   <si>
     <t>Neural Index</t>
-  </si>
-  <si>
-    <t>Triple Cross Long</t>
   </si>
 </sst>
 </file>
@@ -150,10 +150,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" readingOrder="0"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -466,9 +466,9 @@
     <col min="14" max="14" width="15.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="17.7109375" customWidth="1"/>
-    <col min="17" max="17" width="23.7109375" customWidth="1"/>
-    <col min="18" max="18" width="27" customWidth="1"/>
-    <col min="19" max="19" width="23.28515625" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="22" width="14.5703125" customWidth="1"/>
     <col min="23" max="16384" width="8.7265625"/>
   </cols>
@@ -477,74 +477,74 @@
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="M1" t="s">
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q1" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="L2" s="1"/>
       <c r="M2" t="s">
         <v>4</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
         <v>10</v>
@@ -553,2940 +553,3076 @@
         <v>8</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="1">
-        <v>46261</v>
+      <c r="A3" s="2">
+        <v>46269</v>
       </c>
       <c r="B3">
-        <v>4.66131591796875</v>
+        <v>3.72772216796875</v>
       </c>
       <c r="C3">
-        <v>-1.491943359375</v>
+        <v>2.60296630859375</v>
       </c>
       <c r="D3">
-        <v>-3.8359375</v>
+        <v>0.3096923828125</v>
       </c>
       <c r="E3">
-        <v>716.929992675781</v>
+        <v>719.344970703125</v>
       </c>
       <c r="F3">
-        <v>721.349975585938</v>
+        <v>721.859985351563</v>
       </c>
       <c r="G3">
-        <v>714.525024414063</v>
+        <v>716.559997558594</v>
       </c>
       <c r="H3">
-        <v>721.109985351563</v>
+        <v>718.960021972656</v>
       </c>
       <c r="I3">
-        <v>722.337341308594</v>
+        <v>722.363159179688</v>
       </c>
       <c r="J3">
-        <v>717.721252441406</v>
+        <v>716.705444335938</v>
       </c>
       <c r="K3">
-        <v>28723400</v>
+        <v>32780670</v>
       </c>
       <c r="L3">
-        <v>0.713811993598938</v>
+        <v>-0.234040766954422</v>
       </c>
       <c r="M3">
-        <v>74.1502151489258</v>
+        <v>47.793140411377</v>
       </c>
       <c r="N3">
-        <v>-12.5261697769165</v>
+        <v>-7.73266696929932</v>
       </c>
       <c r="O3" t="s">
         <v>1</v>
       </c>
       <c r="P3">
-        <v>35.1892890930176</v>
+        <v>57.7196006774902</v>
       </c>
       <c r="Q3">
-        <v>715.721313476563</v>
+        <v>716.620361328125</v>
       </c>
       <c r="R3">
-        <v>715.231018066406</v>
+        <v>715.381286621094</v>
       </c>
       <c r="S3">
-        <v>714.299743652344</v>
+        <v>714.463317871094</v>
       </c>
       <c r="T3">
-        <v>0.98736572265625</v>
+        <v>0.503173828125</v>
       </c>
       <c r="U3">
-        <v>3.19622802734375</v>
+        <v>0.14544677734375</v>
       </c>
       <c r="V3">
-        <v>4.6160888671875</v>
+        <v>5.65771484375</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="1">
-        <v>46260</v>
+      <c r="A4" s="2">
+        <v>46268</v>
       </c>
       <c r="B4">
-        <v>0.4306640625</v>
+        <v>1.111083984375</v>
       </c>
       <c r="C4">
-        <v>-6.2967529296875</v>
+        <v>0.99615478515625</v>
       </c>
       <c r="D4">
-        <v>-6.01812744140625</v>
+        <v>-2.15606689453125</v>
       </c>
       <c r="E4">
-        <v>708.409973144531</v>
+        <v>710.849975585938</v>
       </c>
       <c r="F4">
-        <v>713.02001953125</v>
+        <v>718.914978027344</v>
       </c>
       <c r="G4">
-        <v>707.969970703125</v>
+        <v>709.690002441406</v>
       </c>
       <c r="H4">
-        <v>711.369995117188</v>
+        <v>717.669982910156</v>
       </c>
       <c r="I4">
-        <v>714.13525390625</v>
+        <v>719.351440429688</v>
       </c>
       <c r="J4">
-        <v>708.566284179688</v>
+        <v>714.108703613281</v>
       </c>
       <c r="K4">
-        <v>20392300</v>
+        <v>29449700</v>
       </c>
       <c r="L4">
-        <v>-0.141427174210548</v>
+        <v>-0.0333281010389328</v>
       </c>
       <c r="M4">
-        <v>84.7684555053711</v>
+        <v>51.7985496520996</v>
       </c>
       <c r="N4">
-        <v>1.23760998249054</v>
+        <v>-23.523889541626</v>
       </c>
       <c r="O4" t="s">
         <v>1</v>
       </c>
       <c r="P4">
+        <v>50.7881851196289</v>
+      </c>
+      <c r="Q4">
+        <v>713.895751953125</v>
+      </c>
+      <c r="R4">
+        <v>714.236145019531</v>
+      </c>
+      <c r="S4">
+        <v>713.808471679688</v>
+      </c>
+      <c r="T4">
+        <v>0.43646240234375</v>
+      </c>
+      <c r="U4">
+        <v>4.418701171875</v>
+      </c>
+      <c r="V4">
+        <v>5.24273681640625</v>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B5">
+        <v>-4.34771728515625</v>
+      </c>
+      <c r="C5">
+        <v>-0.8651123046875</v>
+      </c>
+      <c r="D5">
+        <v>-4.5257568359375</v>
+      </c>
+      <c r="E5">
+        <v>707.099975585938</v>
+      </c>
+      <c r="F5">
+        <v>709.798889160156</v>
+      </c>
+      <c r="G5">
+        <v>705.099975585938</v>
+      </c>
+      <c r="H5">
+        <v>709.239990234375</v>
+      </c>
+      <c r="I5">
+        <v>712.845642089844</v>
+      </c>
+      <c r="J5">
+        <v>706.473327636719</v>
+      </c>
+      <c r="K5">
+        <v>23476200</v>
+      </c>
+      <c r="L5">
+        <v>-0.784281432628632</v>
+      </c>
+      <c r="M5">
+        <v>67.7316741943359</v>
+      </c>
+      <c r="N5">
+        <v>-9.31163692474365</v>
+      </c>
+      <c r="O5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5">
+        <v>-10.4177856445313</v>
+      </c>
+      <c r="Q5">
+        <v>710.752807617188</v>
+      </c>
+      <c r="R5">
+        <v>713.091125488281</v>
+      </c>
+      <c r="S5">
+        <v>713.333984375</v>
+      </c>
+      <c r="T5">
+        <v>3.0467529296875</v>
+      </c>
+      <c r="U5">
+        <v>1.37335205078125</v>
+      </c>
+      <c r="V5">
+        <v>6.372314453125</v>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B6">
+        <v>-4.03338623046875</v>
+      </c>
+      <c r="C6">
+        <v>-0.24066162109375</v>
+      </c>
+      <c r="D6">
+        <v>-4.17218017578125</v>
+      </c>
+      <c r="E6">
+        <v>707.390014648438</v>
+      </c>
+      <c r="F6">
+        <v>712.299987792969</v>
+      </c>
+      <c r="G6">
+        <v>704.659973144531</v>
+      </c>
+      <c r="H6">
+        <v>707.640014648438</v>
+      </c>
+      <c r="I6">
+        <v>711.4423828125</v>
+      </c>
+      <c r="J6">
+        <v>703.673706054688</v>
+      </c>
+      <c r="K6">
+        <v>35236100</v>
+      </c>
+      <c r="L6">
+        <v>-0.139043897390366</v>
+      </c>
+      <c r="M6">
+        <v>74.6861801147461</v>
+      </c>
+      <c r="N6">
+        <v>16.2526073455811</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6">
+        <v>-28.9910221099854</v>
+      </c>
+      <c r="Q6">
+        <v>711.9873046875</v>
+      </c>
+      <c r="R6">
+        <v>714.055480957031</v>
+      </c>
+      <c r="S6">
+        <v>713.907104492188</v>
+      </c>
+      <c r="T6">
+        <v>-0.85760498046875</v>
+      </c>
+      <c r="U6">
+        <v>-0.98626708984375</v>
+      </c>
+      <c r="V6">
+        <v>7.7686767578125</v>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B7">
+        <v>1.43621826171875</v>
+      </c>
+      <c r="C7">
+        <v>2.0867919921875</v>
+      </c>
+      <c r="D7">
+        <v>-2.449462890625</v>
+      </c>
+      <c r="E7">
+        <v>715.169982910156</v>
+      </c>
+      <c r="F7">
+        <v>717.580017089844</v>
+      </c>
+      <c r="G7">
+        <v>713.159973144531</v>
+      </c>
+      <c r="H7">
+        <v>716.760009765625</v>
+      </c>
+      <c r="I7">
+        <v>719.753356933594</v>
+      </c>
+      <c r="J7">
+        <v>713.601440429688</v>
+      </c>
+      <c r="K7">
+        <v>32237100</v>
+      </c>
+      <c r="L7">
+        <v>0.409528464078903</v>
+      </c>
+      <c r="M7">
+        <v>64.2447357177734</v>
+      </c>
+      <c r="N7">
+        <v>-10.1967639923096</v>
+      </c>
+      <c r="O7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7">
+        <v>-4.16709566116333</v>
+      </c>
+      <c r="Q7">
+        <v>716.4013671875</v>
+      </c>
+      <c r="R7">
+        <v>715.804931640625</v>
+      </c>
+      <c r="S7">
+        <v>714.654663085938</v>
+      </c>
+      <c r="T7">
+        <v>2.17333984375</v>
+      </c>
+      <c r="U7">
+        <v>0.44146728515625</v>
+      </c>
+      <c r="V7">
+        <v>6.15191650390625</v>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B8">
+        <v>3.5447998046875</v>
+      </c>
+      <c r="C8">
+        <v>0.5439453125</v>
+      </c>
+      <c r="D8">
+        <v>-3.02606201171875</v>
+      </c>
+      <c r="E8">
+        <v>719.739990234375</v>
+      </c>
+      <c r="F8">
+        <v>724.125</v>
+      </c>
+      <c r="G8">
+        <v>715.085021972656</v>
+      </c>
+      <c r="H8">
+        <v>716.429992675781</v>
+      </c>
+      <c r="I8">
+        <v>719.943054199219</v>
+      </c>
+      <c r="J8">
+        <v>713.0546875</v>
+      </c>
+      <c r="K8">
+        <v>34105300</v>
+      </c>
+      <c r="L8">
+        <v>0.137622654438019</v>
+      </c>
+      <c r="M8">
+        <v>71.5394439697266</v>
+      </c>
+      <c r="N8">
+        <v>-3.5209219455719</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>0.550081491470337</v>
+      </c>
+      <c r="Q8">
+        <v>716.098693847656</v>
+      </c>
+      <c r="R8">
+        <v>715.528686523438</v>
+      </c>
+      <c r="S8">
+        <v>714.415161132813</v>
+      </c>
+      <c r="T8">
+        <v>-4.18194580078125</v>
+      </c>
+      <c r="U8">
+        <v>-2.03033447265625</v>
+      </c>
+      <c r="V8">
+        <v>6.88836669921875</v>
+      </c>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B9">
+        <v>4.66131591796875</v>
+      </c>
+      <c r="C9">
+        <v>-1.491943359375</v>
+      </c>
+      <c r="D9">
+        <v>-3.8359375</v>
+      </c>
+      <c r="E9">
+        <v>716.929992675781</v>
+      </c>
+      <c r="F9">
+        <v>721.349975585938</v>
+      </c>
+      <c r="G9">
+        <v>714.525024414063</v>
+      </c>
+      <c r="H9">
+        <v>721.109985351563</v>
+      </c>
+      <c r="I9">
+        <v>722.337341308594</v>
+      </c>
+      <c r="J9">
+        <v>717.721252441406</v>
+      </c>
+      <c r="K9">
+        <v>28723400</v>
+      </c>
+      <c r="L9">
+        <v>0.713811993598938</v>
+      </c>
+      <c r="M9">
+        <v>74.1502151489258</v>
+      </c>
+      <c r="N9">
+        <v>-12.5261697769165</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>35.1892890930176</v>
+      </c>
+      <c r="Q9">
+        <v>715.721313476563</v>
+      </c>
+      <c r="R9">
+        <v>715.231018066406</v>
+      </c>
+      <c r="S9">
+        <v>714.299743652344</v>
+      </c>
+      <c r="T9">
+        <v>0.98736572265625</v>
+      </c>
+      <c r="U9">
+        <v>3.19622802734375</v>
+      </c>
+      <c r="V9">
+        <v>4.6160888671875</v>
+      </c>
+    </row>
+    <row r="10" ht="19.5" customHeight="1">
+      <c r="A10" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B10">
+        <v>0.4306640625</v>
+      </c>
+      <c r="C10">
+        <v>-6.2967529296875</v>
+      </c>
+      <c r="D10">
+        <v>-6.01812744140625</v>
+      </c>
+      <c r="E10">
+        <v>708.409973144531</v>
+      </c>
+      <c r="F10">
+        <v>713.02001953125</v>
+      </c>
+      <c r="G10">
+        <v>707.969970703125</v>
+      </c>
+      <c r="H10">
+        <v>711.369995117188</v>
+      </c>
+      <c r="I10">
+        <v>714.13525390625</v>
+      </c>
+      <c r="J10">
+        <v>708.566284179688</v>
+      </c>
+      <c r="K10">
+        <v>20392300</v>
+      </c>
+      <c r="L10">
+        <v>-0.141427174210548</v>
+      </c>
+      <c r="M10">
+        <v>84.7684555053711</v>
+      </c>
+      <c r="N10">
+        <v>1.23760998249054</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <v>10.8492841720581</v>
       </c>
-      <c r="Q4">
+      <c r="Q10">
         <v>711.046569824219</v>
       </c>
-      <c r="R4">
+      <c r="R10">
         <v>713.631652832031</v>
       </c>
-      <c r="S4">
+      <c r="S10">
         <v>713.460998535156</v>
       </c>
-      <c r="T4">
+      <c r="T10">
         <v>1.115234375</v>
       </c>
-      <c r="U4">
+      <c r="U10">
         <v>0.5963134765625</v>
       </c>
-      <c r="V4">
+      <c r="V10">
         <v>5.5689697265625</v>
       </c>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="1">
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="2">
         <v>46259</v>
       </c>
-      <c r="B5">
+      <c r="B11">
         <v>-1.2520751953125</v>
       </c>
-      <c r="C5">
+      <c r="C11">
         <v>-7.48583984375</v>
       </c>
-      <c r="D5">
+      <c r="D11">
         <v>-6.08203125</v>
       </c>
-      <c r="E5">
+      <c r="E11">
         <v>711.219970703125</v>
       </c>
-      <c r="F5">
+      <c r="F11">
         <v>714.039978027344</v>
       </c>
-      <c r="G5">
+      <c r="G11">
         <v>707.450012207031</v>
       </c>
-      <c r="H5">
+      <c r="H11">
         <v>710.719970703125</v>
       </c>
-      <c r="I5">
+      <c r="I11">
         <v>714.233215332031</v>
       </c>
-      <c r="J5">
+      <c r="J11">
         <v>708.015258789063</v>
       </c>
-      <c r="K5">
+      <c r="K11">
         <v>23869600</v>
       </c>
-      <c r="L5">
+      <c r="L11">
         <v>-0.31761822104454</v>
       </c>
-      <c r="M5">
+      <c r="M11">
         <v>83.732177734375</v>
       </c>
-      <c r="N5">
+      <c r="N11">
         <v>9.97407245635986</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O11" t="s">
         <v>1</v>
       </c>
-      <c r="P5">
+      <c r="P11">
         <v>5.51300573348999</v>
       </c>
-      <c r="Q5">
+      <c r="Q11">
         <v>710.73046875</v>
       </c>
-      <c r="R5">
+      <c r="R11">
         <v>714.225708007813</v>
       </c>
-      <c r="S5">
+      <c r="S11">
         <v>713.566101074219</v>
       </c>
-      <c r="T5">
+      <c r="T11">
         <v>0.1932373046875</v>
       </c>
-      <c r="U5">
+      <c r="U11">
         <v>0.56524658203125</v>
       </c>
-      <c r="V5">
+      <c r="V11">
         <v>6.21795654296875</v>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="1">
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="2">
         <v>46258</v>
       </c>
-      <c r="B6">
+      <c r="B12">
         <v>-4.09735107421875</v>
       </c>
-      <c r="C6">
+      <c r="C12">
         <v>-7.77984619140625</v>
       </c>
-      <c r="D6">
+      <c r="D12">
         <v>-6.29669189453125</v>
       </c>
-      <c r="E6">
+      <c r="E12">
         <v>709.659973144531</v>
       </c>
-      <c r="F6">
+      <c r="F12">
         <v>709.789978027344</v>
       </c>
-      <c r="G6">
+      <c r="G12">
         <v>702.700012207031</v>
       </c>
-      <c r="H6">
+      <c r="H12">
         <v>706.320007324219</v>
       </c>
-      <c r="I6">
+      <c r="I12">
         <v>710.232482910156</v>
       </c>
-      <c r="J6">
+      <c r="J12">
         <v>702.45703125</v>
       </c>
-      <c r="K6">
+      <c r="K12">
         <v>37443100</v>
       </c>
-      <c r="L6">
+      <c r="L12">
         <v>-0.749046683311462</v>
       </c>
-      <c r="M6">
+      <c r="M12">
         <v>76.1381072998047</v>
       </c>
-      <c r="N6">
+      <c r="N12">
         <v>-10.0091505050659</v>
       </c>
-      <c r="O6" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6">
+      <c r="O12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P12">
         <v>-22.8135929107666</v>
       </c>
-      <c r="Q6">
+      <c r="Q12">
         <v>710.474365234375</v>
       </c>
-      <c r="R6">
+      <c r="R12">
         <v>715.191345214844</v>
       </c>
-      <c r="S6">
+      <c r="S12">
         <v>713.859497070313</v>
       </c>
-      <c r="T6">
+      <c r="T12">
         <v>0.4425048828125</v>
       </c>
-      <c r="U6">
+      <c r="U12">
         <v>-0.24298095703125</v>
       </c>
-      <c r="V6">
+      <c r="V12">
         <v>7.77545166015625</v>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="1">
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="2">
         <v>46255</v>
       </c>
-      <c r="B7">
+      <c r="B13">
         <v>-3.96600341796875</v>
       </c>
-      <c r="C7">
+      <c r="C13">
         <v>-5.479248046875</v>
       </c>
-      <c r="D7">
+      <c r="D13">
         <v>-2.70074462890625</v>
       </c>
-      <c r="E7">
+      <c r="E13">
         <v>715.22998046875</v>
       </c>
-      <c r="F7">
+      <c r="F13">
         <v>715.673889160156</v>
       </c>
-      <c r="G7">
+      <c r="G13">
         <v>709.200012207031</v>
       </c>
-      <c r="H7">
+      <c r="H13">
         <v>713.440002441406</v>
       </c>
-      <c r="I7">
+      <c r="I13">
         <v>716.713745117188</v>
       </c>
-      <c r="J7">
+      <c r="J13">
         <v>710.5546875</v>
       </c>
-      <c r="K7">
+      <c r="K13">
         <v>33399400</v>
       </c>
-      <c r="L7">
+      <c r="L13">
         <v>-0.884286046028137</v>
       </c>
-      <c r="M7">
+      <c r="M13">
         <v>84.6064987182617</v>
       </c>
-      <c r="N7">
+      <c r="N13">
         <v>48.485767364502</v>
       </c>
-      <c r="O7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7">
+      <c r="O13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P13">
         <v>-1.74106681346893</v>
       </c>
-      <c r="Q7">
+      <c r="Q13">
         <v>714.61328125</v>
       </c>
-      <c r="R7">
+      <c r="R13">
         <v>717.7197265625</v>
       </c>
-      <c r="S7">
+      <c r="S13">
         <v>714.918212890625</v>
       </c>
-      <c r="T7">
+      <c r="T13">
         <v>1.03985595703125</v>
       </c>
-      <c r="U7">
+      <c r="U13">
         <v>1.35467529296875</v>
       </c>
-      <c r="V7">
+      <c r="V13">
         <v>6.1590576171875</v>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="1">
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="2">
         <v>46254</v>
       </c>
-      <c r="B8">
+      <c r="B14">
         <v>-7.43365478515625</v>
       </c>
-      <c r="C8">
+      <c r="C14">
         <v>-4.934814453125</v>
       </c>
-      <c r="D8">
+      <c r="D14">
         <v>0.49609375</v>
       </c>
-      <c r="E8">
+      <c r="E14">
         <v>712.090026855469</v>
       </c>
-      <c r="F8">
+      <c r="F14">
         <v>714.940002441406</v>
       </c>
-      <c r="G8">
+      <c r="G14">
         <v>708.52001953125</v>
       </c>
-      <c r="H8">
+      <c r="H14">
         <v>710.929992675781</v>
       </c>
-      <c r="I8">
+      <c r="I14">
         <v>715.544738769531</v>
       </c>
-      <c r="J8">
+      <c r="J14">
         <v>707.915893554688</v>
       </c>
-      <c r="K8">
+      <c r="K14">
         <v>33396400</v>
       </c>
-      <c r="L8">
+      <c r="L14">
         <v>-0.928094744682312</v>
       </c>
-      <c r="M8">
+      <c r="M14">
         <v>56.9795341491699</v>
       </c>
-      <c r="N8">
+      <c r="N14">
         <v>39.8270530700684</v>
       </c>
-      <c r="O8" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8">
+      <c r="O14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14">
         <v>-14.3682527542114</v>
       </c>
-      <c r="Q8">
+      <c r="Q14">
         <v>715.648803710938</v>
       </c>
-      <c r="R8">
+      <c r="R14">
         <v>718.887145996094</v>
       </c>
-      <c r="S8">
+      <c r="S14">
         <v>715.012329101563</v>
       </c>
-      <c r="T8">
+      <c r="T14">
         <v>0.604736328125</v>
       </c>
-      <c r="U8">
+      <c r="U14">
         <v>-0.6041259765625</v>
       </c>
-      <c r="V8">
+      <c r="V14">
         <v>7.62884521484375</v>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="1">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="2">
         <v>46253</v>
       </c>
-      <c r="B9">
+      <c r="B15">
         <v>-7.27069091796875</v>
       </c>
-      <c r="C9">
+      <c r="C15">
         <v>-1.59088134765625</v>
       </c>
-      <c r="D9">
+      <c r="D15">
         <v>5.09222412109375</v>
       </c>
-      <c r="E9">
+      <c r="E15">
         <v>720.390014648438</v>
       </c>
-      <c r="F9">
+      <c r="F15">
         <v>721.499816894531</v>
       </c>
-      <c r="G9">
+      <c r="G15">
         <v>712.609985351563</v>
       </c>
-      <c r="H9">
+      <c r="H15">
         <v>716.080017089844</v>
       </c>
-      <c r="I9">
+      <c r="I15">
         <v>720.196044921875</v>
       </c>
-      <c r="J9">
+      <c r="J15">
         <v>712.312255859375</v>
       </c>
-      <c r="K9">
+      <c r="K15">
         <v>35801700</v>
       </c>
-      <c r="L9">
+      <c r="L15">
         <v>-0.790475010871887</v>
       </c>
-      <c r="M9">
+      <c r="M15">
         <v>40.7500076293945</v>
       </c>
-      <c r="N9">
+      <c r="N15">
         <v>-0.867587327957153</v>
       </c>
-      <c r="O9" t="s">
-        <v>21</v>
-      </c>
-      <c r="P9">
+      <c r="O15" t="s">
+        <v>23</v>
+      </c>
+      <c r="P15">
         <v>-27.9632911682129</v>
       </c>
-      <c r="Q9">
+      <c r="Q15">
         <v>719.837768554688</v>
       </c>
-      <c r="R9">
+      <c r="R15">
         <v>720.874938964844</v>
       </c>
-      <c r="S9">
+      <c r="S15">
         <v>715.392578125</v>
       </c>
-      <c r="T9">
+      <c r="T15">
         <v>-1.30377197265625</v>
       </c>
-      <c r="U9">
+      <c r="U15">
         <v>-0.2977294921875</v>
       </c>
-      <c r="V9">
+      <c r="V15">
         <v>7.8837890625</v>
       </c>
     </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="1">
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="2">
         <v>46252</v>
       </c>
-      <c r="B10">
+      <c r="B16">
         <v>-5.08782958984375</v>
       </c>
-      <c r="C10">
+      <c r="C16">
         <v>1.26361083984375</v>
       </c>
-      <c r="D10">
+      <c r="D16">
         <v>10.6339111328125</v>
       </c>
-      <c r="E10">
+      <c r="E16">
         <v>720.210021972656</v>
       </c>
-      <c r="F10">
+      <c r="F16">
         <v>722.130004882813</v>
       </c>
-      <c r="G10">
+      <c r="G16">
         <v>715.919982910156</v>
       </c>
-      <c r="H10">
+      <c r="H16">
         <v>717.510009765625</v>
       </c>
-      <c r="I10">
+      <c r="I16">
         <v>721.464477539063</v>
       </c>
-      <c r="J10">
+      <c r="J16">
         <v>713.809631347656</v>
       </c>
-      <c r="K10">
+      <c r="K16">
         <v>48997100</v>
       </c>
-      <c r="L10">
+      <c r="L16">
         <v>-0.470953077077866</v>
       </c>
-      <c r="M10">
+      <c r="M16">
         <v>41.1066436767578</v>
       </c>
-      <c r="N10">
+      <c r="N16">
         <v>41.1687278747559</v>
       </c>
-      <c r="O10" t="s">
-        <v>21</v>
-      </c>
-      <c r="P10">
+      <c r="O16" t="s">
+        <v>23</v>
+      </c>
+      <c r="P16">
         <v>-47.562686920166</v>
       </c>
-      <c r="Q10">
+      <c r="Q16">
         <v>723.48291015625</v>
       </c>
-      <c r="R10">
+      <c r="R16">
         <v>722.074768066406</v>
       </c>
-      <c r="S10">
+      <c r="S16">
         <v>715.1767578125</v>
       </c>
-      <c r="T10">
+      <c r="T16">
         <v>-0.66552734375</v>
       </c>
-      <c r="U10">
+      <c r="U16">
         <v>-2.1103515625</v>
       </c>
-      <c r="V10">
+      <c r="V16">
         <v>7.65484619140625</v>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="1">
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="2">
         <v>46251</v>
       </c>
-      <c r="B11">
+      <c r="B17">
         <v>3.04315185546875</v>
       </c>
-      <c r="C11">
+      <c r="C17">
         <v>4.91015625</v>
       </c>
-      <c r="D11">
+      <c r="D17">
         <v>16.1221923828125</v>
       </c>
-      <c r="E11">
+      <c r="E17">
         <v>732.950012207031</v>
       </c>
-      <c r="F11">
+      <c r="F17">
         <v>734.580017089844</v>
       </c>
-      <c r="G11">
+      <c r="G17">
         <v>729.27001953125</v>
       </c>
-      <c r="H11">
+      <c r="H17">
         <v>729.869995117188</v>
       </c>
-      <c r="I11">
+      <c r="I17">
         <v>733.000610351563</v>
       </c>
-      <c r="J11">
+      <c r="J17">
         <v>727.500427246094</v>
       </c>
-      <c r="K11">
+      <c r="K17">
         <v>26452500</v>
       </c>
-      <c r="L11">
+      <c r="L17">
         <v>-0.632856070995331</v>
       </c>
-      <c r="M11">
+      <c r="M17">
         <v>29.118803024292</v>
       </c>
-      <c r="N11">
+      <c r="N17">
         <v>-30.5778942108154</v>
       </c>
-      <c r="O11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11">
+      <c r="O17" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17">
         <v>-0.659402906894684</v>
       </c>
-      <c r="Q11">
+      <c r="Q17">
         <v>729.34814453125</v>
       </c>
-      <c r="R11">
+      <c r="R17">
         <v>723.375366210938</v>
       </c>
-      <c r="S11">
+      <c r="S17">
         <v>715.094543457031</v>
       </c>
-      <c r="T11">
+      <c r="T17">
         <v>-1.57940673828125</v>
       </c>
-      <c r="U11">
+      <c r="U17">
         <v>-1.76959228515625</v>
       </c>
-      <c r="V11">
+      <c r="V17">
         <v>5.50018310546875</v>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="1">
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="2">
         <v>46248</v>
       </c>
-      <c r="B12">
+      <c r="B18">
         <v>4.747802734375</v>
       </c>
-      <c r="C12">
+      <c r="C18">
         <v>7.09246826171875</v>
       </c>
-      <c r="D12">
+      <c r="D18">
         <v>17.9688720703125</v>
       </c>
-      <c r="E12">
+      <c r="E18">
         <v>733.409973144531</v>
       </c>
-      <c r="F12">
+      <c r="F18">
         <v>734.390014648438</v>
       </c>
-      <c r="G12">
+      <c r="G18">
         <v>728.320007324219</v>
       </c>
-      <c r="H12">
+      <c r="H18">
         <v>731.070007324219</v>
       </c>
-      <c r="I12">
+      <c r="I18">
         <v>734.302001953125</v>
       </c>
-      <c r="J12">
+      <c r="J18">
         <v>727.537048339844</v>
       </c>
-      <c r="K12">
+      <c r="K18">
         <v>23790600</v>
       </c>
-      <c r="L12">
+      <c r="L18">
         <v>-0.310950875282288</v>
       </c>
-      <c r="M12">
+      <c r="M18">
         <v>41.9445686340332</v>
       </c>
-      <c r="N12">
+      <c r="N18">
         <v>2.53283834457397</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O18" t="s">
         <v>1</v>
       </c>
-      <c r="P12">
+      <c r="P18">
         <v>12.7733783721924</v>
       </c>
-      <c r="Q12">
+      <c r="Q18">
         <v>728.561706542969</v>
       </c>
-      <c r="R12">
+      <c r="R18">
         <v>721.666564941406</v>
       </c>
-      <c r="S12">
+      <c r="S18">
         <v>713.505493164063</v>
       </c>
-      <c r="T12">
+      <c r="T18">
         <v>-0.0880126953125</v>
       </c>
-      <c r="U12">
+      <c r="U18">
         <v>-0.782958984375</v>
       </c>
-      <c r="V12">
+      <c r="V18">
         <v>6.76495361328125</v>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="1">
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="2">
         <v>46247</v>
       </c>
-      <c r="B13">
+      <c r="B19">
         <v>4.3778076171875</v>
       </c>
-      <c r="C13">
+      <c r="C19">
         <v>8.908935546875</v>
       </c>
-      <c r="D13">
+      <c r="D19">
         <v>18.5191040039063</v>
       </c>
-      <c r="E13">
+      <c r="E19">
         <v>725.150024414063</v>
       </c>
-      <c r="F13">
+      <c r="F19">
         <v>733.960021972656</v>
       </c>
-      <c r="G13">
+      <c r="G19">
         <v>724.030029296875</v>
       </c>
-      <c r="H13">
+      <c r="H19">
         <v>732.070007324219</v>
       </c>
-      <c r="I13">
+      <c r="I19">
         <v>732.538391113281</v>
       </c>
-      <c r="J13">
+      <c r="J19">
         <v>727.682556152344</v>
       </c>
-      <c r="K13">
+      <c r="K19">
         <v>31599700</v>
       </c>
-      <c r="L13">
+      <c r="L19">
         <v>-0.488571882247925</v>
       </c>
-      <c r="M13">
+      <c r="M19">
         <v>40.9084243774414</v>
       </c>
-      <c r="N13">
+      <c r="N19">
         <v>-31.3219966888428</v>
-      </c>
-      <c r="O13" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13">
-        <v>30.4323463439941</v>
-      </c>
-      <c r="Q13">
-        <v>726.150024414063</v>
-      </c>
-      <c r="R13">
-        <v>718.895812988281</v>
-      </c>
-      <c r="S13">
-        <v>711.396850585938</v>
-      </c>
-      <c r="T13">
-        <v>-1.421630859375</v>
-      </c>
-      <c r="U13">
-        <v>3.65252685546875</v>
-      </c>
-      <c r="V13">
-        <v>4.8558349609375</v>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="1">
-        <v>46246</v>
-      </c>
-      <c r="B14">
-        <v>2.327392578125</v>
-      </c>
-      <c r="C14">
-        <v>9.25762939453125</v>
-      </c>
-      <c r="D14">
-        <v>17.2620849609375</v>
-      </c>
-      <c r="E14">
-        <v>727.080017089844</v>
-      </c>
-      <c r="F14">
-        <v>727.25</v>
-      </c>
-      <c r="G14">
-        <v>722.919982910156</v>
-      </c>
-      <c r="H14">
-        <v>723.700012207031</v>
-      </c>
-      <c r="I14">
-        <v>726.914245605469</v>
-      </c>
-      <c r="J14">
-        <v>721.6142578125</v>
-      </c>
-      <c r="K14">
-        <v>29065900</v>
-      </c>
-      <c r="L14">
-        <v>-1.10904657840729</v>
-      </c>
-      <c r="M14">
-        <v>59.5655403137207</v>
-      </c>
-      <c r="N14">
-        <v>-8.88726615905762</v>
-      </c>
-      <c r="O14" t="s">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>18.1262340545654</v>
-      </c>
-      <c r="Q14">
-        <v>721.5166015625</v>
-      </c>
-      <c r="R14">
-        <v>715.153076171875</v>
-      </c>
-      <c r="S14">
-        <v>709.211975097656</v>
-      </c>
-      <c r="T14">
-        <v>-0.33575439453125</v>
-      </c>
-      <c r="U14">
-        <v>-1.30572509765625</v>
-      </c>
-      <c r="V14">
-        <v>5.29998779296875</v>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="1">
-        <v>46245</v>
-      </c>
-      <c r="B15">
-        <v>0.384765625</v>
-      </c>
-      <c r="C15">
-        <v>12.8827514648438</v>
-      </c>
-      <c r="D15">
-        <v>15.763671875</v>
-      </c>
-      <c r="E15">
-        <v>723.289978027344</v>
-      </c>
-      <c r="F15">
-        <v>723.349975585938</v>
-      </c>
-      <c r="G15">
-        <v>715.5</v>
-      </c>
-      <c r="H15">
-        <v>718.450012207031</v>
-      </c>
-      <c r="I15">
-        <v>721.348022460938</v>
-      </c>
-      <c r="J15">
-        <v>715.432067871094</v>
-      </c>
-      <c r="K15">
-        <v>29286100</v>
-      </c>
-      <c r="L15">
-        <v>-0.973330557346344</v>
-      </c>
-      <c r="M15">
-        <v>65.3756484985352</v>
-      </c>
-      <c r="N15">
-        <v>2.9482729434967</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15">
-        <v>-9.89096736907959</v>
-      </c>
-      <c r="Q15">
-        <v>718.969360351563</v>
-      </c>
-      <c r="R15">
-        <v>712.544189453125</v>
-      </c>
-      <c r="S15">
-        <v>707.421081542969</v>
-      </c>
-      <c r="T15">
-        <v>-2.001953125</v>
-      </c>
-      <c r="U15">
-        <v>-0.06793212890625</v>
-      </c>
-      <c r="V15">
-        <v>5.91595458984375</v>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="1">
-        <v>46244</v>
-      </c>
-      <c r="B16">
-        <v>0.97235107421875</v>
-      </c>
-      <c r="C16">
-        <v>16.9237670898438</v>
-      </c>
-      <c r="D16">
-        <v>15.2864379882813</v>
-      </c>
-      <c r="E16">
-        <v>722.390014648438</v>
-      </c>
-      <c r="F16">
-        <v>724.669982910156</v>
-      </c>
-      <c r="G16">
-        <v>720.330017089844</v>
-      </c>
-      <c r="H16">
-        <v>720.869995117188</v>
-      </c>
-      <c r="I16">
-        <v>724.498474121094</v>
-      </c>
-      <c r="J16">
-        <v>718.993835449219</v>
-      </c>
-      <c r="K16">
-        <v>26243100</v>
-      </c>
-      <c r="L16">
-        <v>-1.02761697769165</v>
-      </c>
-      <c r="M16">
-        <v>63.5033950805664</v>
-      </c>
-      <c r="N16">
-        <v>4.0243992805481</v>
-      </c>
-      <c r="O16" t="s">
-        <v>1</v>
-      </c>
-      <c r="P16">
-        <v>9.99762535095215</v>
-      </c>
-      <c r="Q16">
-        <v>719.53515625</v>
-      </c>
-      <c r="R16">
-        <v>710.855163574219</v>
-      </c>
-      <c r="S16">
-        <v>706.193542480469</v>
-      </c>
-      <c r="T16">
-        <v>-0.1715087890625</v>
-      </c>
-      <c r="U16">
-        <v>-1.336181640625</v>
-      </c>
-      <c r="V16">
-        <v>5.504638671875</v>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="1">
-        <v>46241</v>
-      </c>
-      <c r="B17">
-        <v>4.0394287109375</v>
-      </c>
-      <c r="C17">
-        <v>18.4527587890625</v>
-      </c>
-      <c r="D17">
-        <v>14.3407592773438</v>
-      </c>
-      <c r="E17">
-        <v>720.150024414063</v>
-      </c>
-      <c r="F17">
-        <v>723.630004882813</v>
-      </c>
-      <c r="G17">
-        <v>716.510009765625</v>
-      </c>
-      <c r="H17">
-        <v>723.030029296875</v>
-      </c>
-      <c r="I17">
-        <v>726.10888671875</v>
-      </c>
-      <c r="J17">
-        <v>718.251037597656</v>
-      </c>
-      <c r="K17">
-        <v>31070300</v>
-      </c>
-      <c r="L17">
-        <v>-0.726187586784363</v>
-      </c>
-      <c r="M17">
-        <v>61.0466346740723</v>
-      </c>
-      <c r="N17">
-        <v>-0.528325259685516</v>
-      </c>
-      <c r="O17" t="s">
-        <v>1</v>
-      </c>
-      <c r="P17">
-        <v>26.1653099060059</v>
-      </c>
-      <c r="Q17">
-        <v>717.619018554688</v>
-      </c>
-      <c r="R17">
-        <v>707.809143066406</v>
-      </c>
-      <c r="S17">
-        <v>704.476501464844</v>
-      </c>
-      <c r="T17">
-        <v>2.4788818359375</v>
-      </c>
-      <c r="U17">
-        <v>1.74102783203125</v>
-      </c>
-      <c r="V17">
-        <v>7.85784912109375</v>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="1">
-        <v>46240</v>
-      </c>
-      <c r="B18">
-        <v>5.7655029296875</v>
-      </c>
-      <c r="C18">
-        <v>17.0516967773438</v>
-      </c>
-      <c r="D18">
-        <v>11.1168212890625</v>
-      </c>
-      <c r="E18">
-        <v>710.820007324219</v>
-      </c>
-      <c r="F18">
-        <v>719.320007324219</v>
-      </c>
-      <c r="G18">
-        <v>708.5</v>
-      </c>
-      <c r="H18">
-        <v>714.650024414063</v>
-      </c>
-      <c r="I18">
-        <v>718.173400878906</v>
-      </c>
-      <c r="J18">
-        <v>708.951232910156</v>
-      </c>
-      <c r="K18">
-        <v>33035800</v>
-      </c>
-      <c r="L18">
-        <v>-0.627615809440613</v>
-      </c>
-      <c r="M18">
-        <v>61.3708724975586</v>
-      </c>
-      <c r="N18">
-        <v>-10.5575513839722</v>
-      </c>
-      <c r="O18" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18">
-        <v>-23.3668766021729</v>
-      </c>
-      <c r="Q18">
-        <v>712.781005859375</v>
-      </c>
-      <c r="R18">
-        <v>703.359313964844</v>
-      </c>
-      <c r="S18">
-        <v>702.144226074219</v>
-      </c>
-      <c r="T18">
-        <v>-1.1466064453125</v>
-      </c>
-      <c r="U18">
-        <v>0.45123291015625</v>
-      </c>
-      <c r="V18">
-        <v>9.22216796875</v>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="1">
-        <v>46239</v>
-      </c>
-      <c r="B19">
-        <v>13.2140502929688</v>
-      </c>
-      <c r="C19">
-        <v>17.2907104492188</v>
-      </c>
-      <c r="D19">
-        <v>8.81109619140625</v>
-      </c>
-      <c r="E19">
-        <v>726.25</v>
-      </c>
-      <c r="F19">
-        <v>728.539978027344</v>
-      </c>
-      <c r="G19">
-        <v>716.919982910156</v>
-      </c>
-      <c r="H19">
-        <v>717.299987792969</v>
-      </c>
-      <c r="I19">
-        <v>722.862182617188</v>
-      </c>
-      <c r="J19">
-        <v>712.977844238281</v>
-      </c>
-      <c r="K19">
-        <v>33540100</v>
-      </c>
-      <c r="L19">
-        <v>-0.500950396060944</v>
-      </c>
-      <c r="M19">
-        <v>68.6149291992188</v>
-      </c>
-      <c r="N19">
-        <v>15.4603137969971</v>
       </c>
       <c r="O19" t="s">
         <v>1</v>
       </c>
       <c r="P19">
-        <v>28.8229656219482</v>
+        <v>30.4323463439941</v>
       </c>
       <c r="Q19">
-        <v>711.650634765625</v>
+        <v>726.150024414063</v>
       </c>
       <c r="R19">
-        <v>700.618591308594</v>
+        <v>718.895812988281</v>
       </c>
       <c r="S19">
-        <v>700.785400390625</v>
+        <v>711.396850585938</v>
       </c>
       <c r="T19">
-        <v>-5.67779541015625</v>
+        <v>-1.421630859375</v>
       </c>
       <c r="U19">
-        <v>-3.942138671875</v>
+        <v>3.65252685546875</v>
       </c>
       <c r="V19">
-        <v>9.88433837890625</v>
+        <v>4.8558349609375</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="1">
-        <v>46238</v>
+      <c r="A20" s="2">
+        <v>46246</v>
       </c>
       <c r="B20">
-        <v>20.4347534179688</v>
+        <v>2.327392578125</v>
       </c>
       <c r="C20">
-        <v>12.6027221679688</v>
+        <v>9.25762939453125</v>
       </c>
       <c r="D20">
-        <v>3.1591796875</v>
+        <v>17.2620849609375</v>
       </c>
       <c r="E20">
-        <v>708.159973144531</v>
+        <v>727.080017089844</v>
       </c>
       <c r="F20">
-        <v>725.659973144531</v>
+        <v>727.25</v>
       </c>
       <c r="G20">
-        <v>707.530029296875</v>
+        <v>722.919982910156</v>
       </c>
       <c r="H20">
-        <v>723.849975585938</v>
+        <v>723.700012207031</v>
       </c>
       <c r="I20">
-        <v>724.495361328125</v>
+        <v>726.914245605469</v>
       </c>
       <c r="J20">
-        <v>715.428039550781</v>
+        <v>721.6142578125</v>
       </c>
       <c r="K20">
-        <v>59778600</v>
+        <v>29065900</v>
       </c>
       <c r="L20">
-        <v>-0.300473153591156</v>
+        <v>-1.10904657840729</v>
       </c>
       <c r="M20">
-        <v>59.4272842407227</v>
+        <v>59.5655403137207</v>
       </c>
       <c r="N20">
-        <v>-21.2858924865723</v>
+        <v>-8.88726615905762</v>
       </c>
       <c r="O20" t="s">
         <v>1</v>
       </c>
       <c r="P20">
-        <v>100.000007629395</v>
+        <v>18.1262340545654</v>
       </c>
       <c r="Q20">
-        <v>705.591552734375</v>
+        <v>721.5166015625</v>
       </c>
       <c r="R20">
-        <v>695.908142089844</v>
+        <v>715.153076171875</v>
       </c>
       <c r="S20">
-        <v>698.772827148438</v>
+        <v>709.211975097656</v>
       </c>
       <c r="T20">
-        <v>-1.16461181640625</v>
+        <v>-0.33575439453125</v>
       </c>
       <c r="U20">
-        <v>7.89801025390625</v>
+        <v>-1.30572509765625</v>
       </c>
       <c r="V20">
-        <v>9.06732177734375</v>
+        <v>5.29998779296875</v>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="1">
-        <v>46237</v>
+      <c r="A21" s="2">
+        <v>46245</v>
       </c>
       <c r="B21">
-        <v>11.339599609375</v>
+        <v>0.384765625</v>
       </c>
       <c r="C21">
-        <v>0.62603759765625</v>
+        <v>12.8827514648438</v>
       </c>
       <c r="D21">
-        <v>-6.712646484375</v>
+        <v>15.763671875</v>
       </c>
       <c r="E21">
-        <v>688.299987792969</v>
+        <v>723.289978027344</v>
       </c>
       <c r="F21">
-        <v>701.590026855469</v>
+        <v>723.349975585938</v>
       </c>
       <c r="G21">
-        <v>685.820007324219</v>
+        <v>715.5</v>
       </c>
       <c r="H21">
-        <v>700.070007324219</v>
+        <v>718.450012207031</v>
       </c>
       <c r="I21">
-        <v>701.723510742188</v>
+        <v>721.348022460938</v>
       </c>
       <c r="J21">
-        <v>691.503540039063</v>
+        <v>715.432067871094</v>
       </c>
       <c r="K21">
-        <v>44965000</v>
+        <v>29286100</v>
       </c>
       <c r="L21">
-        <v>-0.909996390342712</v>
+        <v>-0.973330557346344</v>
       </c>
       <c r="M21">
-        <v>75.4976272583008</v>
+        <v>65.3756484985352</v>
       </c>
       <c r="N21">
-        <v>-15.1427478790283</v>
+        <v>2.9482729434967</v>
       </c>
       <c r="O21" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P21">
-        <v>66.5761184692383</v>
+        <v>-9.89096736907959</v>
       </c>
       <c r="Q21">
-        <v>689.914428710938</v>
+        <v>718.969360351563</v>
       </c>
       <c r="R21">
-        <v>688.366577148438</v>
+        <v>712.544189453125</v>
       </c>
       <c r="S21">
-        <v>695.902160644531</v>
+        <v>707.421081542969</v>
       </c>
       <c r="T21">
-        <v>0.13348388671875</v>
+        <v>-2.001953125</v>
       </c>
       <c r="U21">
-        <v>5.68353271484375</v>
+        <v>-0.06793212890625</v>
       </c>
       <c r="V21">
-        <v>10.219970703125</v>
+        <v>5.91595458984375</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="1">
-        <v>46234</v>
+      <c r="A22" s="2">
+        <v>46244</v>
       </c>
       <c r="B22">
-        <v>5.615966796875</v>
+        <v>0.97235107421875</v>
       </c>
       <c r="C22">
-        <v>-5.2982177734375</v>
+        <v>16.9237670898438</v>
       </c>
       <c r="D22">
-        <v>-11.5888671875</v>
+        <v>15.2864379882813</v>
       </c>
       <c r="E22">
-        <v>692.109985351563</v>
+        <v>722.390014648438</v>
       </c>
       <c r="F22">
-        <v>695.77001953125</v>
+        <v>724.669982910156</v>
       </c>
       <c r="G22">
-        <v>680.051208496094</v>
+        <v>720.330017089844</v>
       </c>
       <c r="H22">
-        <v>687.989990234375</v>
+        <v>720.869995117188</v>
       </c>
       <c r="I22">
-        <v>690.9306640625</v>
+        <v>724.498474121094</v>
       </c>
       <c r="J22">
-        <v>681.263366699219</v>
+        <v>718.993835449219</v>
       </c>
       <c r="K22">
-        <v>50540400</v>
+        <v>26243100</v>
       </c>
       <c r="L22">
-        <v>-2.08857083320618</v>
+        <v>-1.02761697769165</v>
       </c>
       <c r="M22">
-        <v>88.9701538085938</v>
+        <v>63.5033950805664</v>
       </c>
       <c r="N22">
-        <v>2.25866198539734</v>
+        <v>4.0243992805481</v>
       </c>
       <c r="O22" t="s">
         <v>1</v>
       </c>
       <c r="P22">
-        <v>67.7133255004883</v>
+        <v>9.99762535095215</v>
       </c>
       <c r="Q22">
-        <v>682.060668945313</v>
+        <v>719.53515625</v>
       </c>
       <c r="R22">
-        <v>685.576721191406</v>
+        <v>710.855163574219</v>
       </c>
       <c r="S22">
-        <v>695.608276367188</v>
+        <v>706.193542480469</v>
       </c>
       <c r="T22">
-        <v>-4.83935546875</v>
+        <v>-0.1715087890625</v>
       </c>
       <c r="U22">
-        <v>1.212158203125</v>
+        <v>-1.336181640625</v>
       </c>
       <c r="V22">
-        <v>9.66729736328125</v>
+        <v>5.504638671875</v>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="1">
-        <v>46233</v>
+      <c r="A23" s="2">
+        <v>46241</v>
       </c>
       <c r="B23">
-        <v>0.4974365234375</v>
+        <v>4.0394287109375</v>
       </c>
       <c r="C23">
-        <v>-9.81195068359375</v>
+        <v>18.4527587890625</v>
       </c>
       <c r="D23">
-        <v>-15.7636108398438</v>
+        <v>14.3407592773438</v>
       </c>
       <c r="E23">
-        <v>674.760009765625</v>
+        <v>720.150024414063</v>
       </c>
       <c r="F23">
-        <v>685.119995117188</v>
+        <v>723.630004882813</v>
       </c>
       <c r="G23">
-        <v>673.299987792969</v>
+        <v>716.510009765625</v>
       </c>
       <c r="H23">
-        <v>683.549987792969</v>
+        <v>723.030029296875</v>
       </c>
       <c r="I23">
-        <v>687.009155273438</v>
+        <v>726.10888671875</v>
       </c>
       <c r="J23">
-        <v>678.221374511719</v>
+        <v>718.251037597656</v>
       </c>
       <c r="K23">
-        <v>66753600</v>
+        <v>31070300</v>
       </c>
       <c r="L23">
-        <v>-2.08381009101868</v>
+        <v>-0.726187586784363</v>
       </c>
       <c r="M23">
-        <v>87.0050048828125</v>
+        <v>61.0466346740723</v>
       </c>
       <c r="N23">
-        <v>-12.9949884414673</v>
+        <v>-0.528325259685516</v>
       </c>
       <c r="O23" t="s">
         <v>1</v>
       </c>
       <c r="P23">
-        <v>68.3619155883789</v>
+        <v>26.1653099060059</v>
       </c>
       <c r="Q23">
-        <v>677.404541015625</v>
+        <v>717.619018554688</v>
       </c>
       <c r="R23">
-        <v>684.794189453125</v>
+        <v>707.809143066406</v>
       </c>
       <c r="S23">
-        <v>696.5146484375</v>
+        <v>704.476501464844</v>
       </c>
       <c r="T23">
-        <v>1.88916015625</v>
+        <v>2.4788818359375</v>
       </c>
       <c r="U23">
-        <v>4.92138671875</v>
+        <v>1.74102783203125</v>
       </c>
       <c r="V23">
-        <v>8.78778076171875</v>
+        <v>7.85784912109375</v>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="1">
-        <v>46232</v>
+      <c r="A24" s="2">
+        <v>46240</v>
       </c>
       <c r="B24">
-        <v>-11.2006225585938</v>
+        <v>5.7655029296875</v>
       </c>
       <c r="C24">
-        <v>-15.3350219726563</v>
+        <v>17.0516967773438</v>
       </c>
       <c r="D24">
-        <v>-19.4429321289063</v>
+        <v>11.1168212890625</v>
       </c>
       <c r="E24">
-        <v>675.510009765625</v>
+        <v>710.820007324219</v>
       </c>
       <c r="F24">
-        <v>680.049987792969</v>
+        <v>719.320007324219</v>
       </c>
       <c r="G24">
-        <v>661.140014648438</v>
+        <v>708.5</v>
       </c>
       <c r="H24">
-        <v>661.72998046875</v>
+        <v>714.650024414063</v>
       </c>
       <c r="I24">
-        <v>670.015625</v>
+        <v>718.173400878906</v>
       </c>
       <c r="J24">
-        <v>656.316345214844</v>
+        <v>708.951232910156</v>
       </c>
       <c r="K24">
-        <v>57233200</v>
+        <v>33035800</v>
       </c>
       <c r="L24">
-        <v>-1.9204740524292</v>
+        <v>-0.627615809440613</v>
       </c>
       <c r="M24">
-        <v>99.9999923706055</v>
+        <v>61.3708724975586</v>
       </c>
       <c r="N24">
-        <v>3.20350408554077</v>
+        <v>-10.5575513839722</v>
       </c>
       <c r="O24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P24">
-        <v>-68.9146041870117</v>
+        <v>-23.3668766021729</v>
       </c>
       <c r="Q24">
-        <v>671.892639160156</v>
+        <v>712.781005859375</v>
       </c>
       <c r="R24">
-        <v>685.085021972656</v>
+        <v>703.359313964844</v>
       </c>
       <c r="S24">
-        <v>697.902770996094</v>
+        <v>702.144226074219</v>
       </c>
       <c r="T24">
-        <v>-10.0343627929688</v>
+        <v>-1.1466064453125</v>
       </c>
       <c r="U24">
-        <v>-4.82366943359375</v>
+        <v>0.45123291015625</v>
       </c>
       <c r="V24">
-        <v>13.6992797851563</v>
+        <v>9.22216796875</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="1">
-        <v>46231</v>
+      <c r="A25" s="2">
+        <v>46239</v>
       </c>
       <c r="B25">
-        <v>-9.48968505859375</v>
+        <v>13.2140502929688</v>
       </c>
       <c r="C25">
-        <v>-12.2387084960938</v>
+        <v>17.2907104492188</v>
       </c>
       <c r="D25">
-        <v>-15.5038452148438</v>
+        <v>8.81109619140625</v>
       </c>
       <c r="E25">
-        <v>676.22998046875</v>
+        <v>726.25</v>
       </c>
       <c r="F25">
-        <v>679.400024414063</v>
+        <v>728.539978027344</v>
       </c>
       <c r="G25">
-        <v>667.880004882813</v>
+        <v>716.919982910156</v>
       </c>
       <c r="H25">
-        <v>675.489990234375</v>
+        <v>717.299987792969</v>
       </c>
       <c r="I25">
-        <v>681.398559570313</v>
+        <v>722.862182617188</v>
       </c>
       <c r="J25">
-        <v>669.311828613281</v>
+        <v>712.977844238281</v>
       </c>
       <c r="K25">
-        <v>51398700</v>
+        <v>33540100</v>
       </c>
       <c r="L25">
-        <v>-0.783804774284363</v>
+        <v>-0.500950396060944</v>
       </c>
       <c r="M25">
-        <v>96.8959274291992</v>
+        <v>68.6149291992188</v>
       </c>
       <c r="N25">
-        <v>5.64116907119751</v>
+        <v>15.4603137969971</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>-45.0695037841797</v>
+        <v>28.8229656219482</v>
       </c>
       <c r="Q25">
-        <v>681.100524902344</v>
+        <v>711.650634765625</v>
       </c>
       <c r="R25">
-        <v>691.612365722656</v>
+        <v>700.618591308594</v>
       </c>
       <c r="S25">
-        <v>701.984680175781</v>
+        <v>700.785400390625</v>
       </c>
       <c r="T25">
-        <v>1.99853515625</v>
+        <v>-5.67779541015625</v>
       </c>
       <c r="U25">
-        <v>1.43182373046875</v>
+        <v>-3.942138671875</v>
       </c>
       <c r="V25">
-        <v>12.0867309570313</v>
+        <v>9.88433837890625</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="1">
-        <v>46230</v>
+      <c r="A26" s="2">
+        <v>46238</v>
       </c>
       <c r="B26">
-        <v>-10.3001098632813</v>
+        <v>20.4347534179688</v>
       </c>
       <c r="C26">
-        <v>-11.3073120117188</v>
+        <v>12.6027221679688</v>
       </c>
       <c r="D26">
-        <v>-12.7749633789063</v>
+        <v>3.1591796875</v>
       </c>
       <c r="E26">
-        <v>691.679992675781</v>
+        <v>708.159973144531</v>
       </c>
       <c r="F26">
-        <v>692.299987792969</v>
+        <v>725.659973144531</v>
       </c>
       <c r="G26">
-        <v>675.945007324219</v>
+        <v>707.530029296875</v>
       </c>
       <c r="H26">
-        <v>682.119995117188</v>
+        <v>723.849975585938</v>
       </c>
       <c r="I26">
-        <v>687.197937011719</v>
+        <v>724.495361328125</v>
       </c>
       <c r="J26">
-        <v>676.772521972656</v>
+        <v>715.428039550781</v>
       </c>
       <c r="K26">
-        <v>42681400</v>
+        <v>59778600</v>
       </c>
       <c r="L26">
-        <v>-0.777614057064056</v>
+        <v>-0.300473153591156</v>
       </c>
       <c r="M26">
-        <v>91.7217483520508</v>
+        <v>59.4272842407227</v>
       </c>
       <c r="N26">
-        <v>28.3568496704102</v>
+        <v>-21.2858924865723</v>
       </c>
       <c r="O26" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P26">
-        <v>-35.6940422058105</v>
+        <v>100.000007629395</v>
       </c>
       <c r="Q26">
-        <v>686.793579101563</v>
+        <v>705.591552734375</v>
       </c>
       <c r="R26">
-        <v>696.032958984375</v>
+        <v>695.908142089844</v>
       </c>
       <c r="S26">
-        <v>705.08837890625</v>
+        <v>698.772827148438</v>
       </c>
       <c r="T26">
-        <v>-5.10205078125</v>
+        <v>-1.16461181640625</v>
       </c>
       <c r="U26">
-        <v>0.8275146484375</v>
+        <v>7.89801025390625</v>
       </c>
       <c r="V26">
-        <v>10.4254150390625</v>
+        <v>9.06732177734375</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="1">
-        <v>46227</v>
+      <c r="A27" s="2">
+        <v>46237</v>
       </c>
       <c r="B27">
-        <v>-8.69158935546875</v>
+        <v>11.339599609375</v>
       </c>
       <c r="C27">
-        <v>-9.875</v>
+        <v>0.62603759765625</v>
       </c>
       <c r="D27">
-        <v>-11.1927490234375</v>
+        <v>-6.712646484375</v>
       </c>
       <c r="E27">
-        <v>690.409973144531</v>
+        <v>688.299987792969</v>
       </c>
       <c r="F27">
-        <v>692.630004882813</v>
+        <v>701.590026855469</v>
       </c>
       <c r="G27">
-        <v>682.47998046875</v>
+        <v>685.820007324219</v>
       </c>
       <c r="H27">
-        <v>684.22998046875</v>
+        <v>700.070007324219</v>
       </c>
       <c r="I27">
-        <v>690.563537597656</v>
+        <v>701.723510742188</v>
       </c>
       <c r="J27">
-        <v>679.935974121094</v>
+        <v>691.503540039063</v>
       </c>
       <c r="K27">
-        <v>42876600</v>
+        <v>44965000</v>
       </c>
       <c r="L27">
-        <v>-0.775710344314575</v>
+        <v>-0.909996390342712</v>
       </c>
       <c r="M27">
-        <v>71.4583969116211</v>
+        <v>75.4976272583008</v>
       </c>
       <c r="N27">
-        <v>26.3548107147217</v>
+        <v>-15.1427478790283</v>
       </c>
       <c r="O27" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P27">
-        <v>-63.8044128417969</v>
+        <v>66.5761184692383</v>
       </c>
       <c r="Q27">
-        <v>691.569458007813</v>
+        <v>689.914428710938</v>
       </c>
       <c r="R27">
-        <v>699.823181152344</v>
+        <v>688.366577148438</v>
       </c>
       <c r="S27">
-        <v>707.758605957031</v>
+        <v>695.902160644531</v>
       </c>
       <c r="T27">
-        <v>-2.06646728515625</v>
+        <v>0.13348388671875</v>
       </c>
       <c r="U27">
-        <v>-2.54400634765625</v>
+        <v>5.68353271484375</v>
       </c>
       <c r="V27">
-        <v>10.6275634765625</v>
+        <v>10.219970703125</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="1">
-        <v>46226</v>
+      <c r="A28" s="2">
+        <v>46234</v>
       </c>
       <c r="B28">
-        <v>-3.48541259765625</v>
+        <v>5.615966796875</v>
       </c>
       <c r="C28">
-        <v>-8.06353759765625</v>
+        <v>-5.2982177734375</v>
       </c>
       <c r="D28">
-        <v>-8.079833984375</v>
+        <v>-11.5888671875</v>
       </c>
       <c r="E28">
-        <v>694.669982910156</v>
+        <v>692.109985351563</v>
       </c>
       <c r="F28">
-        <v>698.659973144531</v>
+        <v>695.77001953125</v>
       </c>
       <c r="G28">
-        <v>687.789978027344</v>
+        <v>680.051208496094</v>
       </c>
       <c r="H28">
-        <v>691.960021972656</v>
+        <v>687.989990234375</v>
       </c>
       <c r="I28">
-        <v>696.182250976563</v>
+        <v>690.9306640625</v>
       </c>
       <c r="J28">
-        <v>686.057800292969</v>
+        <v>681.263366699219</v>
       </c>
       <c r="K28">
-        <v>44028500</v>
+        <v>50540400</v>
       </c>
       <c r="L28">
-        <v>-0.707615435123444</v>
+        <v>-2.08857083320618</v>
       </c>
       <c r="M28">
-        <v>56.5537605285645</v>
+        <v>88.9701538085938</v>
       </c>
       <c r="N28">
-        <v>7.45290517807007</v>
+        <v>2.25866198539734</v>
       </c>
       <c r="O28" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P28">
-        <v>-56.6292991638184</v>
+        <v>67.7133255004883</v>
       </c>
       <c r="Q28">
-        <v>698.227111816406</v>
+        <v>682.060668945313</v>
       </c>
       <c r="R28">
-        <v>704.183776855469</v>
+        <v>685.576721191406</v>
       </c>
       <c r="S28">
-        <v>710.521728515625</v>
+        <v>695.608276367188</v>
       </c>
       <c r="T28">
-        <v>-2.47772216796875</v>
+        <v>-4.83935546875</v>
       </c>
       <c r="U28">
-        <v>-1.732177734375</v>
+        <v>1.212158203125</v>
       </c>
       <c r="V28">
-        <v>10.1244506835938</v>
+        <v>9.66729736328125</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="1">
-        <v>46225</v>
+      <c r="A29" s="2">
+        <v>46233</v>
       </c>
       <c r="B29">
-        <v>3.01220703125</v>
+        <v>0.4974365234375</v>
       </c>
       <c r="C29">
-        <v>-5.4625244140625</v>
+        <v>-9.81195068359375</v>
       </c>
       <c r="D29">
-        <v>-6.10992431640625</v>
+        <v>-15.7636108398438</v>
       </c>
       <c r="E29">
-        <v>703.619995117188</v>
+        <v>674.760009765625</v>
       </c>
       <c r="F29">
-        <v>709.650024414063</v>
+        <v>685.119995117188</v>
       </c>
       <c r="G29">
-        <v>703.619995117188</v>
+        <v>673.299987792969</v>
       </c>
       <c r="H29">
-        <v>705.349975585938</v>
+        <v>683.549987792969</v>
       </c>
       <c r="I29">
-        <v>708.769348144531</v>
+        <v>687.009155273438</v>
       </c>
       <c r="J29">
-        <v>701.754638671875</v>
+        <v>678.221374511719</v>
       </c>
       <c r="K29">
-        <v>23692100</v>
+        <v>66753600</v>
       </c>
       <c r="L29">
-        <v>-0.678091883659363</v>
+        <v>-2.08381009101868</v>
       </c>
       <c r="M29">
-        <v>52.6312065124512</v>
+        <v>87.0050048828125</v>
       </c>
       <c r="N29">
-        <v>-15.308910369873</v>
+        <v>-12.9949884414673</v>
       </c>
       <c r="O29" t="s">
         <v>1</v>
       </c>
       <c r="P29">
-        <v>10.9916353225708</v>
+        <v>68.3619155883789</v>
       </c>
       <c r="Q29">
-        <v>705.042114257813</v>
+        <v>677.404541015625</v>
       </c>
       <c r="R29">
-        <v>707.900085449219</v>
+        <v>684.794189453125</v>
       </c>
       <c r="S29">
-        <v>712.692932128906</v>
+        <v>696.5146484375</v>
       </c>
       <c r="T29">
-        <v>-0.88067626953125</v>
+        <v>1.88916015625</v>
       </c>
       <c r="U29">
-        <v>-1.8653564453125</v>
+        <v>4.92138671875</v>
       </c>
       <c r="V29">
-        <v>7.01470947265625</v>
+        <v>8.78778076171875</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="1">
-        <v>46224</v>
+      <c r="A30" s="2">
+        <v>46232</v>
       </c>
       <c r="B30">
-        <v>0.6416015625</v>
+        <v>-11.2006225585938</v>
       </c>
       <c r="C30">
-        <v>-6.202392578125</v>
+        <v>-15.3350219726563</v>
       </c>
       <c r="D30">
-        <v>-7.814697265625</v>
+        <v>-19.4429321289063</v>
       </c>
       <c r="E30">
-        <v>706.570007324219</v>
+        <v>675.510009765625</v>
       </c>
       <c r="F30">
-        <v>710.049987792969</v>
+        <v>680.049987792969</v>
       </c>
       <c r="G30">
-        <v>702.799987792969</v>
+        <v>661.140014648438</v>
       </c>
       <c r="H30">
-        <v>708.969970703125</v>
+        <v>661.72998046875</v>
       </c>
       <c r="I30">
-        <v>712.483276367188</v>
+        <v>670.015625</v>
       </c>
       <c r="J30">
-        <v>705.233276367188</v>
+        <v>656.316345214844</v>
       </c>
       <c r="K30">
-        <v>33728300</v>
+        <v>57233200</v>
       </c>
       <c r="L30">
-        <v>-0.954281747341156</v>
+        <v>-1.9204740524292</v>
       </c>
       <c r="M30">
-        <v>62.1449165344238</v>
+        <v>99.9999923706055</v>
       </c>
       <c r="N30">
-        <v>-6.62933874130249</v>
+        <v>3.20350408554077</v>
       </c>
       <c r="O30" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P30">
-        <v>48.3449096679688</v>
+        <v>-68.9146041870117</v>
       </c>
       <c r="Q30">
-        <v>704.79150390625</v>
+        <v>671.892639160156</v>
       </c>
       <c r="R30">
-        <v>708.46826171875</v>
+        <v>685.085021972656</v>
       </c>
       <c r="S30">
-        <v>713.447265625</v>
+        <v>697.902770996094</v>
       </c>
       <c r="T30">
-        <v>2.43328857421875</v>
+        <v>-10.0343627929688</v>
       </c>
       <c r="U30">
-        <v>2.43328857421875</v>
+        <v>-4.82366943359375</v>
       </c>
       <c r="V30">
-        <v>7.25</v>
+        <v>13.6992797851563</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="1">
-        <v>46223</v>
+      <c r="A31" s="2">
+        <v>46231</v>
       </c>
       <c r="B31">
-        <v>-8.39520263671875</v>
+        <v>-9.48968505859375</v>
       </c>
       <c r="C31">
-        <v>-8.765380859375</v>
+        <v>-12.2387084960938</v>
       </c>
       <c r="D31">
-        <v>-9.8062744140625</v>
+        <v>-15.5038452148438</v>
       </c>
       <c r="E31">
-        <v>702.159973144531</v>
+        <v>676.22998046875</v>
       </c>
       <c r="F31">
-        <v>705.799987792969</v>
+        <v>679.400024414063</v>
       </c>
       <c r="G31">
-        <v>695.510009765625</v>
+        <v>667.880004882813</v>
       </c>
       <c r="H31">
-        <v>696.059997558594</v>
+        <v>675.489990234375</v>
       </c>
       <c r="I31">
-        <v>703.789184570313</v>
+        <v>681.398559570313</v>
       </c>
       <c r="J31">
-        <v>693.406494140625</v>
+        <v>669.311828613281</v>
       </c>
       <c r="K31">
-        <v>29687500</v>
+        <v>51398700</v>
       </c>
       <c r="L31">
-        <v>-0.905709385871887</v>
+        <v>-0.783804774284363</v>
       </c>
       <c r="M31">
-        <v>66.5572204589844</v>
+        <v>96.8959274291992</v>
       </c>
       <c r="N31">
-        <v>22.5973968505859</v>
+        <v>5.64116907119751</v>
       </c>
       <c r="O31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P31">
-        <v>-6.00122213363647</v>
+        <v>-45.0695037841797</v>
       </c>
       <c r="Q31">
-        <v>700.701416015625</v>
+        <v>681.100524902344</v>
       </c>
       <c r="R31">
-        <v>708.291809082031</v>
+        <v>691.612365722656</v>
       </c>
       <c r="S31">
-        <v>713.96923828125</v>
+        <v>701.984680175781</v>
       </c>
       <c r="T31">
-        <v>-2.01080322265625</v>
+        <v>1.99853515625</v>
       </c>
       <c r="U31">
-        <v>-2.103515625</v>
+        <v>1.43182373046875</v>
       </c>
       <c r="V31">
-        <v>10.3826904296875</v>
+        <v>12.0867309570313</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="1">
-        <v>46220</v>
+      <c r="A32" s="2">
+        <v>46230</v>
       </c>
       <c r="B32">
-        <v>-9.927001953125</v>
+        <v>-10.3001098632813</v>
       </c>
       <c r="C32">
-        <v>-7.9847412109375</v>
+        <v>-11.3073120117188</v>
       </c>
       <c r="D32">
-        <v>-7.42694091796875</v>
+        <v>-12.7749633789063</v>
       </c>
       <c r="E32">
-        <v>691.650024414063</v>
+        <v>691.679992675781</v>
       </c>
       <c r="F32">
-        <v>702.299987792969</v>
+        <v>692.299987792969</v>
       </c>
       <c r="G32">
-        <v>686.760009765625</v>
+        <v>675.945007324219</v>
       </c>
       <c r="H32">
-        <v>695.330017089844</v>
+        <v>682.119995117188</v>
       </c>
       <c r="I32">
-        <v>701.341003417969</v>
+        <v>687.197937011719</v>
       </c>
       <c r="J32">
-        <v>688.661193847656</v>
+        <v>676.772521972656</v>
       </c>
       <c r="K32">
-        <v>54109200</v>
+        <v>42681400</v>
       </c>
       <c r="L32">
-        <v>-1.21904349327087</v>
+        <v>-0.777614057064056</v>
       </c>
       <c r="M32">
-        <v>54.2892608642578</v>
+        <v>91.7217483520508</v>
       </c>
       <c r="N32">
-        <v>8.37738990783691</v>
+        <v>28.3568496704102</v>
       </c>
       <c r="O32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P32">
-        <v>-64.7480239868164</v>
+        <v>-35.6940422058105</v>
       </c>
       <c r="Q32">
-        <v>703.639892578125</v>
+        <v>686.793579101563</v>
       </c>
       <c r="R32">
-        <v>711.3662109375</v>
+        <v>696.032958984375</v>
       </c>
       <c r="S32">
-        <v>715.791137695313</v>
+        <v>705.08837890625</v>
       </c>
       <c r="T32">
-        <v>-0.958984375</v>
+        <v>-5.10205078125</v>
       </c>
       <c r="U32">
-        <v>1.90118408203125</v>
+        <v>0.8275146484375</v>
       </c>
       <c r="V32">
-        <v>12.6798095703125</v>
+        <v>10.4254150390625</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="1">
-        <v>46219</v>
+      <c r="A33" s="2">
+        <v>46227</v>
       </c>
       <c r="B33">
-        <v>-5.863037109375</v>
+        <v>-8.69158935546875</v>
       </c>
       <c r="C33">
-        <v>-2.36517333984375</v>
+        <v>-9.875</v>
       </c>
       <c r="D33">
-        <v>-3.09661865234375</v>
+        <v>-11.1927490234375</v>
       </c>
       <c r="E33">
-        <v>712.010009765625</v>
+        <v>690.409973144531</v>
       </c>
       <c r="F33">
-        <v>713.598999023438</v>
+        <v>692.630004882813</v>
       </c>
       <c r="G33">
-        <v>702.609985351563</v>
+        <v>682.47998046875</v>
       </c>
       <c r="H33">
-        <v>705.940002441406</v>
+        <v>684.22998046875</v>
       </c>
       <c r="I33">
-        <v>712.521850585938</v>
+        <v>690.563537597656</v>
       </c>
       <c r="J33">
-        <v>701.248962402344</v>
+        <v>679.935974121094</v>
       </c>
       <c r="K33">
-        <v>39402000</v>
+        <v>42876600</v>
       </c>
       <c r="L33">
-        <v>-1.98428201675415</v>
+        <v>-0.775710344314575</v>
       </c>
       <c r="M33">
-        <v>50.0927925109863</v>
+        <v>71.4583969116211</v>
       </c>
       <c r="N33">
-        <v>7.75767660140991</v>
+        <v>26.3548107147217</v>
       </c>
       <c r="O33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P33">
-        <v>-43.6580963134766</v>
+        <v>-63.8044128417969</v>
       </c>
       <c r="Q33">
-        <v>712.182556152344</v>
+        <v>691.569458007813</v>
       </c>
       <c r="R33">
-        <v>715.892822265625</v>
+        <v>699.823181152344</v>
       </c>
       <c r="S33">
-        <v>718.15576171875</v>
+        <v>707.758605957031</v>
       </c>
       <c r="T33">
-        <v>-1.0771484375</v>
+        <v>-2.06646728515625</v>
       </c>
       <c r="U33">
-        <v>-1.36102294921875</v>
+        <v>-2.54400634765625</v>
       </c>
       <c r="V33">
-        <v>11.2728881835938</v>
+        <v>10.6275634765625</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="1">
-        <v>46218</v>
+      <c r="A34" s="2">
+        <v>46226</v>
       </c>
       <c r="B34">
-        <v>-1.943359375</v>
+        <v>-3.48541259765625</v>
       </c>
       <c r="C34">
-        <v>0.40814208984375</v>
+        <v>-8.06353759765625</v>
       </c>
       <c r="D34">
-        <v>-0.0054931640625</v>
+        <v>-8.079833984375</v>
       </c>
       <c r="E34">
-        <v>723.849975585938</v>
+        <v>694.669982910156</v>
       </c>
       <c r="F34">
-        <v>724.359985351563</v>
+        <v>698.659973144531</v>
       </c>
       <c r="G34">
-        <v>710.22998046875</v>
+        <v>687.789978027344</v>
       </c>
       <c r="H34">
-        <v>717.739990234375</v>
+        <v>691.960021972656</v>
       </c>
       <c r="I34">
-        <v>721.251037597656</v>
+        <v>696.182250976563</v>
       </c>
       <c r="J34">
-        <v>712.604736328125</v>
+        <v>686.057800292969</v>
       </c>
       <c r="K34">
-        <v>32627500</v>
+        <v>44028500</v>
       </c>
       <c r="L34">
-        <v>-1.41428053379059</v>
+        <v>-0.707615435123444</v>
       </c>
       <c r="M34">
-        <v>46.4865188598633</v>
+        <v>56.5537605285645</v>
       </c>
       <c r="N34">
-        <v>-4.76508235931396</v>
+        <v>7.45290517807007</v>
       </c>
       <c r="O34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P34">
-        <v>-2.18429470062256</v>
+        <v>-56.6292991638184</v>
       </c>
       <c r="Q34">
-        <v>717.8037109375</v>
+        <v>698.227111816406</v>
       </c>
       <c r="R34">
-        <v>718.531005859375</v>
+        <v>704.183776855469</v>
       </c>
       <c r="S34">
-        <v>719.552307128906</v>
+        <v>710.521728515625</v>
       </c>
       <c r="T34">
-        <v>-3.10894775390625</v>
+        <v>-2.47772216796875</v>
       </c>
       <c r="U34">
-        <v>2.374755859375</v>
+        <v>-1.732177734375</v>
       </c>
       <c r="V34">
-        <v>8.64630126953125</v>
+        <v>10.1244506835938</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="1">
-        <v>46217</v>
+      <c r="A35" s="2">
+        <v>46225</v>
       </c>
       <c r="B35">
-        <v>0.21160888671875</v>
+        <v>3.01220703125</v>
       </c>
       <c r="C35">
-        <v>-1.59527587890625</v>
+        <v>-5.4625244140625</v>
       </c>
       <c r="D35">
-        <v>0.46612548828125</v>
+        <v>-6.10992431640625</v>
       </c>
       <c r="E35">
-        <v>720.219970703125</v>
+        <v>703.619995117188</v>
       </c>
       <c r="F35">
-        <v>722.289978027344</v>
+        <v>709.650024414063</v>
       </c>
       <c r="G35">
-        <v>714.340026855469</v>
+        <v>703.619995117188</v>
       </c>
       <c r="H35">
-        <v>719.690002441406</v>
+        <v>705.349975585938</v>
       </c>
       <c r="I35">
-        <v>723.544555664063</v>
+        <v>708.769348144531</v>
       </c>
       <c r="J35">
-        <v>716.334533691406</v>
+        <v>701.754638671875</v>
       </c>
       <c r="K35">
-        <v>29448100</v>
+        <v>23692100</v>
       </c>
       <c r="L35">
-        <v>-0.94570779800415</v>
+        <v>-0.678091883659363</v>
       </c>
       <c r="M35">
-        <v>48.8124732971191</v>
+        <v>52.6312065124512</v>
       </c>
       <c r="N35">
-        <v>-5.16571569442749</v>
+        <v>-15.308910369873</v>
       </c>
       <c r="O35" t="s">
         <v>1</v>
       </c>
       <c r="P35">
-        <v>5.93372297286987</v>
+        <v>10.9916353225708</v>
       </c>
       <c r="Q35">
-        <v>718.3955078125</v>
+        <v>705.042114257813</v>
       </c>
       <c r="R35">
-        <v>718.438903808594</v>
+        <v>707.900085449219</v>
       </c>
       <c r="S35">
-        <v>719.708923339844</v>
+        <v>712.692932128906</v>
       </c>
       <c r="T35">
-        <v>1.25457763671875</v>
+        <v>-0.88067626953125</v>
       </c>
       <c r="U35">
-        <v>1.9945068359375</v>
+        <v>-1.8653564453125</v>
       </c>
       <c r="V35">
-        <v>7.21002197265625</v>
+        <v>7.01470947265625</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="1">
-        <v>46216</v>
+      <c r="A36" s="2">
+        <v>46224</v>
       </c>
       <c r="B36">
-        <v>-0.3555908203125</v>
+        <v>0.6416015625</v>
       </c>
       <c r="C36">
-        <v>-3.0672607421875</v>
+        <v>-6.202392578125</v>
       </c>
       <c r="D36">
-        <v>-1.38330078125</v>
+        <v>-7.814697265625</v>
       </c>
       <c r="E36">
-        <v>717.719970703125</v>
+        <v>706.570007324219</v>
       </c>
       <c r="F36">
-        <v>718.739990234375</v>
+        <v>710.049987792969</v>
       </c>
       <c r="G36">
-        <v>710.080017089844</v>
+        <v>702.799987792969</v>
       </c>
       <c r="H36">
-        <v>711.739990234375</v>
+        <v>708.969970703125</v>
       </c>
       <c r="I36">
-        <v>717.577209472656</v>
+        <v>712.483276367188</v>
       </c>
       <c r="J36">
-        <v>707.793212890625</v>
+        <v>705.233276367188</v>
       </c>
       <c r="K36">
-        <v>36552300</v>
+        <v>33728300</v>
       </c>
       <c r="L36">
-        <v>-0.0714227557182312</v>
+        <v>-0.954281747341156</v>
       </c>
       <c r="M36">
-        <v>51.4713363647461</v>
+        <v>62.1449165344238</v>
       </c>
       <c r="N36">
-        <v>4.72496747970581</v>
+        <v>-6.62933874130249</v>
       </c>
       <c r="O36" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P36">
-        <v>-42.1362648010254</v>
+        <v>48.3449096679688</v>
       </c>
       <c r="Q36">
-        <v>716.920593261719</v>
+        <v>704.79150390625</v>
       </c>
       <c r="R36">
-        <v>718.116577148438</v>
+        <v>708.46826171875</v>
       </c>
       <c r="S36">
-        <v>719.618469238281</v>
+        <v>713.447265625</v>
       </c>
       <c r="T36">
-        <v>-1.16278076171875</v>
+        <v>2.43328857421875</v>
       </c>
       <c r="U36">
-        <v>-2.28680419921875</v>
+        <v>2.43328857421875</v>
       </c>
       <c r="V36">
-        <v>9.78399658203125</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="1">
-        <v>46213</v>
+      <c r="A37" s="2">
+        <v>46223</v>
       </c>
       <c r="B37">
-        <v>4.54119873046875</v>
+        <v>-8.39520263671875</v>
       </c>
       <c r="C37">
-        <v>1.09893798828125</v>
+        <v>-8.765380859375</v>
       </c>
       <c r="D37">
-        <v>-0.62530517578125</v>
+        <v>-9.8062744140625</v>
       </c>
       <c r="E37">
-        <v>720.700012207031</v>
+        <v>702.159973144531</v>
       </c>
       <c r="F37">
-        <v>726.390014648438</v>
+        <v>705.799987792969</v>
       </c>
       <c r="G37">
-        <v>717</v>
+        <v>695.510009765625</v>
       </c>
       <c r="H37">
-        <v>725.510009765625</v>
+        <v>696.059997558594</v>
       </c>
       <c r="I37">
-        <v>728.048034667969</v>
+        <v>703.789184570313</v>
       </c>
       <c r="J37">
-        <v>721.283996582031</v>
+        <v>693.406494140625</v>
       </c>
       <c r="K37">
-        <v>26415900</v>
+        <v>29687500</v>
       </c>
       <c r="L37">
-        <v>-0.166184201836586</v>
+        <v>-0.905709385871887</v>
       </c>
       <c r="M37">
-        <v>49.1490592956543</v>
+        <v>66.5572204589844</v>
       </c>
       <c r="N37">
-        <v>-9.55446624755859</v>
+        <v>22.5973968505859</v>
       </c>
       <c r="O37" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P37">
-        <v>29.1831836700439</v>
+        <v>-6.00122213363647</v>
       </c>
       <c r="Q37">
-        <v>721.479248046875</v>
+        <v>700.701416015625</v>
       </c>
       <c r="R37">
-        <v>719.98193359375</v>
+        <v>708.291809082031</v>
       </c>
       <c r="S37">
-        <v>720.620422363281</v>
+        <v>713.96923828125</v>
       </c>
       <c r="T37">
-        <v>1.65802001953125</v>
+        <v>-2.01080322265625</v>
       </c>
       <c r="U37">
-        <v>4.28399658203125</v>
+        <v>-2.103515625</v>
       </c>
       <c r="V37">
-        <v>6.7640380859375</v>
+        <v>10.3826904296875</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="1">
-        <v>46212</v>
+      <c r="A38" s="2">
+        <v>46220</v>
       </c>
       <c r="B38">
-        <v>3.296630859375</v>
+        <v>-9.927001953125</v>
       </c>
       <c r="C38">
-        <v>-0.72021484375</v>
+        <v>-7.9847412109375</v>
       </c>
       <c r="D38">
-        <v>-2.30474853515625</v>
+        <v>-7.42694091796875</v>
       </c>
       <c r="E38">
-        <v>718.330017089844</v>
+        <v>691.650024414063</v>
       </c>
       <c r="F38">
-        <v>724.22998046875</v>
+        <v>702.299987792969</v>
       </c>
       <c r="G38">
-        <v>715.125</v>
+        <v>686.760009765625</v>
       </c>
       <c r="H38">
-        <v>723.280029296875</v>
+        <v>695.330017089844</v>
       </c>
       <c r="I38">
-        <v>726.686767578125</v>
+        <v>701.341003417969</v>
       </c>
       <c r="J38">
-        <v>719.118225097656</v>
+        <v>688.661193847656</v>
       </c>
       <c r="K38">
-        <v>33654700</v>
+        <v>54109200</v>
       </c>
       <c r="L38">
-        <v>-1.11665856838226</v>
+        <v>-1.21904349327087</v>
       </c>
       <c r="M38">
-        <v>54.3410568237305</v>
+        <v>54.2892608642578</v>
       </c>
       <c r="N38">
-        <v>-1.37647461891174</v>
+        <v>8.37738990783691</v>
       </c>
       <c r="O38" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P38">
-        <v>56.2780990600586</v>
+        <v>-64.7480239868164</v>
       </c>
       <c r="Q38">
-        <v>718.006164550781</v>
+        <v>703.639892578125</v>
       </c>
       <c r="R38">
-        <v>718.503051757813</v>
+        <v>711.3662109375</v>
       </c>
       <c r="S38">
-        <v>720.065307617188</v>
+        <v>715.791137695313</v>
       </c>
       <c r="T38">
-        <v>2.456787109375</v>
+        <v>-0.958984375</v>
       </c>
       <c r="U38">
-        <v>3.99322509765625</v>
+        <v>1.90118408203125</v>
       </c>
       <c r="V38">
-        <v>7.56854248046875</v>
+        <v>12.6798095703125</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="1">
-        <v>46211</v>
+      <c r="A39" s="2">
+        <v>46219</v>
       </c>
       <c r="B39">
-        <v>-4.7235107421875</v>
+        <v>-5.863037109375</v>
       </c>
       <c r="C39">
-        <v>-3.04364013671875</v>
+        <v>-2.36517333984375</v>
       </c>
       <c r="D39">
-        <v>-5.07476806640625</v>
+        <v>-3.09661865234375</v>
       </c>
       <c r="E39">
-        <v>704.950012207031</v>
+        <v>712.010009765625</v>
       </c>
       <c r="F39">
-        <v>712.259887695313</v>
+        <v>713.598999023438</v>
       </c>
       <c r="G39">
-        <v>700.909973144531</v>
+        <v>702.609985351563</v>
       </c>
       <c r="H39">
-        <v>711.440002441406</v>
+        <v>705.940002441406</v>
       </c>
       <c r="I39">
-        <v>715.620361328125</v>
+        <v>712.521850585938</v>
       </c>
       <c r="J39">
-        <v>704.994506835938</v>
+        <v>701.248962402344</v>
       </c>
       <c r="K39">
-        <v>35603100</v>
+        <v>39402000</v>
       </c>
       <c r="L39">
-        <v>-1.43523001670837</v>
+        <v>-1.98428201675415</v>
       </c>
       <c r="M39">
-        <v>55.0994873046875</v>
+        <v>50.0927925109863</v>
       </c>
       <c r="N39">
-        <v>-16.1432189941406</v>
+        <v>7.75767660140991</v>
       </c>
       <c r="O39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P39">
-        <v>-15.6323156356812</v>
+        <v>-43.6580963134766</v>
       </c>
       <c r="Q39">
-        <v>712.987182617188</v>
+        <v>712.182556152344</v>
       </c>
       <c r="R39">
-        <v>717.214111328125</v>
+        <v>715.892822265625</v>
       </c>
       <c r="S39">
-        <v>719.531494140625</v>
+        <v>718.15576171875</v>
       </c>
       <c r="T39">
-        <v>3.3604736328125</v>
+        <v>-1.0771484375</v>
       </c>
       <c r="U39">
-        <v>4.08453369140625</v>
+        <v>-1.36102294921875</v>
       </c>
       <c r="V39">
-        <v>10.6258544921875</v>
+        <v>11.2728881835938</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="1">
-        <v>46210</v>
+      <c r="A40" s="2">
+        <v>46218</v>
       </c>
       <c r="B40">
-        <v>-7.9444580078125</v>
+        <v>-1.943359375</v>
       </c>
       <c r="C40">
-        <v>-0.99530029296875</v>
+        <v>0.40814208984375</v>
       </c>
       <c r="D40">
-        <v>-5.45904541015625</v>
+        <v>-0.0054931640625</v>
       </c>
       <c r="E40">
-        <v>714.169982910156</v>
+        <v>723.849975585938</v>
       </c>
       <c r="F40">
-        <v>716.349975585938</v>
+        <v>724.359985351563</v>
       </c>
       <c r="G40">
-        <v>704.900024414063</v>
+        <v>710.22998046875</v>
       </c>
       <c r="H40">
-        <v>709.429992675781</v>
+        <v>717.739990234375</v>
       </c>
       <c r="I40">
-        <v>714.261169433594</v>
+        <v>721.251037597656</v>
       </c>
       <c r="J40">
-        <v>704.237060546875</v>
+        <v>712.604736328125</v>
       </c>
       <c r="K40">
-        <v>42483000</v>
+        <v>32627500</v>
       </c>
       <c r="L40">
-        <v>-2.93475341796875</v>
+        <v>-1.41428053379059</v>
       </c>
       <c r="M40">
-        <v>65.706657409668</v>
+        <v>46.4865188598633</v>
       </c>
       <c r="N40">
-        <v>-6.48241281509399</v>
+        <v>-4.76508235931396</v>
       </c>
       <c r="O40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P40">
-        <v>-38.1205101013184</v>
+        <v>-2.18429470062256</v>
       </c>
       <c r="Q40">
-        <v>715.312561035156</v>
+        <v>717.8037109375</v>
       </c>
       <c r="R40">
-        <v>718.993896484375</v>
+        <v>718.531005859375</v>
       </c>
       <c r="S40">
-        <v>720.435485839844</v>
+        <v>719.552307128906</v>
       </c>
       <c r="T40">
-        <v>-2.08880615234375</v>
+        <v>-3.10894775390625</v>
       </c>
       <c r="U40">
-        <v>-0.6629638671875</v>
+        <v>2.374755859375</v>
       </c>
       <c r="V40">
-        <v>10.0241088867188</v>
+        <v>8.64630126953125</v>
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="1">
-        <v>46209</v>
+      <c r="A41" s="2">
+        <v>46217</v>
       </c>
       <c r="B41">
-        <v>-2.8165283203125</v>
+        <v>0.21160888671875</v>
       </c>
       <c r="C41">
-        <v>0.947509765625</v>
+        <v>-1.59527587890625</v>
       </c>
       <c r="D41">
-        <v>-2.495361328125</v>
+        <v>0.46612548828125</v>
       </c>
       <c r="E41">
-        <v>719.929992675781</v>
+        <v>720.219970703125</v>
       </c>
       <c r="F41">
-        <v>726.080017089844</v>
+        <v>722.289978027344</v>
       </c>
       <c r="G41">
-        <v>718.450012207031</v>
+        <v>714.340026855469</v>
       </c>
       <c r="H41">
-        <v>722.820007324219</v>
+        <v>719.690002441406</v>
       </c>
       <c r="I41">
-        <v>729.223693847656</v>
+        <v>723.544555664063</v>
       </c>
       <c r="J41">
-        <v>718.437683105469</v>
+        <v>716.334533691406</v>
       </c>
       <c r="K41">
-        <v>30220400</v>
+        <v>29448100</v>
       </c>
       <c r="L41">
-        <v>-2.4647536277771</v>
+        <v>-0.94570779800415</v>
       </c>
       <c r="M41">
-        <v>70.2612838745117</v>
+        <v>48.8124732971191</v>
       </c>
       <c r="N41">
-        <v>3.65661525726318</v>
+        <v>-5.16571569442749</v>
       </c>
       <c r="O41" t="s">
         <v>1</v>
       </c>
       <c r="P41">
-        <v>18.3796253204346</v>
+        <v>5.93372297286987</v>
       </c>
       <c r="Q41">
-        <v>721.317932128906</v>
+        <v>718.3955078125</v>
       </c>
       <c r="R41">
-        <v>721.685180664063</v>
+        <v>718.438903808594</v>
       </c>
       <c r="S41">
-        <v>721.850463867188</v>
+        <v>719.708923339844</v>
       </c>
       <c r="T41">
-        <v>3.1436767578125</v>
+        <v>1.25457763671875</v>
       </c>
       <c r="U41">
-        <v>-0.0123291015625</v>
+        <v>1.9945068359375</v>
       </c>
       <c r="V41">
-        <v>10.7860107421875</v>
+        <v>7.21002197265625</v>
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="1">
-        <v>46205</v>
+      <c r="A42" s="2">
+        <v>46216</v>
       </c>
       <c r="B42">
-        <v>-3.747802734375</v>
+        <v>-0.3555908203125</v>
       </c>
       <c r="C42">
-        <v>-2.68170166015625</v>
+        <v>-3.0672607421875</v>
       </c>
       <c r="D42">
-        <v>-3.40606689453125</v>
+        <v>-1.38330078125</v>
       </c>
       <c r="E42">
-        <v>725.580017089844</v>
+        <v>717.719970703125</v>
       </c>
       <c r="F42">
-        <v>730.830017089844</v>
+        <v>718.739990234375</v>
       </c>
       <c r="G42">
-        <v>707.559997558594</v>
+        <v>710.080017089844</v>
       </c>
       <c r="H42">
-        <v>712.599975585938</v>
+        <v>711.739990234375</v>
       </c>
       <c r="I42">
-        <v>718.628479003906</v>
+        <v>717.577209472656</v>
       </c>
       <c r="J42">
-        <v>705.427856445313</v>
+        <v>707.793212890625</v>
       </c>
       <c r="K42">
-        <v>51086000</v>
+        <v>36552300</v>
       </c>
       <c r="L42">
-        <v>-2.74999117851257</v>
+        <v>-0.0714227557182312</v>
       </c>
       <c r="M42">
-        <v>67.7827301025391</v>
+        <v>51.4713363647461</v>
       </c>
       <c r="N42">
-        <v>14.6252498626709</v>
+        <v>4.72496747970581</v>
       </c>
       <c r="O42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P42">
-        <v>-52.3691177368164</v>
+        <v>-42.1362648010254</v>
       </c>
       <c r="Q42">
-        <v>719.125122070313</v>
+        <v>716.920593261719</v>
       </c>
       <c r="R42">
-        <v>720.899353027344</v>
+        <v>718.116577148438</v>
       </c>
       <c r="S42">
-        <v>721.46142578125</v>
+        <v>719.618469238281</v>
       </c>
       <c r="T42">
-        <v>-12.2015380859375</v>
+        <v>-1.16278076171875</v>
       </c>
       <c r="U42">
-        <v>-2.13214111328125</v>
+        <v>-2.28680419921875</v>
       </c>
       <c r="V42">
-        <v>13.2006225585938</v>
+        <v>9.78399658203125</v>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="1">
-        <v>46204</v>
+      <c r="A43" s="2">
+        <v>46213</v>
       </c>
       <c r="B43">
-        <v>5.48199462890625</v>
+        <v>4.54119873046875</v>
       </c>
       <c r="C43">
-        <v>1.29547119140625</v>
+        <v>1.09893798828125</v>
       </c>
       <c r="D43">
-        <v>1.181640625</v>
+        <v>-0.62530517578125</v>
       </c>
       <c r="E43">
-        <v>729.190002441406</v>
+        <v>720.700012207031</v>
       </c>
       <c r="F43">
-        <v>731.919982910156</v>
+        <v>726.390014648438</v>
       </c>
       <c r="G43">
-        <v>724.599975585938</v>
+        <v>717</v>
       </c>
       <c r="H43">
-        <v>725.169982910156</v>
+        <v>725.510009765625</v>
       </c>
       <c r="I43">
-        <v>731.202941894531</v>
+        <v>728.048034667969</v>
       </c>
       <c r="J43">
-        <v>721.92822265625</v>
+        <v>721.283996582031</v>
       </c>
       <c r="K43">
-        <v>40803700</v>
+        <v>26415900</v>
       </c>
       <c r="L43">
-        <v>-1.9528489112854</v>
+        <v>-0.166184201836586</v>
       </c>
       <c r="M43">
-        <v>59.134204864502</v>
+        <v>49.1490592956543</v>
       </c>
       <c r="N43">
-        <v>25.8970050811768</v>
+        <v>-9.55446624755859</v>
       </c>
       <c r="O43" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P43">
-        <v>-6.59338569641113</v>
+        <v>29.1831836700439</v>
       </c>
       <c r="Q43">
-        <v>726.038452148438</v>
+        <v>721.479248046875</v>
       </c>
       <c r="R43">
-        <v>723.370727539063</v>
+        <v>719.98193359375</v>
       </c>
       <c r="S43">
-        <v>722.493774414063</v>
+        <v>720.620422363281</v>
       </c>
       <c r="T43">
-        <v>-0.717041015625</v>
+        <v>1.65802001953125</v>
       </c>
       <c r="U43">
-        <v>-2.6717529296875</v>
+        <v>4.28399658203125</v>
       </c>
       <c r="V43">
-        <v>9.27471923828125</v>
+        <v>6.7640380859375</v>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="1">
-        <v>46203</v>
+      <c r="A44" s="2">
+        <v>46212</v>
       </c>
       <c r="B44">
-        <v>10.5760498046875</v>
+        <v>3.296630859375</v>
       </c>
       <c r="C44">
-        <v>1.1090087890625</v>
+        <v>-0.72021484375</v>
       </c>
       <c r="D44">
-        <v>2.15655517578125</v>
+        <v>-2.30474853515625</v>
       </c>
       <c r="E44">
-        <v>724.179992675781</v>
+        <v>718.330017089844</v>
       </c>
       <c r="F44">
-        <v>737.619995117188</v>
+        <v>724.22998046875</v>
       </c>
       <c r="G44">
-        <v>723.909973144531</v>
+        <v>715.125</v>
       </c>
       <c r="H44">
-        <v>736.400024414063</v>
+        <v>723.280029296875</v>
       </c>
       <c r="I44">
-        <v>740.130432128906</v>
+        <v>726.686767578125</v>
       </c>
       <c r="J44">
-        <v>729.166198730469</v>
+        <v>719.118225097656</v>
       </c>
       <c r="K44">
-        <v>42121800</v>
+        <v>33654700</v>
       </c>
       <c r="L44">
-        <v>-1.489990234375</v>
+        <v>-1.11665856838226</v>
       </c>
       <c r="M44">
-        <v>46.9703025817871</v>
+        <v>54.3410568237305</v>
       </c>
       <c r="N44">
-        <v>-18.5084857940674</v>
+        <v>-1.37647461891174</v>
       </c>
       <c r="O44" t="s">
         <v>1</v>
       </c>
       <c r="P44">
-        <v>57.9281425476074</v>
+        <v>56.2780990600586</v>
       </c>
       <c r="Q44">
-        <v>725.990234375</v>
+        <v>718.006164550781</v>
       </c>
       <c r="R44">
-        <v>723.10791015625</v>
+        <v>718.503051757813</v>
       </c>
       <c r="S44">
-        <v>722.2724609375</v>
+        <v>720.065307617188</v>
       </c>
       <c r="T44">
-        <v>2.51043701171875</v>
+        <v>2.456787109375</v>
       </c>
       <c r="U44">
-        <v>5.2562255859375</v>
+        <v>3.99322509765625</v>
       </c>
       <c r="V44">
-        <v>10.9642333984375</v>
+        <v>7.56854248046875</v>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="1">
-        <v>46202</v>
+      <c r="A45" s="2">
+        <v>46211</v>
       </c>
       <c r="B45">
-        <v>3.40582275390625</v>
+        <v>-4.7235107421875</v>
       </c>
       <c r="C45">
-        <v>-7.25604248046875</v>
+        <v>-3.04364013671875</v>
       </c>
       <c r="D45">
-        <v>-1.9508056640625</v>
+        <v>-5.07476806640625</v>
       </c>
       <c r="E45">
-        <v>713.989990234375</v>
+        <v>704.950012207031</v>
       </c>
       <c r="F45">
-        <v>724.580017089844</v>
+        <v>712.259887695313</v>
       </c>
       <c r="G45">
-        <v>705.171997070313</v>
+        <v>700.909973144531</v>
       </c>
       <c r="H45">
-        <v>724.080017089844</v>
+        <v>711.440002441406</v>
       </c>
       <c r="I45">
-        <v>725.809997558594</v>
+        <v>715.620361328125</v>
       </c>
       <c r="J45">
-        <v>714.771484375</v>
+        <v>704.994506835938</v>
       </c>
       <c r="K45">
-        <v>44939000</v>
+        <v>35603100</v>
       </c>
       <c r="L45">
-        <v>-2.04951691627502</v>
+        <v>-1.43523001670837</v>
       </c>
       <c r="M45">
-        <v>57.6382751464844</v>
+        <v>55.0994873046875</v>
       </c>
       <c r="N45">
-        <v>-16.8400115966797</v>
+        <v>-16.1432189941406</v>
       </c>
       <c r="O45" t="s">
+        <v>23</v>
+      </c>
+      <c r="P45">
+        <v>-15.6323156356812</v>
+      </c>
+      <c r="Q45">
+        <v>712.987182617188</v>
+      </c>
+      <c r="R45">
+        <v>717.214111328125</v>
+      </c>
+      <c r="S45">
+        <v>719.531494140625</v>
+      </c>
+      <c r="T45">
+        <v>3.3604736328125</v>
+      </c>
+      <c r="U45">
+        <v>4.08453369140625</v>
+      </c>
+      <c r="V45">
+        <v>10.6258544921875</v>
+      </c>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="2">
+        <v>46210</v>
+      </c>
+      <c r="B46">
+        <v>-7.9444580078125</v>
+      </c>
+      <c r="C46">
+        <v>-0.99530029296875</v>
+      </c>
+      <c r="D46">
+        <v>-5.45904541015625</v>
+      </c>
+      <c r="E46">
+        <v>714.169982910156</v>
+      </c>
+      <c r="F46">
+        <v>716.349975585938</v>
+      </c>
+      <c r="G46">
+        <v>704.900024414063</v>
+      </c>
+      <c r="H46">
+        <v>709.429992675781</v>
+      </c>
+      <c r="I46">
+        <v>714.261169433594</v>
+      </c>
+      <c r="J46">
+        <v>704.237060546875</v>
+      </c>
+      <c r="K46">
+        <v>42483000</v>
+      </c>
+      <c r="L46">
+        <v>-2.93475341796875</v>
+      </c>
+      <c r="M46">
+        <v>65.706657409668</v>
+      </c>
+      <c r="N46">
+        <v>-6.48241281509399</v>
+      </c>
+      <c r="O46" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46">
+        <v>-38.1205101013184</v>
+      </c>
+      <c r="Q46">
+        <v>715.312561035156</v>
+      </c>
+      <c r="R46">
+        <v>718.993896484375</v>
+      </c>
+      <c r="S46">
+        <v>720.435485839844</v>
+      </c>
+      <c r="T46">
+        <v>-2.08880615234375</v>
+      </c>
+      <c r="U46">
+        <v>-0.6629638671875</v>
+      </c>
+      <c r="V46">
+        <v>10.0241088867188</v>
+      </c>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B47">
+        <v>-2.8165283203125</v>
+      </c>
+      <c r="C47">
+        <v>0.947509765625</v>
+      </c>
+      <c r="D47">
+        <v>-2.495361328125</v>
+      </c>
+      <c r="E47">
+        <v>719.929992675781</v>
+      </c>
+      <c r="F47">
+        <v>726.080017089844</v>
+      </c>
+      <c r="G47">
+        <v>718.450012207031</v>
+      </c>
+      <c r="H47">
+        <v>722.820007324219</v>
+      </c>
+      <c r="I47">
+        <v>729.223693847656</v>
+      </c>
+      <c r="J47">
+        <v>718.437683105469</v>
+      </c>
+      <c r="K47">
+        <v>30220400</v>
+      </c>
+      <c r="L47">
+        <v>-2.4647536277771</v>
+      </c>
+      <c r="M47">
+        <v>70.2612838745117</v>
+      </c>
+      <c r="N47">
+        <v>3.65661525726318</v>
+      </c>
+      <c r="O47" t="s">
         <v>1</v>
       </c>
-      <c r="P45">
-        <v>20.9863204956055</v>
-      </c>
-      <c r="Q45">
-        <v>716.725952148438</v>
-      </c>
-      <c r="R45">
-        <v>719.314147949219</v>
-      </c>
-      <c r="S45">
-        <v>720.439880371094</v>
-      </c>
-      <c r="T45">
-        <v>1.22998046875</v>
-      </c>
-      <c r="U45">
-        <v>9.5994873046875</v>
-      </c>
-      <c r="V45">
-        <v>11.0385131835938</v>
+      <c r="P47">
+        <v>18.3796253204346</v>
+      </c>
+      <c r="Q47">
+        <v>721.317932128906</v>
+      </c>
+      <c r="R47">
+        <v>721.685180664063</v>
+      </c>
+      <c r="S47">
+        <v>721.850463867188</v>
+      </c>
+      <c r="T47">
+        <v>3.1436767578125</v>
+      </c>
+      <c r="U47">
+        <v>-0.0123291015625</v>
+      </c>
+      <c r="V47">
+        <v>10.7860107421875</v>
       </c>
     </row>
   </sheetData>
